--- a/outputs/week2_excel/603418_友升股份_三表抽取.xlsx
+++ b/outputs/week2_excel/603418_友升股份_三表抽取.xlsx
@@ -2306,13 +2306,13 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>张松满</t>
+          <t>孙国奉</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>162.5</t>
+          <t>175.0</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
@@ -2386,13 +2386,13 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>孙国奉</t>
+          <t>张松满</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>175.0</t>
+          <t>162.5</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>东方富海（上海）创业投资企业（有限合伙）</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
+          <t>东方富海（上海）创业投资企业（有限合伙）</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
@@ -2584,7 +2584,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
@@ -2622,7 +2622,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
@@ -2660,7 +2660,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>深圳市创新投资集团有限公司</t>
+          <t>镇江红土创业投资有限公司</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
@@ -2698,7 +2698,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
+          <t>昆山红土高新创业投资有限公司</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>深圳市创新投资集团有限公司</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
@@ -2752,7 +2752,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2812,7 +2812,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>镇江红土创业投资有限公司</t>
+          <t>丰利财富（北京）国际资本管理股份有限公司</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
@@ -2850,7 +2850,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>昆山红土高新创业投资有限公司</t>
+          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
@@ -2866,7 +2866,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2888,7 +2888,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>丰利财富（北京）国际资本管理股份有限公司</t>
+          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
@@ -2926,15 +2926,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>丰利财富（北京）国际资本管理股份有限公司</t>
+          <t>曾烨</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
@@ -2946,7 +2942,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2968,7 +2964,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>曾烨</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
@@ -3082,11 +3078,15 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>深圳市创新投资集团有限公司</t>
+          <t>丰利财富（北京）国际资本管理股份有限公司</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
@@ -3120,7 +3120,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>刘云锋</t>
+          <t>深圳市创新投资集团有限公司</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3158,7 +3158,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
+          <t>刘云锋</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
@@ -3212,7 +3212,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3234,7 +3234,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
+          <t>曾烨</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
@@ -3250,7 +3250,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3272,7 +3272,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>CASREV FUND</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
@@ -3288,7 +3288,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>珠海拓域投资合伙企业（有限合伙）</t>
+          <t>夏东</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>曾烨</t>
+          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
@@ -3402,7 +3402,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3424,7 +3424,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
+          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
@@ -3462,7 +3462,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
@@ -3478,7 +3478,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3500,7 +3500,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>夏东</t>
+          <t>CASREV FUND</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
@@ -3538,7 +3538,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
+          <t>珠海拓域投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
@@ -3576,13 +3576,13 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
+          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>1584.0</t>
+          <t>7412.0</t>
         </is>
       </c>
       <c r="G58" t="inlineStr"/>
@@ -3618,13 +3618,13 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>CASREV FUND</t>
+          <t>珠海拓域投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>1000.0</t>
         </is>
       </c>
       <c r="G59" t="inlineStr"/>
@@ -3660,13 +3660,13 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>夏东</t>
+          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>1584.0</t>
         </is>
       </c>
       <c r="G60" t="inlineStr"/>
@@ -3702,15 +3702,11 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>珠海拓域投资合伙企业（有限合伙）</t>
+          <t>火炬电子科技股份有限公司</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
@@ -3722,7 +3718,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3744,11 +3740,15 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>火炬电子科技股份有限公司</t>
+          <t>CASREV FUND</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr"/>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
@@ -3760,7 +3760,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3782,13 +3782,13 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
+          <t>夏东</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
-          <t>7412.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="G63" t="inlineStr"/>
@@ -3866,15 +3866,11 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>火炬电子科技股份有限公司</t>
+          <t>中小企业发展基金（深圳有限合伙）</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>5000.0</t>
-        </is>
-      </c>
+      <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
@@ -3886,7 +3882,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3908,11 +3904,15 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>中小企业发展基金（深圳有限合伙）</t>
+          <t>火炬电子科技股份有限公司</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr"/>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>5000.0</t>
+        </is>
+      </c>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
@@ -3924,7 +3924,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3984,7 +3984,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>张俊武</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
@@ -4022,15 +4022,11 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>昆山谷捷金属制品有限公司</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr"/>
@@ -4042,7 +4038,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -4064,7 +4060,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>张俊武</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
@@ -4102,11 +4098,15 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>昆山谷捷金属制品有限公司</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr"/>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr"/>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -4318,7 +4318,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>上海广弘实业有限公司</t>
+          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
+          <t>上海广弘实业有限公司</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
@@ -4474,11 +4474,15 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>黄山佳捷股权管理中心（有限合伙）</t>
+          <t>上海广弘实业有限公司</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr"/>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>10377.0</t>
+        </is>
+      </c>
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr"/>
@@ -4490,7 +4494,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -4512,15 +4516,11 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>上海广弘实业有限公司</t>
+          <t>黄山佳捷股权管理中心（有限合伙）</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>10377.0</t>
-        </is>
-      </c>
+      <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr"/>
@@ -4532,7 +4532,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -4554,7 +4554,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>张俊武</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
@@ -4592,7 +4592,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>张俊武</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
@@ -4630,7 +4630,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>上海广弘实业有限公司</t>
+          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
         </is>
       </c>
       <c r="E85" t="inlineStr"/>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
+          <t>上海广弘实业有限公司</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
@@ -4744,7 +4744,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
@@ -5432,14 +5432,22 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>上海市青浦县徐泾乡工业公司</t>
+          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr"/>
-      <c r="G102" t="inlineStr"/>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>1020.0</t>
+        </is>
+      </c>
       <c r="H102" t="inlineStr"/>
-      <c r="I102" t="inlineStr"/>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>1020.0</t>
+        </is>
+      </c>
       <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr">
         <is>
@@ -5448,7 +5456,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5516,22 +5524,14 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>罗世兵</t>
+          <t>友升太平洋(美国)投资有限公司</t>
         </is>
       </c>
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr"/>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>204.0</t>
-        </is>
-      </c>
+      <c r="G104" t="inlineStr"/>
       <c r="H104" t="inlineStr"/>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>204.0</t>
-        </is>
-      </c>
+      <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr">
         <is>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5562,14 +5562,22 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>友升太平洋(美国)投资有限公司</t>
+          <t>上海泽升贸易有限公司</t>
         </is>
       </c>
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr"/>
-      <c r="G105" t="inlineStr"/>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>8976.0</t>
+        </is>
+      </c>
       <c r="H105" t="inlineStr"/>
-      <c r="I105" t="inlineStr"/>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>8976.0</t>
+        </is>
+      </c>
       <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr">
         <is>
@@ -5578,7 +5586,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5600,22 +5608,14 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>上海泽升贸易有限公司</t>
+          <t>上海市青浦县徐泾乡工业公司</t>
         </is>
       </c>
       <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr"/>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>8976.0</t>
-        </is>
-      </c>
+      <c r="G106" t="inlineStr"/>
       <c r="H106" t="inlineStr"/>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>8976.0</t>
-        </is>
-      </c>
+      <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr">
         <is>
@@ -5624,7 +5624,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5646,20 +5646,20 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
+          <t>罗世兵</t>
         </is>
       </c>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr">
         <is>
-          <t>1020.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="H107" t="inlineStr"/>
       <c r="I107" t="inlineStr">
         <is>
-          <t>1020.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="J107" t="inlineStr"/>
@@ -5692,23 +5692,23 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
+          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>1020.0</t>
         </is>
       </c>
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>1020.0</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>3600.0</t>
+          <t>2040.0</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -5742,22 +5742,26 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr"/>
+          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr">
         <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="H109" t="inlineStr"/>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
+          <t>1800.0</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>3600.0</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr">
         <is>
@@ -5766,7 +5770,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5788,26 +5792,22 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>罗世兵</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>204.0</t>
-        </is>
-      </c>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr">
         <is>
-          <t>204.0</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>408.0</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr"/>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr">
         <is>
@@ -5816,7 +5816,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5838,22 +5838,26 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>上海骁墨信息技术服务中心(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr"/>
+          <t>上海泽升贸易有限公司</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>8976.0</t>
+        </is>
+      </c>
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr">
         <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr"/>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
+          <t>8976.0</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>17952.0</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr">
         <is>
@@ -5862,7 +5866,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5884,20 +5888,20 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
+          <t>上海骁墨信息技术服务中心(有限合伙)</t>
         </is>
       </c>
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr">
         <is>
-          <t>840.0</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="H112" t="inlineStr"/>
       <c r="I112" t="inlineStr">
         <is>
-          <t>840.0</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="J112" t="inlineStr"/>
@@ -5930,23 +5934,23 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>上海泽升贸易有限公司</t>
+          <t>罗世兵</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>8976.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr">
         <is>
-          <t>8976.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>17952.0</t>
+          <t>408.0</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -5980,26 +5984,22 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>1020.0</t>
-        </is>
-      </c>
+          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr">
         <is>
-          <t>1020.0</t>
-        </is>
-      </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>2040.0</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr"/>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
       <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr">
         <is>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6030,22 +6030,30 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>深圳市达晨创程私募股权投资基金企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr"/>
-      <c r="F115" t="inlineStr"/>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>7000.0</t>
+        </is>
+      </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>86.5984</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr"/>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>86.5984</t>
-        </is>
-      </c>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>1680.0</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr">
         <is>
@@ -6054,7 +6062,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -6076,20 +6084,20 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>上海联炻企业管理中心(有限合伙)</t>
+          <t>江西赣江新区财投晨源股权投资中心(有限合伙)</t>
         </is>
       </c>
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="H116" t="inlineStr"/>
       <c r="I116" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="J116" t="inlineStr"/>
@@ -6168,20 +6176,20 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙)</t>
+          <t>上海联炻企业管理中心(有限合伙)</t>
         </is>
       </c>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="H118" t="inlineStr"/>
       <c r="I118" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="J118" t="inlineStr"/>
@@ -6214,22 +6222,30 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>深圳市财智创赢私募股权投资企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr"/>
-      <c r="F119" t="inlineStr"/>
+          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>3000.0</t>
+        </is>
+      </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>10.1093</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr"/>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>10.1093</t>
-        </is>
-      </c>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>720.0</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr">
         <is>
@@ -6238,7 +6254,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -6260,30 +6276,22 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>840.0</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>7000.0</t>
-        </is>
-      </c>
+          <t>深圳市达晨财智创业投资管理有限公司</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr"/>
+      <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr">
         <is>
-          <t>840.0</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>1680.0</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr"/>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
       <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr">
         <is>
@@ -6292,7 +6300,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6314,20 +6322,20 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>安吉璞颉企业管理合伙企业(有限合伙)</t>
+          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr">
         <is>
-          <t>148.6667</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="H121" t="inlineStr"/>
       <c r="I121" t="inlineStr">
         <is>
-          <t>148.6667</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="J121" t="inlineStr"/>
@@ -6360,27 +6368,27 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
+          <t>上海骁墨信息技术服务中心(有限合伙)</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>1500.0</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
           <t>360.0</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>3000.0</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>720.0</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -6414,20 +6422,20 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>上海杉创智至创业投资合伙企业(有限合伙)</t>
+          <t>深圳市杉晖创业投资合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr">
         <is>
-          <t>59.4667</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="H123" t="inlineStr"/>
       <c r="I123" t="inlineStr">
         <is>
-          <t>59.4667</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="J123" t="inlineStr"/>
@@ -6460,20 +6468,20 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>深圳市达晨财智创业投资管理有限公司</t>
+          <t>深圳市达晨创程私募股权投资基金企业(有限合伙)</t>
         </is>
       </c>
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>86.5984</t>
         </is>
       </c>
       <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>86.5984</t>
         </is>
       </c>
       <c r="J124" t="inlineStr"/>
@@ -6506,20 +6514,20 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>江西赣江新区财投晨源股权投资中心(有限合伙)</t>
+          <t>上海杉创智至创业投资合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr"/>
       <c r="G125" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>59.4667</t>
         </is>
       </c>
       <c r="H125" t="inlineStr"/>
       <c r="I125" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>59.4667</t>
         </is>
       </c>
       <c r="J125" t="inlineStr"/>
@@ -6552,30 +6560,22 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>上海骁墨信息技术服务中心(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>1500.0</t>
-        </is>
-      </c>
+          <t>深圳市财智创赢私募股权投资企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr"/>
+      <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr">
         <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr"/>
+          <t>10.1093</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>10.1093</t>
+        </is>
+      </c>
       <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr">
         <is>
@@ -6584,7 +6584,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6606,20 +6606,20 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>深圳市杉晖创业投资合伙企业(有限合伙)</t>
+          <t>安吉璞颉企业管理合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr"/>
       <c r="G127" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>148.6667</t>
         </is>
       </c>
       <c r="H127" t="inlineStr"/>
       <c r="I127" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>148.6667</t>
         </is>
       </c>
       <c r="J127" t="inlineStr"/>
@@ -7502,7 +7502,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>华泰大健康一号</t>
+          <t>高新同华</t>
         </is>
       </c>
       <c r="E145" t="inlineStr"/>
@@ -7540,7 +7540,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>黄学英/刘鸿雁</t>
+          <t>黄学英</t>
         </is>
       </c>
       <c r="E146" t="inlineStr"/>
@@ -7556,7 +7556,7 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -7578,7 +7578,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>高新同华</t>
+          <t>周乃鼎</t>
         </is>
       </c>
       <c r="E147" t="inlineStr"/>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -7616,7 +7616,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>复星惟盈</t>
+          <t>陆民</t>
         </is>
       </c>
       <c r="E148" t="inlineStr"/>
@@ -7630,11 +7630,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L148" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
+      <c r="L148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -7654,7 +7650,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>黄学英</t>
+          <t>华泰大健康一号</t>
         </is>
       </c>
       <c r="E149" t="inlineStr"/>
@@ -7692,7 +7688,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>苏州贤达</t>
+          <t>复星惟盈</t>
         </is>
       </c>
       <c r="E150" t="inlineStr"/>
@@ -7730,7 +7726,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>周乃鼎</t>
+          <t>国寿疌泉</t>
         </is>
       </c>
       <c r="E151" t="inlineStr"/>
@@ -7746,7 +7742,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -7768,7 +7764,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>陆民</t>
+          <t>史建伟</t>
         </is>
       </c>
       <c r="E152" t="inlineStr"/>
@@ -7782,7 +7778,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L152" t="inlineStr"/>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -7802,7 +7802,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>史建伟</t>
+          <t>黄学英/刘鸿雁</t>
         </is>
       </c>
       <c r="E153" t="inlineStr"/>
@@ -7840,7 +7840,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Cheer Rise Consultants Limited</t>
+          <t>周金清</t>
         </is>
       </c>
       <c r="E154" t="inlineStr"/>
@@ -7856,7 +7856,7 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -7878,7 +7878,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>周金清</t>
+          <t>Cheer Rise Consultants Limited</t>
         </is>
       </c>
       <c r="E155" t="inlineStr"/>
@@ -7894,7 +7894,7 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -7916,7 +7916,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>国寿疌泉</t>
+          <t>苏州贤达</t>
         </is>
       </c>
       <c r="E156" t="inlineStr"/>
@@ -7992,7 +7992,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>深圳中证投资有限责任公司</t>
+          <t>QM101 Limited</t>
         </is>
       </c>
       <c r="E158" t="inlineStr"/>
@@ -8030,7 +8030,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>金石智娱股权投资（深圳）合伙企业（有限合伙）</t>
+          <t>华金同达（深圳）投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E159" t="inlineStr"/>
@@ -8106,7 +8106,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>香港迅雷有限公司</t>
         </is>
       </c>
       <c r="E161" t="inlineStr"/>
@@ -8122,7 +8122,7 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -8144,7 +8144,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>华金同达（深圳）投资合伙企业（有限合伙）</t>
+          <t>金石智娱股权投资（深圳）合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E162" t="inlineStr"/>
@@ -8182,7 +8182,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>厦门富凯海创投资管理有限责任公司</t>
+          <t>北京岚锋创视网络科技有限公司</t>
         </is>
       </c>
       <c r="E163" t="inlineStr"/>
@@ -8198,7 +8198,7 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -8220,7 +8220,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>深圳中证投资有限责任公司</t>
         </is>
       </c>
       <c r="E164" t="inlineStr"/>
@@ -8258,7 +8258,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>QM101 Limited</t>
+          <t>厦门富凯海创投资管理有限责任公司</t>
         </is>
       </c>
       <c r="E165" t="inlineStr"/>
@@ -8296,7 +8296,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>QM101 Limited</t>
+          <t>EARN ACE LIMITED</t>
         </is>
       </c>
       <c r="E166" t="inlineStr"/>
@@ -8334,7 +8334,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>QM101 Limited</t>
         </is>
       </c>
       <c r="E167" t="inlineStr"/>
@@ -8372,11 +8372,15 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>北京岚锋创视网络科技有限公司</t>
         </is>
       </c>
       <c r="E168" t="inlineStr"/>
-      <c r="F168" t="inlineStr"/>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G168" t="inlineStr"/>
       <c r="H168" t="inlineStr"/>
       <c r="I168" t="inlineStr"/>
@@ -8386,11 +8390,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L168" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
+      <c r="L168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -8410,15 +8410,11 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>香港迅雷有限公司</t>
         </is>
       </c>
       <c r="E169" t="inlineStr"/>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F169" t="inlineStr"/>
       <c r="G169" t="inlineStr"/>
       <c r="H169" t="inlineStr"/>
       <c r="I169" t="inlineStr"/>
@@ -8428,7 +8424,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L169" t="inlineStr"/>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -8448,7 +8448,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>EARN ACE LIMITED</t>
         </is>
       </c>
       <c r="E170" t="inlineStr"/>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>QM101 Limited</t>
         </is>
       </c>
       <c r="E171" t="inlineStr"/>
@@ -8562,7 +8562,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>北京岚锋创视网络科技有限公司</t>
         </is>
       </c>
       <c r="E173" t="inlineStr"/>
@@ -8600,7 +8600,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>QM101 Limited</t>
+          <t>香港迅雷有限公司</t>
         </is>
       </c>
       <c r="E174" t="inlineStr"/>
@@ -8802,15 +8802,11 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>吴功友(王金林代持)</t>
+          <t>牛威</t>
         </is>
       </c>
       <c r="E179" t="inlineStr"/>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>400.0</t>
-        </is>
-      </c>
+      <c r="F179" t="inlineStr"/>
       <c r="G179" t="inlineStr"/>
       <c r="H179" t="inlineStr"/>
       <c r="I179" t="inlineStr"/>
@@ -8822,7 +8818,7 @@
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -8844,7 +8840,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>牛威</t>
+          <t>吴功友</t>
         </is>
       </c>
       <c r="E180" t="inlineStr"/>
@@ -8882,13 +8878,13 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>四方股份</t>
+          <t>吴功友(王金林代持)</t>
         </is>
       </c>
       <c r="E181" t="inlineStr"/>
       <c r="F181" t="inlineStr">
         <is>
-          <t>1200.0</t>
+          <t>400.0</t>
         </is>
       </c>
       <c r="G181" t="inlineStr"/>
@@ -8924,11 +8920,15 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>吴功友</t>
+          <t>四方股份</t>
         </is>
       </c>
       <c r="E182" t="inlineStr"/>
-      <c r="F182" t="inlineStr"/>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>1200.0</t>
+        </is>
+      </c>
       <c r="G182" t="inlineStr"/>
       <c r="H182" t="inlineStr"/>
       <c r="I182" t="inlineStr"/>
@@ -8940,7 +8940,7 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -9004,20 +9004,20 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>策星揽月</t>
+          <t>幸福二期</t>
         </is>
       </c>
       <c r="E184" t="inlineStr"/>
       <c r="F184" t="inlineStr"/>
       <c r="G184" t="inlineStr">
         <is>
-          <t>412.5</t>
+          <t>300.0</t>
         </is>
       </c>
       <c r="H184" t="inlineStr"/>
       <c r="I184" t="inlineStr">
         <is>
-          <t>412.5</t>
+          <t>300.0</t>
         </is>
       </c>
       <c r="J184" t="inlineStr"/>
@@ -9092,20 +9092,20 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>中科星图股份有限公司</t>
+          <t>策星九天</t>
         </is>
       </c>
       <c r="E186" t="inlineStr"/>
       <c r="F186" t="inlineStr"/>
       <c r="G186" t="inlineStr">
         <is>
-          <t>3825.0</t>
+          <t>2345.0781</t>
         </is>
       </c>
       <c r="H186" t="inlineStr"/>
       <c r="I186" t="inlineStr">
         <is>
-          <t>3825.0</t>
+          <t>2345.0781</t>
         </is>
       </c>
       <c r="J186" t="inlineStr"/>
@@ -9138,20 +9138,20 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>策星九天</t>
+          <t>中科星图股份有限公司</t>
         </is>
       </c>
       <c r="E187" t="inlineStr"/>
       <c r="F187" t="inlineStr"/>
       <c r="G187" t="inlineStr">
         <is>
-          <t>2345.0781</t>
+          <t>3825.0</t>
         </is>
       </c>
       <c r="H187" t="inlineStr"/>
       <c r="I187" t="inlineStr">
         <is>
-          <t>2345.0781</t>
+          <t>3825.0</t>
         </is>
       </c>
       <c r="J187" t="inlineStr"/>
@@ -9226,20 +9226,20 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>幸福一期</t>
+          <t>策星揽月</t>
         </is>
       </c>
       <c r="E189" t="inlineStr"/>
       <c r="F189" t="inlineStr"/>
       <c r="G189" t="inlineStr">
         <is>
-          <t>917.4219</t>
+          <t>412.5</t>
         </is>
       </c>
       <c r="H189" t="inlineStr"/>
       <c r="I189" t="inlineStr">
         <is>
-          <t>917.4219</t>
+          <t>412.5</t>
         </is>
       </c>
       <c r="J189" t="inlineStr"/>
@@ -9272,20 +9272,20 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>策星银河</t>
+          <t>幸福一期</t>
         </is>
       </c>
       <c r="E190" t="inlineStr"/>
       <c r="F190" t="inlineStr"/>
       <c r="G190" t="inlineStr">
         <is>
-          <t>279.0</t>
+          <t>917.4219</t>
         </is>
       </c>
       <c r="H190" t="inlineStr"/>
       <c r="I190" t="inlineStr">
         <is>
-          <t>279.0</t>
+          <t>917.4219</t>
         </is>
       </c>
       <c r="J190" t="inlineStr"/>
@@ -9318,20 +9318,20 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>幸福二期</t>
+          <t>策星银河</t>
         </is>
       </c>
       <c r="E191" t="inlineStr"/>
       <c r="F191" t="inlineStr"/>
       <c r="G191" t="inlineStr">
         <is>
-          <t>300.0</t>
+          <t>279.0</t>
         </is>
       </c>
       <c r="H191" t="inlineStr"/>
       <c r="I191" t="inlineStr">
         <is>
-          <t>300.0</t>
+          <t>279.0</t>
         </is>
       </c>
       <c r="J191" t="inlineStr"/>
@@ -9759,7 +9759,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>生成时间: 2026-06-12T10:04:41.059788</t>
+          <t>生成时间: 2026-06-12T14:44:15.828372</t>
         </is>
       </c>
     </row>

--- a/outputs/week2_excel/603418_友升股份_三表抽取.xlsx
+++ b/outputs/week2_excel/603418_友升股份_三表抽取.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -452,7 +452,10 @@
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="60" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -488,6 +491,21 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>事件类型</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>增资后总股本(万股)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>认购占比</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>原文证据</t>
         </is>
       </c>
@@ -510,6 +528,16 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
+          <t>设立</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>60.00%</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>友升有限成立于1992年12月4日，由徐泾工业公司、友升太平洋美国共同出资设立的中外合资有限责任公司，注册资本为400万美元。徐泾工业公司出资240万美元(60%)，友升太平洋美国出资160万美元(40%)。上海青浦会计师事务所分别于1993年8月20日、1996年12月31日出具验资报告，确认友升有限400万美元注册资金已全部到位。</t>
         </is>
       </c>
@@ -532,6 +560,16 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
+          <t>设立</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>40.00%</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>友升有限成立于1992年12月4日，由徐泾工业公司、友升太平洋美国共同出资设立的中外合资有限责任公司，注册资本为400万美元。徐泾工业公司出资240万美元(60%)，友升太平洋美国出资160万美元(40%)。上海青浦会计师事务所分别于1993年8月20日、1996年12月31日出具验资报告，确认友升有限400万美元注册资金已全部到位。</t>
         </is>
       </c>
@@ -557,6 +595,16 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
+          <t>整体变更</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>74.80%</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>公司由上海友升铝业有限公司整体变更设立。根据会计师出具的《审计报告》，友升有限截至2020年5月31日的净资产为40,482.37万元。以友升有限截至2020年5月31日的净资产40,482.37万元按3.3735:1的比例折合股本12,000.00万元（每股面值1.00元），净资产超过股本部分全部计入资本公积。2020年9月9日，公司在上海市市场监督管理局登记注册。泽升贸易8,976.00万股(74.80%)，达晨创联基金1,800.00万股(15.00%)，共青城泽升1,020.00万股(8.50%)，罗世兵204.00万股(1.70%)。</t>
         </is>
       </c>
@@ -582,6 +630,16 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
+          <t>整体变更</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>15.00%</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>公司由上海友升铝业有限公司整体变更设立。根据会计师出具的《审计报告》，友升有限截至2020年5月31日的净资产为40,482.37万元。以友升有限截至2020年5月31日的净资产40,482.37万元按3.3735:1的比例折合股本12,000.00万元（每股面值1.00元），净资产超过股本部分全部计入资本公积。2020年9月9日，公司在上海市市场监督管理局登记注册。泽升贸易8,976.00万股(74.80%)，达晨创联基金1,800.00万股(15.00%)，共青城泽升1,020.00万股(8.50%)，罗世兵204.00万股(1.70%)。</t>
         </is>
       </c>
@@ -607,6 +665,16 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
+          <t>整体变更</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>8.50%</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>公司由上海友升铝业有限公司整体变更设立。根据会计师出具的《审计报告》，友升有限截至2020年5月31日的净资产为40,482.37万元。以友升有限截至2020年5月31日的净资产40,482.37万元按3.3735:1的比例折合股本12,000.00万元（每股面值1.00元），净资产超过股本部分全部计入资本公积。2020年9月9日，公司在上海市市场监督管理局登记注册。泽升贸易8,976.00万股(74.80%)，达晨创联基金1,800.00万股(15.00%)，共青城泽升1,020.00万股(8.50%)，罗世兵204.00万股(1.70%)。</t>
         </is>
       </c>
@@ -632,6 +700,16 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
+          <t>整体变更</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1.70%</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>公司由上海友升铝业有限公司整体变更设立。根据会计师出具的《审计报告》，友升有限截至2020年5月31日的净资产为40,482.37万元。以友升有限截至2020年5月31日的净资产40,482.37万元按3.3735:1的比例折合股本12,000.00万元（每股面值1.00元），净资产超过股本部分全部计入资本公积。2020年9月9日，公司在上海市市场监督管理局登记注册。泽升贸易8,976.00万股(74.80%)，达晨创联基金1,800.00万股(15.00%)，共青城泽升1,020.00万股(8.50%)，罗世兵204.00万股(1.70%)。</t>
         </is>
       </c>
@@ -663,6 +741,16 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
+          <t>增资</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>6.28%</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>2020年9月，金浦临港基金、金浦科创基金和上海骁墨与本次增资前公司股东泽升贸易、罗世兵、共青城泽升、达晨创联基金共同签署《投资协议》，约定金浦临港基金、金浦科创基金和上海骁墨分别以7,000万元、3,000万元和1,500万元认购发行人新增注册资本840万元、360万元和180万元。新增股份的认购价格为8.3333元/股。2020年9月30日完成工商变更。增资后：泽升贸易67.09%、达晨创联基金13.45%、共青城泽升7.62%、金浦临港基金6.28%、金浦科创基金2.69%、罗世兵1.52%、上海骁墨1.35%。</t>
         </is>
       </c>
@@ -694,6 +782,16 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
+          <t>增资</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2.69%</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>2020年9月，金浦临港基金、金浦科创基金和上海骁墨与本次增资前公司股东泽升贸易、罗世兵、共青城泽升、达晨创联基金共同签署《投资协议》，约定金浦临港基金、金浦科创基金和上海骁墨分别以7,000万元、3,000万元和1,500万元认购发行人新增注册资本840万元、360万元和180万元。新增股份的认购价格为8.3333元/股。2020年9月30日完成工商变更。增资后：泽升贸易67.09%、达晨创联基金13.45%、共青城泽升7.62%、金浦临港基金6.28%、金浦科创基金2.69%、罗世兵1.52%、上海骁墨1.35%。</t>
         </is>
       </c>
@@ -725,6 +823,16 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
+          <t>增资</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1.35%</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>2020年9月，金浦临港基金、金浦科创基金和上海骁墨与本次增资前公司股东泽升贸易、罗世兵、共青城泽升、达晨创联基金共同签署《投资协议》，约定金浦临港基金、金浦科创基金和上海骁墨分别以7,000万元、3,000万元和1,500万元认购发行人新增注册资本840万元、360万元和180万元。新增股份的认购价格为8.3333元/股。2020年9月30日完成工商变更。增资后：泽升贸易67.09%、达晨创联基金13.45%、共青城泽升7.62%、金浦临港基金6.28%、金浦科创基金2.69%、罗世兵1.52%、上海骁墨1.35%。</t>
         </is>
       </c>
@@ -756,6 +864,16 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
+          <t>增资</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2.05%</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>2022年12月4日，友升股份召开第一届董事会第十六次会议，同意增加注册资本至14,480.1333万元，新增股份的认购价格为33.6323元/股。杉晖创业认购297.3333万股(10,000万元)，上海联炻认购297.3333万股(10,000万元)，安吉璞颉认购148.6667万股(5,000万元)，财投晨源认购89.2万股(3,000万元)，深圳达晨创程认购86.5984万股(2,912.5万元)，杉创智至认购59.4667万股(2,000万元)，杭州达晨创程认购51.959万股(1,747.5万元)，达晨财汇认购29.7333万股(1,000万元)，达晨财智认购29.7333万股(1,000万元)，财智创赢认购10.1093万股(340万元)。合计1,100.1333万股，37,000万元。2022年12月19日完成工商变更。</t>
         </is>
       </c>
@@ -787,6 +905,16 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
+          <t>增资</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2.05%</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>2022年12月4日，友升股份召开第一届董事会第十六次会议，同意增加注册资本至14,480.1333万元，新增股份的认购价格为33.6323元/股。杉晖创业认购297.3333万股(10,000万元)，上海联炻认购297.3333万股(10,000万元)，安吉璞颉认购148.6667万股(5,000万元)，财投晨源认购89.2万股(3,000万元)，深圳达晨创程认购86.5984万股(2,912.5万元)，杉创智至认购59.4667万股(2,000万元)，杭州达晨创程认购51.959万股(1,747.5万元)，达晨财汇认购29.7333万股(1,000万元)，达晨财智认购29.7333万股(1,000万元)，财智创赢认购10.1093万股(340万元)。合计1,100.1333万股，37,000万元。2022年12月19日完成工商变更。</t>
         </is>
       </c>
@@ -818,6 +946,16 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
+          <t>增资</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1.03%</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
           <t>2022年12月4日，友升股份召开第一届董事会第十六次会议，同意增加注册资本至14,480.1333万元，新增股份的认购价格为33.6323元/股。杉晖创业认购297.3333万股(10,000万元)，上海联炻认购297.3333万股(10,000万元)，安吉璞颉认购148.6667万股(5,000万元)，财投晨源认购89.2万股(3,000万元)，深圳达晨创程认购86.5984万股(2,912.5万元)，杉创智至认购59.4667万股(2,000万元)，杭州达晨创程认购51.959万股(1,747.5万元)，达晨财汇认购29.7333万股(1,000万元)，达晨财智认购29.7333万股(1,000万元)，财智创赢认购10.1093万股(340万元)。合计1,100.1333万股，37,000万元。2022年12月19日完成工商变更。</t>
         </is>
       </c>
@@ -849,6 +987,16 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
+          <t>增资</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>0.62%</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
           <t>2022年12月4日，友升股份召开第一届董事会第十六次会议，同意增加注册资本至14,480.1333万元，新增股份的认购价格为33.6323元/股。杉晖创业认购297.3333万股(10,000万元)，上海联炻认购297.3333万股(10,000万元)，安吉璞颉认购148.6667万股(5,000万元)，财投晨源认购89.2万股(3,000万元)，深圳达晨创程认购86.5984万股(2,912.5万元)，杉创智至认购59.4667万股(2,000万元)，杭州达晨创程认购51.959万股(1,747.5万元)，达晨财汇认购29.7333万股(1,000万元)，达晨财智认购29.7333万股(1,000万元)，财智创赢认购10.1093万股(340万元)。合计1,100.1333万股，37,000万元。2022年12月19日完成工商变更。</t>
         </is>
       </c>
@@ -880,6 +1028,16 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
+          <t>增资</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>0.60%</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
           <t>2022年12月4日，友升股份召开第一届董事会第十六次会议，同意增加注册资本至14,480.1333万元，新增股份的认购价格为33.6323元/股。杉晖创业认购297.3333万股(10,000万元)，上海联炻认购297.3333万股(10,000万元)，安吉璞颉认购148.6667万股(5,000万元)，财投晨源认购89.2万股(3,000万元)，深圳达晨创程认购86.5984万股(2,912.5万元)，杉创智至认购59.4667万股(2,000万元)，杭州达晨创程认购51.959万股(1,747.5万元)，达晨财汇认购29.7333万股(1,000万元)，达晨财智认购29.7333万股(1,000万元)，财智创赢认购10.1093万股(340万元)。合计1,100.1333万股，37,000万元。2022年12月19日完成工商变更。</t>
         </is>
       </c>
@@ -911,6 +1069,16 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
+          <t>增资</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>0.41%</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
           <t>2022年12月4日，友升股份召开第一届董事会第十六次会议，同意增加注册资本至14,480.1333万元，新增股份的认购价格为33.6323元/股。杉晖创业认购297.3333万股(10,000万元)，上海联炻认购297.3333万股(10,000万元)，安吉璞颉认购148.6667万股(5,000万元)，财投晨源认购89.2万股(3,000万元)，深圳达晨创程认购86.5984万股(2,912.5万元)，杉创智至认购59.4667万股(2,000万元)，杭州达晨创程认购51.959万股(1,747.5万元)，达晨财汇认购29.7333万股(1,000万元)，达晨财智认购29.7333万股(1,000万元)，财智创赢认购10.1093万股(340万元)。合计1,100.1333万股，37,000万元。2022年12月19日完成工商变更。</t>
         </is>
       </c>
@@ -942,6 +1110,16 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
+          <t>增资</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>0.36%</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
           <t>2022年12月4日，友升股份召开第一届董事会第十六次会议，同意增加注册资本至14,480.1333万元，新增股份的认购价格为33.6323元/股。杉晖创业认购297.3333万股(10,000万元)，上海联炻认购297.3333万股(10,000万元)，安吉璞颉认购148.6667万股(5,000万元)，财投晨源认购89.2万股(3,000万元)，深圳达晨创程认购86.5984万股(2,912.5万元)，杉创智至认购59.4667万股(2,000万元)，杭州达晨创程认购51.959万股(1,747.5万元)，达晨财汇认购29.7333万股(1,000万元)，达晨财智认购29.7333万股(1,000万元)，财智创赢认购10.1093万股(340万元)。合计1,100.1333万股，37,000万元。2022年12月19日完成工商变更。</t>
         </is>
       </c>
@@ -973,6 +1151,16 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
+          <t>增资</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>0.21%</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
           <t>2022年12月4日，友升股份召开第一届董事会第十六次会议，同意增加注册资本至14,480.1333万元，新增股份的认购价格为33.6323元/股。杉晖创业认购297.3333万股(10,000万元)，上海联炻认购297.3333万股(10,000万元)，安吉璞颉认购148.6667万股(5,000万元)，财投晨源认购89.2万股(3,000万元)，深圳达晨创程认购86.5984万股(2,912.5万元)，杉创智至认购59.4667万股(2,000万元)，杭州达晨创程认购51.959万股(1,747.5万元)，达晨财汇认购29.7333万股(1,000万元)，达晨财智认购29.7333万股(1,000万元)，财智创赢认购10.1093万股(340万元)。合计1,100.1333万股，37,000万元。2022年12月19日完成工商变更。</t>
         </is>
       </c>
@@ -1004,6 +1192,16 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
+          <t>增资</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0.21%</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
           <t>2022年12月4日，友升股份召开第一届董事会第十六次会议，同意增加注册资本至14,480.1333万元，新增股份的认购价格为33.6323元/股。杉晖创业认购297.3333万股(10,000万元)，上海联炻认购297.3333万股(10,000万元)，安吉璞颉认购148.6667万股(5,000万元)，财投晨源认购89.2万股(3,000万元)，深圳达晨创程认购86.5984万股(2,912.5万元)，杉创智至认购59.4667万股(2,000万元)，杭州达晨创程认购51.959万股(1,747.5万元)，达晨财汇认购29.7333万股(1,000万元)，达晨财智认购29.7333万股(1,000万元)，财智创赢认购10.1093万股(340万元)。合计1,100.1333万股，37,000万元。2022年12月19日完成工商变更。</t>
         </is>
       </c>
@@ -1034,6 +1232,16 @@
         <v>33.6323</v>
       </c>
       <c r="G20" t="inlineStr">
+        <is>
+          <t>增资</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>0.07%</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
         <is>
           <t>2022年12月4日，友升股份召开第一届董事会第十六次会议，同意增加注册资本至14,480.1333万元，新增股份的认购价格为33.6323元/股。杉晖创业认购297.3333万股(10,000万元)，上海联炻认购297.3333万股(10,000万元)，安吉璞颉认购148.6667万股(5,000万元)，财投晨源认购89.2万股(3,000万元)，深圳达晨创程认购86.5984万股(2,912.5万元)，杉创智至认购59.4667万股(2,000万元)，杭州达晨创程认购51.959万股(1,747.5万元)，达晨财汇认购29.7333万股(1,000万元)，达晨财智认购29.7333万股(1,000万元)，财智创赢认购10.1093万股(340万元)。合计1,100.1333万股，37,000万元。2022年12月19日完成工商变更。</t>
         </is>
@@ -1050,7 +1258,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:M20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1062,7 +1270,10 @@
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="60" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1113,6 +1324,21 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>快照序号</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>股东类型</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>原始创始人</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>原文证据</t>
         </is>
       </c>
@@ -1145,6 +1371,21 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
+          <t>t1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
           <t>友升有限成立于1992年12月4日，由徐泾工业公司、友升太平洋美国共同出资设立的中外合资有限责任公司，注册资本为400万美元。徐泾工业公司出资240万美元(60%)，友升太平洋美国出资160万美元(40%)。上海青浦会计师事务所分别于1993年8月20日、1996年12月31日出具验资报告，确认友升有限400万美元注册资金已全部到位。</t>
         </is>
       </c>
@@ -1177,6 +1418,21 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
+          <t>t1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>外部PE</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
           <t>友升有限成立于1992年12月4日，由徐泾工业公司、友升太平洋美国共同出资设立的中外合资有限责任公司，注册资本为400万美元。徐泾工业公司出资240万美元(60%)，友升太平洋美国出资160万美元(40%)。上海青浦会计师事务所分别于1993年8月20日、1996年12月31日出具验资报告，确认友升有限400万美元注册资金已全部到位。</t>
         </is>
       </c>
@@ -1212,6 +1468,21 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
+          <t>t2</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
           <t>公司由上海友升铝业有限公司整体变更设立。根据会计师出具的《审计报告》，友升有限截至2020年5月31日的净资产为40,482.37万元。以友升有限截至2020年5月31日的净资产40,482.37万元按3.3735:1的比例折合股本12,000.00万元（每股面值1.00元），净资产超过股本部分全部计入资本公积。2020年9月9日，公司在上海市市场监督管理局登记注册。泽升贸易8,976.00万股(74.80%)，达晨创联基金1,800.00万股(15.00%)，共青城泽升1,020.00万股(8.50%)，罗世兵204.00万股(1.70%)。</t>
         </is>
       </c>
@@ -1247,6 +1518,21 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
+          <t>t2</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>外部PE</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
           <t>公司由上海友升铝业有限公司整体变更设立。根据会计师出具的《审计报告》，友升有限截至2020年5月31日的净资产为40,482.37万元。以友升有限截至2020年5月31日的净资产40,482.37万元按3.3735:1的比例折合股本12,000.00万元（每股面值1.00元），净资产超过股本部分全部计入资本公积。2020年9月9日，公司在上海市市场监督管理局登记注册。泽升贸易8,976.00万股(74.80%)，达晨创联基金1,800.00万股(15.00%)，共青城泽升1,020.00万股(8.50%)，罗世兵204.00万股(1.70%)。</t>
         </is>
       </c>
@@ -1282,6 +1568,21 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
+          <t>t2</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>外部PE</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
           <t>公司由上海友升铝业有限公司整体变更设立。根据会计师出具的《审计报告》，友升有限截至2020年5月31日的净资产为40,482.37万元。以友升有限截至2020年5月31日的净资产40,482.37万元按3.3735:1的比例折合股本12,000.00万元（每股面值1.00元），净资产超过股本部分全部计入资本公积。2020年9月9日，公司在上海市市场监督管理局登记注册。泽升贸易8,976.00万股(74.80%)，达晨创联基金1,800.00万股(15.00%)，共青城泽升1,020.00万股(8.50%)，罗世兵204.00万股(1.70%)。</t>
         </is>
       </c>
@@ -1317,6 +1618,21 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
+          <t>t2</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
           <t>公司由上海友升铝业有限公司整体变更设立。根据会计师出具的《审计报告》，友升有限截至2020年5月31日的净资产为40,482.37万元。以友升有限截至2020年5月31日的净资产40,482.37万元按3.3735:1的比例折合股本12,000.00万元（每股面值1.00元），净资产超过股本部分全部计入资本公积。2020年9月9日，公司在上海市市场监督管理局登记注册。泽升贸易8,976.00万股(74.80%)，达晨创联基金1,800.00万股(15.00%)，共青城泽升1,020.00万股(8.50%)，罗世兵204.00万股(1.70%)。</t>
         </is>
       </c>
@@ -1355,6 +1671,21 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
+          <t>t3</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>外部PE</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
           <t>2020年9月，金浦临港基金、金浦科创基金和上海骁墨与本次增资前公司股东泽升贸易、罗世兵、共青城泽升、达晨创联基金共同签署《投资协议》，约定金浦临港基金、金浦科创基金和上海骁墨分别以7,000万元、3,000万元和1,500万元认购发行人新增注册资本840万元、360万元和180万元。新增股份的认购价格为8.3333元/股。2020年9月30日完成工商变更。增资后：泽升贸易67.09%、达晨创联基金13.45%、共青城泽升7.62%、金浦临港基金6.28%、金浦科创基金2.69%、罗世兵1.52%、上海骁墨1.35%。</t>
         </is>
       </c>
@@ -1393,6 +1724,21 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
+          <t>t3</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>外部PE</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
           <t>2020年9月，金浦临港基金、金浦科创基金和上海骁墨与本次增资前公司股东泽升贸易、罗世兵、共青城泽升、达晨创联基金共同签署《投资协议》，约定金浦临港基金、金浦科创基金和上海骁墨分别以7,000万元、3,000万元和1,500万元认购发行人新增注册资本840万元、360万元和180万元。新增股份的认购价格为8.3333元/股。2020年9月30日完成工商变更。增资后：泽升贸易67.09%、达晨创联基金13.45%、共青城泽升7.62%、金浦临港基金6.28%、金浦科创基金2.69%、罗世兵1.52%、上海骁墨1.35%。</t>
         </is>
       </c>
@@ -1431,6 +1777,21 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
+          <t>t3</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>外部PE</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
           <t>2020年9月，金浦临港基金、金浦科创基金和上海骁墨与本次增资前公司股东泽升贸易、罗世兵、共青城泽升、达晨创联基金共同签署《投资协议》，约定金浦临港基金、金浦科创基金和上海骁墨分别以7,000万元、3,000万元和1,500万元认购发行人新增注册资本840万元、360万元和180万元。新增股份的认购价格为8.3333元/股。2020年9月30日完成工商变更。增资后：泽升贸易67.09%、达晨创联基金13.45%、共青城泽升7.62%、金浦临港基金6.28%、金浦科创基金2.69%、罗世兵1.52%、上海骁墨1.35%。</t>
         </is>
       </c>
@@ -1469,6 +1830,21 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
+          <t>t4</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>外部PE</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
           <t>2022年12月4日，友升股份召开第一届董事会第十六次会议，同意增加注册资本至14,480.1333万元，新增股份的认购价格为33.6323元/股。杉晖创业认购297.3333万股(10,000万元)，上海联炻认购297.3333万股(10,000万元)，安吉璞颉认购148.6667万股(5,000万元)，财投晨源认购89.2万股(3,000万元)，深圳达晨创程认购86.5984万股(2,912.5万元)，杉创智至认购59.4667万股(2,000万元)，杭州达晨创程认购51.959万股(1,747.5万元)，达晨财汇认购29.7333万股(1,000万元)，达晨财智认购29.7333万股(1,000万元)，财智创赢认购10.1093万股(340万元)。合计1,100.1333万股，37,000万元。2022年12月19日完成工商变更。</t>
         </is>
       </c>
@@ -1507,6 +1883,21 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
+          <t>t4</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>外部PE</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
           <t>2022年12月4日，友升股份召开第一届董事会第十六次会议，同意增加注册资本至14,480.1333万元，新增股份的认购价格为33.6323元/股。杉晖创业认购297.3333万股(10,000万元)，上海联炻认购297.3333万股(10,000万元)，安吉璞颉认购148.6667万股(5,000万元)，财投晨源认购89.2万股(3,000万元)，深圳达晨创程认购86.5984万股(2,912.5万元)，杉创智至认购59.4667万股(2,000万元)，杭州达晨创程认购51.959万股(1,747.5万元)，达晨财汇认购29.7333万股(1,000万元)，达晨财智认购29.7333万股(1,000万元)，财智创赢认购10.1093万股(340万元)。合计1,100.1333万股，37,000万元。2022年12月19日完成工商变更。</t>
         </is>
       </c>
@@ -1545,6 +1936,21 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
+          <t>t4</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>外部PE</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
           <t>2022年12月4日，友升股份召开第一届董事会第十六次会议，同意增加注册资本至14,480.1333万元，新增股份的认购价格为33.6323元/股。杉晖创业认购297.3333万股(10,000万元)，上海联炻认购297.3333万股(10,000万元)，安吉璞颉认购148.6667万股(5,000万元)，财投晨源认购89.2万股(3,000万元)，深圳达晨创程认购86.5984万股(2,912.5万元)，杉创智至认购59.4667万股(2,000万元)，杭州达晨创程认购51.959万股(1,747.5万元)，达晨财汇认购29.7333万股(1,000万元)，达晨财智认购29.7333万股(1,000万元)，财智创赢认购10.1093万股(340万元)。合计1,100.1333万股，37,000万元。2022年12月19日完成工商变更。</t>
         </is>
       </c>
@@ -1583,6 +1989,21 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
+          <t>t4</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>外部PE</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
           <t>2022年12月4日，友升股份召开第一届董事会第十六次会议，同意增加注册资本至14,480.1333万元，新增股份的认购价格为33.6323元/股。杉晖创业认购297.3333万股(10,000万元)，上海联炻认购297.3333万股(10,000万元)，安吉璞颉认购148.6667万股(5,000万元)，财投晨源认购89.2万股(3,000万元)，深圳达晨创程认购86.5984万股(2,912.5万元)，杉创智至认购59.4667万股(2,000万元)，杭州达晨创程认购51.959万股(1,747.5万元)，达晨财汇认购29.7333万股(1,000万元)，达晨财智认购29.7333万股(1,000万元)，财智创赢认购10.1093万股(340万元)。合计1,100.1333万股，37,000万元。2022年12月19日完成工商变更。</t>
         </is>
       </c>
@@ -1621,6 +2042,21 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
+          <t>t4</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>外部PE</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
           <t>2022年12月4日，友升股份召开第一届董事会第十六次会议，同意增加注册资本至14,480.1333万元，新增股份的认购价格为33.6323元/股。杉晖创业认购297.3333万股(10,000万元)，上海联炻认购297.3333万股(10,000万元)，安吉璞颉认购148.6667万股(5,000万元)，财投晨源认购89.2万股(3,000万元)，深圳达晨创程认购86.5984万股(2,912.5万元)，杉创智至认购59.4667万股(2,000万元)，杭州达晨创程认购51.959万股(1,747.5万元)，达晨财汇认购29.7333万股(1,000万元)，达晨财智认购29.7333万股(1,000万元)，财智创赢认购10.1093万股(340万元)。合计1,100.1333万股，37,000万元。2022年12月19日完成工商变更。</t>
         </is>
       </c>
@@ -1659,6 +2095,21 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
+          <t>t4</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>外部PE</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
           <t>2022年12月4日，友升股份召开第一届董事会第十六次会议，同意增加注册资本至14,480.1333万元，新增股份的认购价格为33.6323元/股。杉晖创业认购297.3333万股(10,000万元)，上海联炻认购297.3333万股(10,000万元)，安吉璞颉认购148.6667万股(5,000万元)，财投晨源认购89.2万股(3,000万元)，深圳达晨创程认购86.5984万股(2,912.5万元)，杉创智至认购59.4667万股(2,000万元)，杭州达晨创程认购51.959万股(1,747.5万元)，达晨财汇认购29.7333万股(1,000万元)，达晨财智认购29.7333万股(1,000万元)，财智创赢认购10.1093万股(340万元)。合计1,100.1333万股，37,000万元。2022年12月19日完成工商变更。</t>
         </is>
       </c>
@@ -1697,6 +2148,21 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
+          <t>t4</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>外部PE</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
           <t>2022年12月4日，友升股份召开第一届董事会第十六次会议，同意增加注册资本至14,480.1333万元，新增股份的认购价格为33.6323元/股。杉晖创业认购297.3333万股(10,000万元)，上海联炻认购297.3333万股(10,000万元)，安吉璞颉认购148.6667万股(5,000万元)，财投晨源认购89.2万股(3,000万元)，深圳达晨创程认购86.5984万股(2,912.5万元)，杉创智至认购59.4667万股(2,000万元)，杭州达晨创程认购51.959万股(1,747.5万元)，达晨财汇认购29.7333万股(1,000万元)，达晨财智认购29.7333万股(1,000万元)，财智创赢认购10.1093万股(340万元)。合计1,100.1333万股，37,000万元。2022年12月19日完成工商变更。</t>
         </is>
       </c>
@@ -1735,6 +2201,21 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
+          <t>t4</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>外部PE</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
           <t>2022年12月4日，友升股份召开第一届董事会第十六次会议，同意增加注册资本至14,480.1333万元，新增股份的认购价格为33.6323元/股。杉晖创业认购297.3333万股(10,000万元)，上海联炻认购297.3333万股(10,000万元)，安吉璞颉认购148.6667万股(5,000万元)，财投晨源认购89.2万股(3,000万元)，深圳达晨创程认购86.5984万股(2,912.5万元)，杉创智至认购59.4667万股(2,000万元)，杭州达晨创程认购51.959万股(1,747.5万元)，达晨财汇认购29.7333万股(1,000万元)，达晨财智认购29.7333万股(1,000万元)，财智创赢认购10.1093万股(340万元)。合计1,100.1333万股，37,000万元。2022年12月19日完成工商变更。</t>
         </is>
       </c>
@@ -1773,6 +2254,21 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
+          <t>t4</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>外部PE</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
           <t>2022年12月4日，友升股份召开第一届董事会第十六次会议，同意增加注册资本至14,480.1333万元，新增股份的认购价格为33.6323元/股。杉晖创业认购297.3333万股(10,000万元)，上海联炻认购297.3333万股(10,000万元)，安吉璞颉认购148.6667万股(5,000万元)，财投晨源认购89.2万股(3,000万元)，深圳达晨创程认购86.5984万股(2,912.5万元)，杉创智至认购59.4667万股(2,000万元)，杭州达晨创程认购51.959万股(1,747.5万元)，达晨财汇认购29.7333万股(1,000万元)，达晨财智认购29.7333万股(1,000万元)，财智创赢认购10.1093万股(340万元)。合计1,100.1333万股，37,000万元。2022年12月19日完成工商变更。</t>
         </is>
       </c>
@@ -1810,6 +2306,21 @@
         </is>
       </c>
       <c r="J20" t="inlineStr">
+        <is>
+          <t>t4</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>外部PE</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
         <is>
           <t>2022年12月4日，友升股份召开第一届董事会第十六次会议，同意增加注册资本至14,480.1333万元，新增股份的认购价格为33.6323元/股。杉晖创业认购297.3333万股(10,000万元)，上海联炻认购297.3333万股(10,000万元)，安吉璞颉认购148.6667万股(5,000万元)，财投晨源认购89.2万股(3,000万元)，深圳达晨创程认购86.5984万股(2,912.5万元)，杉创智至认购59.4667万股(2,000万元)，杭州达晨创程认购51.959万股(1,747.5万元)，达晨财汇认购29.7333万股(1,000万元)，达晨财智认购29.7333万股(1,000万元)，财智创赢认购10.1093万股(340万元)。合计1,100.1333万股，37,000万元。2022年12月19日完成工商变更。</t>
         </is>
@@ -1826,7 +2337,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L203"/>
+  <dimension ref="A1:L211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2000,100 +2511,84 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>evidence_text</t>
+          <t>event_context</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>str(min=20)</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>equity_snapshot</t>
+          <t>subscription_flow</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>source_page</t>
+          <t>post_event_total_shares</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>str</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+          <t>float|null</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>equity_snapshot</t>
+          <t>subscription_flow</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>snapshot_date</t>
+          <t>post_event_total_capital</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>str(YYYY-MM-DD)</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+          <t>float|null</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>equity_snapshot</t>
+          <t>subscription_flow</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>snapshot_type</t>
+          <t>payment_method</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>str</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>equity_snapshot</t>
+          <t>subscription_flow</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>total_shares</t>
+          <t>subscription_ratio</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>float|null</t>
+          <t>str|null</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -2101,20 +2596,24 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>equity_snapshot</t>
+          <t>subscription_flow</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>total_capital</t>
+          <t>evidence_text</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>float|null</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>str(min=20)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2124,7 +2623,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>shareholder_name</t>
+          <t>source_page</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2146,15 +2645,19 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>shares_held</t>
+          <t>snapshot_date</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>float|null</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>str(YYYY-MM-DD)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2164,15 +2667,19 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>capital_contribution</t>
+          <t>snapshot_type</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>float|null</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2182,12 +2689,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>shareholding_ratio</t>
+          <t>total_shares</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>str|null</t>
+          <t>float|null</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -2200,433 +2707,269 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
+          <t>total_capital</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>float|null</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>equity_snapshot</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>shareholder_name</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>equity_snapshot</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>shares_held</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>float|null</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>equity_snapshot</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>capital_contribution</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>float|null</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>equity_snapshot</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>shareholding_ratio</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>str|null</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>equity_snapshot</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>snapshot_order</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>int|null</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>equity_snapshot</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>shareholder_type_detail</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>equity_snapshot</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>is_original_founder</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>yes/no/unknown</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>equity_snapshot</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
           <t>evidence_text</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>str(min=20)</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>Cross-Check 结果（相邻时点股本追踪 + 认缴存量对应）</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
         <is>
           <t>公司</t>
         </is>
       </c>
-      <c r="B24" s="1" t="inlineStr">
+      <c r="B32" s="1" t="inlineStr">
         <is>
           <t>上一时点</t>
         </is>
       </c>
-      <c r="C24" s="1" t="inlineStr">
+      <c r="C32" s="1" t="inlineStr">
         <is>
           <t>当前时点</t>
         </is>
       </c>
-      <c r="D24" s="1" t="inlineStr">
+      <c r="D32" s="1" t="inlineStr">
         <is>
           <t>股东名称</t>
         </is>
       </c>
-      <c r="E24" s="1" t="inlineStr">
+      <c r="E32" s="1" t="inlineStr">
         <is>
           <t>上一时点持股数
 (万股)</t>
         </is>
       </c>
-      <c r="F24" s="1" t="inlineStr">
+      <c r="F32" s="1" t="inlineStr">
         <is>
           <t>上一时点出资额
 (万元注册资本)</t>
         </is>
       </c>
-      <c r="G24" s="1" t="inlineStr">
+      <c r="G32" s="1" t="inlineStr">
         <is>
           <t>本次认缴/变化
 (万股)</t>
         </is>
       </c>
-      <c r="H24" s="1" t="inlineStr">
+      <c r="H32" s="1" t="inlineStr">
         <is>
           <t>预期变更后
 持股数(万股)</t>
         </is>
       </c>
-      <c r="I24" s="1" t="inlineStr">
+      <c r="I32" s="1" t="inlineStr">
         <is>
           <t>PDF披露
 持股数(万股)</t>
         </is>
       </c>
-      <c r="J24" s="1" t="inlineStr">
+      <c r="J32" s="1" t="inlineStr">
         <is>
           <t>差额(万股)</t>
         </is>
       </c>
-      <c r="K24" s="1" t="inlineStr">
+      <c r="K32" s="1" t="inlineStr">
         <is>
           <t>状态</t>
         </is>
       </c>
-      <c r="L24" s="1" t="inlineStr">
+      <c r="L32" s="1" t="inlineStr">
         <is>
           <t>说明</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>001282_三联锻造</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2004-06-18</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>2014-05</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>孙国奉</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>175.0</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>001282_三联锻造</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2004-06-18</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>2014-05</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>孙国敏</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>162.5</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>001282_三联锻造</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2004-06-18</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>2014-05</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>张松满</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>162.5</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>301563_云汉芯城</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2008-05-07</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>2014-08</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>武汉力源信息技术股份有限公司</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>301563_云汉芯城</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2008-05-07</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>2014-08</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>东方富海（上海）创业投资企业（有限合伙）</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>301563_云汉芯城</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2008-05-07</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>2014-08</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>深圳市云汉电子有限公司</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>25.0</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>301563_云汉芯城</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2008-05-07</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>2014-08</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>刘云锋</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>25.0</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>301563_云汉芯城</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2008-05-07</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>2014-08</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>301563_云汉芯城</t>
+          <t>001282_三联锻造</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2014-08</t>
+          <t>2004-06-18</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2015-08</t>
+          <t>2014-05</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>孙国奉</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>175.0</t>
+        </is>
+      </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
@@ -2636,35 +2979,35 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
+      <c r="L33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>301563_云汉芯城</t>
+          <t>001282_三联锻造</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2014-08</t>
+          <t>2004-06-18</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2015-08</t>
+          <t>2014-05</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>镇江红土创业投资有限公司</t>
+          <t>张松满</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>162.5</t>
+        </is>
+      </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
@@ -2674,35 +3017,35 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
+      <c r="L34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>301563_云汉芯城</t>
+          <t>001282_三联锻造</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2014-08</t>
+          <t>2004-06-18</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2015-08</t>
+          <t>2014-05</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>昆山红土高新创业投资有限公司</t>
+          <t>孙国敏</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>162.5</t>
+        </is>
+      </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
@@ -2714,7 +3057,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2726,17 +3069,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
+          <t>2008-05-07</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
           <t>2014-08</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>2015-08</t>
-        </is>
-      </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>深圳市创新投资集团有限公司</t>
+          <t>东方富海（上海）创业投资企业（有限合伙）</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
@@ -2764,21 +3107,25 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
+          <t>2008-05-07</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
           <t>2014-08</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>2015-08</t>
-        </is>
-      </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>东方富海（上海）创业投资企业（有限合伙）</t>
+          <t>刘云锋</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>25.0</t>
+        </is>
+      </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
@@ -2802,21 +3149,25 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
+          <t>2008-05-07</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
           <t>2014-08</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>2015-08</t>
-        </is>
-      </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>丰利财富（北京）国际资本管理股份有限公司</t>
+          <t>深圳市云汉电子有限公司</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>25.0</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
@@ -2828,7 +3179,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2840,17 +3191,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
+          <t>2008-05-07</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
           <t>2014-08</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>2015-08</t>
-        </is>
-      </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
@@ -2866,7 +3217,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2878,17 +3229,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
+          <t>2008-05-07</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
           <t>2014-08</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>2015-08</t>
-        </is>
-      </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
+          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
@@ -2916,17 +3267,17 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
+          <t>2014-08</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
           <t>2015-08</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>2015-12-03</t>
-        </is>
-      </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>曾烨</t>
+          <t>东方富海（上海）创业投资企业（有限合伙）</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
@@ -2942,7 +3293,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2954,17 +3305,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
+          <t>2014-08</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
           <t>2015-08</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>2015-12-03</t>
-        </is>
-      </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>丰利财富（北京）国际资本管理股份有限公司</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
@@ -2992,17 +3343,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
+          <t>2014-08</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
           <t>2015-08</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>2015-12-03</t>
-        </is>
-      </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>镇江红土创业投资有限公司</t>
+          <t>深圳市创新投资集团有限公司</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
@@ -3018,7 +3369,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3030,17 +3381,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
+          <t>2014-08</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
           <t>2015-08</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>2015-12-03</t>
-        </is>
-      </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>昆山红土高新创业投资有限公司</t>
+          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
@@ -3056,7 +3407,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3068,25 +3419,21 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
+          <t>2014-08</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
           <t>2015-08</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>2015-12-03</t>
-        </is>
-      </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>丰利财富（北京）国际资本管理股份有限公司</t>
+          <t>昆山红土高新创业投资有限公司</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
@@ -3098,7 +3445,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3110,17 +3457,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
+          <t>2014-08</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
           <t>2015-08</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>2015-12-03</t>
-        </is>
-      </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>深圳市创新投资集团有限公司</t>
+          <t>镇江红土创业投资有限公司</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
@@ -3136,7 +3483,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3148,17 +3495,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
+          <t>2014-08</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
           <t>2015-08</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>2015-12-03</t>
-        </is>
-      </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>刘云锋</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
@@ -3174,7 +3521,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3186,17 +3533,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
+          <t>2014-08</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
           <t>2015-08</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>2015-12-03</t>
-        </is>
-      </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
+          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
@@ -3224,17 +3571,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
+          <t>2015-08</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
           <t>2015-12-03</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>2018-06-28</t>
-        </is>
-      </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>曾烨</t>
+          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
@@ -3262,17 +3609,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
+          <t>2015-08</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
           <t>2015-12-03</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>2018-06-28</t>
-        </is>
-      </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>刘云锋</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
@@ -3288,7 +3635,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3300,21 +3647,25 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
+          <t>2015-08</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
           <t>2015-12-03</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>2018-06-28</t>
-        </is>
-      </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>夏东</t>
+          <t>丰利财富（北京）国际资本管理股份有限公司</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
@@ -3326,7 +3677,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3338,17 +3689,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
+          <t>2015-08</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
           <t>2015-12-03</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>2018-06-28</t>
-        </is>
-      </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>刘云锋</t>
+          <t>昆山红土高新创业投资有限公司</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
@@ -3376,17 +3727,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
+          <t>2015-08</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
           <t>2015-12-03</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>2018-06-28</t>
-        </is>
-      </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
+          <t>曾烨</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
@@ -3414,17 +3765,17 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
+          <t>2015-08</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
           <t>2015-12-03</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>2018-06-28</t>
-        </is>
-      </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
+          <t>镇江红土创业投资有限公司</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
@@ -3440,7 +3791,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3452,17 +3803,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
+          <t>2015-08</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
           <t>2015-12-03</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>2018-06-28</t>
-        </is>
-      </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
@@ -3490,17 +3841,17 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
+          <t>2015-08</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
           <t>2015-12-03</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>2018-06-28</t>
-        </is>
-      </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>CASREV FUND</t>
+          <t>深圳市创新投资集团有限公司</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
@@ -3516,7 +3867,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3538,7 +3889,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>珠海拓域投资合伙企业（有限合伙）</t>
+          <t>刘云锋</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
@@ -3554,7 +3905,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3566,25 +3917,21 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
+          <t>2015-12-03</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
           <t>2018-06-28</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>2020-05-28</t>
-        </is>
-      </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
+          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>7412.0</t>
-        </is>
-      </c>
+      <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
@@ -3596,7 +3943,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3608,25 +3955,21 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
+          <t>2015-12-03</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
           <t>2018-06-28</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>2020-05-28</t>
-        </is>
-      </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>珠海拓域投资合伙企业（有限合伙）</t>
+          <t>曾烨</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
@@ -3650,25 +3993,21 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
+          <t>2015-12-03</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
           <t>2018-06-28</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>2020-05-28</t>
-        </is>
-      </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
+          <t>夏东</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>1584.0</t>
-        </is>
-      </c>
+      <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
@@ -3680,7 +4019,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3692,17 +4031,17 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
+          <t>2015-12-03</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
           <t>2018-06-28</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>2020-05-28</t>
-        </is>
-      </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>火炬电子科技股份有限公司</t>
+          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
@@ -3730,25 +4069,21 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
+          <t>2015-12-03</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
           <t>2018-06-28</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>2020-05-28</t>
-        </is>
-      </c>
       <c r="D62" t="inlineStr">
         <is>
           <t>CASREV FUND</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
+      <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
@@ -3760,7 +4095,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3772,25 +4107,21 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
+          <t>2015-12-03</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
           <t>2018-06-28</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>2020-05-28</t>
-        </is>
-      </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>夏东</t>
+          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>204.0</t>
-        </is>
-      </c>
+      <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr"/>
@@ -3802,7 +4133,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3814,25 +4145,21 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
+          <t>2015-12-03</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
           <t>2018-06-28</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>2020-05-28</t>
-        </is>
-      </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
+          <t>珠海拓域投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>3000.0</t>
-        </is>
-      </c>
+      <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
@@ -3844,7 +4171,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3856,17 +4183,17 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2020-05-28</t>
+          <t>2015-12-03</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2020-09-23</t>
+          <t>2018-06-28</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>中小企业发展基金（深圳有限合伙）</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
@@ -3882,7 +4209,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3894,25 +4221,21 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
+          <t>2018-06-28</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
           <t>2020-05-28</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>2020-09-23</t>
-        </is>
-      </c>
       <c r="D66" t="inlineStr">
         <is>
           <t>火炬电子科技股份有限公司</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>5000.0</t>
-        </is>
-      </c>
+      <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
@@ -3924,7 +4247,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3936,21 +4259,25 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
+          <t>2018-06-28</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
           <t>2020-05-28</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>2020-09-23</t>
-        </is>
-      </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>厦门西堤股权投资合伙企业（有限合伙）</t>
+          <t>CASREV FUND</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr"/>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>
@@ -3962,33 +4289,37 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>301581_黄山谷捷</t>
+          <t>301563_云汉芯城</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2012-06-12</t>
+          <t>2018-06-28</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2021-04-07</t>
+          <t>2020-05-28</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr"/>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>3000.0</t>
+        </is>
+      </c>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr"/>
@@ -4000,33 +4331,37 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>301581_黄山谷捷</t>
+          <t>301563_云汉芯城</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2012-06-12</t>
+          <t>2018-06-28</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2021-04-07</t>
+          <t>2020-05-28</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr"/>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>7412.0</t>
+        </is>
+      </c>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr"/>
@@ -4038,33 +4373,37 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>301581_黄山谷捷</t>
+          <t>301563_云汉芯城</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2012-06-12</t>
+          <t>2018-06-28</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2021-04-07</t>
+          <t>2020-05-28</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>张俊武</t>
+          <t>珠海拓域投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr"/>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
@@ -4076,35 +4415,35 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>301581_黄山谷捷</t>
+          <t>301563_云汉芯城</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2012-06-12</t>
+          <t>2018-06-28</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2021-04-07</t>
+          <t>2020-05-28</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>昆山谷捷金属制品有限公司</t>
+          <t>夏东</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
-          <t>1000.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="G71" t="inlineStr"/>
@@ -4125,26 +4464,30 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>301581_黄山谷捷</t>
+          <t>301563_云汉芯城</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2021-04-07</t>
+          <t>2018-06-28</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2021-04-13</t>
+          <t>2020-05-28</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>张俊武</t>
+          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
-      <c r="F72" t="inlineStr"/>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>1584.0</t>
+        </is>
+      </c>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr"/>
@@ -4154,31 +4497,39 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr"/>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>301581_黄山谷捷</t>
+          <t>301563_云汉芯城</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2021-04-07</t>
+          <t>2020-05-28</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2021-04-13</t>
+          <t>2020-09-23</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>火炬电子科技股份有限公司</t>
         </is>
       </c>
       <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr"/>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>5000.0</t>
+        </is>
+      </c>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr"/>
@@ -4188,27 +4539,31 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr"/>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>301581_黄山谷捷</t>
+          <t>301563_云汉芯城</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2021-04-07</t>
+          <t>2020-05-28</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2021-04-13</t>
+          <t>2020-09-23</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>厦门西堤股权投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
@@ -4222,27 +4577,31 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L74" t="inlineStr"/>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>301581_黄山谷捷</t>
+          <t>301563_云汉芯城</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2021-04-13</t>
+          <t>2020-05-28</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2021-11-11</t>
+          <t>2020-09-23</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>张俊武</t>
+          <t>中小企业发展基金（深圳有限合伙）</t>
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
@@ -4258,7 +4617,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -4270,12 +4629,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2021-04-13</t>
+          <t>2012-06-12</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2021-11-11</t>
+          <t>2021-04-07</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -4296,7 +4655,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -4308,17 +4667,17 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2021-04-13</t>
+          <t>2012-06-12</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2021-11-11</t>
+          <t>2021-04-07</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
+          <t>张俊武</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
@@ -4346,17 +4705,17 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2021-04-13</t>
+          <t>2012-06-12</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2021-11-11</t>
+          <t>2021-04-07</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>上海广弘实业有限公司</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
@@ -4384,21 +4743,25 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2021-04-13</t>
+          <t>2012-06-12</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2021-11-11</t>
+          <t>2021-04-07</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>昆山谷捷金属制品有限公司</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr"/>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr"/>
@@ -4422,25 +4785,21 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2021-11-11</t>
+          <t>2021-04-07</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2022-05-26</t>
+          <t>2021-04-13</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>1153.0</t>
-        </is>
-      </c>
+      <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr"/>
@@ -4450,11 +4809,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L80" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
+      <c r="L80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -4464,25 +4819,21 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2021-11-11</t>
+          <t>2021-04-07</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2022-05-26</t>
+          <t>2021-04-13</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>上海广弘实业有限公司</t>
+          <t>张俊武</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>10377.0</t>
-        </is>
-      </c>
+      <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr"/>
@@ -4492,11 +4843,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L81" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
+      <c r="L81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -4506,17 +4853,17 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2021-11-11</t>
+          <t>2021-04-07</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2022-05-26</t>
+          <t>2021-04-13</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>黄山佳捷股权管理中心（有限合伙）</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
@@ -4530,11 +4877,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
+      <c r="L82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -4544,17 +4887,17 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2022-05-26</t>
+          <t>2021-04-13</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2022-09-13</t>
+          <t>2021-11-11</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
@@ -4570,7 +4913,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -4582,12 +4925,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2022-05-26</t>
+          <t>2021-04-13</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2022-09-13</t>
+          <t>2021-11-11</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -4608,7 +4951,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -4620,12 +4963,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2022-05-26</t>
+          <t>2021-04-13</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2022-09-13</t>
+          <t>2021-11-11</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -4658,12 +5001,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2022-05-26</t>
+          <t>2021-04-13</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2022-09-13</t>
+          <t>2021-11-11</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -4696,25 +5039,21 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2022-05-26</t>
+          <t>2021-04-13</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2022-09-13</t>
+          <t>2021-11-11</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>黄山佳捷股权管理中心（有限合伙）</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E87" t="inlineStr"/>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2124.81</t>
-        </is>
-      </c>
+      <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr"/>
@@ -4724,7 +5063,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L87" t="inlineStr"/>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -4734,21 +5077,25 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
+          <t>2021-11-11</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
           <t>2022-05-26</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>2022-09-13</t>
-        </is>
-      </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr"/>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>1153.0</t>
+        </is>
+      </c>
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr"/>
@@ -4760,49 +5107,37 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr"/>
+          <t>301581_黄山谷捷</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2021-11-11</t>
+        </is>
+      </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>2022-05-26</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
+          <t>黄山佳捷股权管理中心（有限合伙）</t>
         </is>
       </c>
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr"/>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>840.0</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>6999.972</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>7000.0</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>-0.028</t>
-        </is>
-      </c>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4810,49 +5145,41 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>price×shares vs amount diff=0.0%</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr"/>
+          <t>301581_黄山谷捷</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2021-11-11</t>
+        </is>
+      </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>2022-05-26</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
+          <t>上海广弘实业有限公司</t>
         </is>
       </c>
       <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr"/>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>2999.988</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>3000.0</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>-0.012</t>
-        </is>
-      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>10377.0</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4860,49 +5187,37 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>price×shares vs amount diff=0.0%</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr"/>
+          <t>301581_黄山谷捷</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2022-05-26</t>
+        </is>
+      </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>2022-09-13</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>上海骁墨信息技术服务中心(有限合伙)</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr"/>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>1499.994</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>1500.0</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>-0.006</t>
-        </is>
-      </c>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4910,49 +5225,37 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>price×shares vs amount diff=0.0%</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr"/>
+          <t>301581_黄山谷捷</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2022-05-26</t>
+        </is>
+      </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2022-09-13</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>深圳市杉晖创业投资合伙企业(有限合伙)</t>
+          <t>张俊武</t>
         </is>
       </c>
       <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr"/>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>297.3333</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>10000.0027</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>10000.0</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>0.0027</t>
-        </is>
-      </c>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4960,49 +5263,37 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>price×shares vs amount diff=0.0%</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr"/>
+          <t>301581_黄山谷捷</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2022-05-26</t>
+        </is>
+      </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2022-09-13</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>上海联炻企业管理中心(有限合伙)</t>
+          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
         </is>
       </c>
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr"/>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>297.3333</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>10000.0027</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>10000.0</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>0.0027</t>
-        </is>
-      </c>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5010,99 +5301,75 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>price×shares vs amount diff=0.0%</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr"/>
+          <t>301581_黄山谷捷</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2022-05-26</t>
+        </is>
+      </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2022-09-13</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>安吉璞颉企业管理合伙企业(有限合伙)</t>
+          <t>黄山佳捷股权管理中心（有限合伙）</t>
         </is>
       </c>
       <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr"/>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>148.6667</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>5000.0031</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>5000.0</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>0.0031</t>
-        </is>
-      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2124.81</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="L94" t="inlineStr">
-        <is>
-          <t>price×shares vs amount diff=0.0%</t>
-        </is>
-      </c>
+      <c r="L94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr"/>
+          <t>301581_黄山谷捷</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>2022-05-26</t>
+        </is>
+      </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2022-09-13</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>江西赣江新区财投晨源股权投资中心(有限合伙)</t>
+          <t>上海广弘实业有限公司</t>
         </is>
       </c>
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr"/>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>89.2</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>3000.0012</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>3000.0</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>0.0012</t>
-        </is>
-      </c>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5110,49 +5377,37 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>price×shares vs amount diff=0.0%</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr"/>
+          <t>301581_黄山谷捷</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>2022-05-26</t>
+        </is>
+      </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2022-09-13</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>深圳市达晨创程私募股权投资基金企业(有限合伙)</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr"/>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>86.5984</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>2912.5034</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>2912.5</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>0.0034</t>
-        </is>
-      </c>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5160,7 +5415,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>price×shares vs amount diff=0.0%</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5173,34 +5428,34 @@
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>上海杉创智至创业投资合伙企业(有限合伙)</t>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr">
         <is>
-          <t>59.4667</t>
+          <t>840.0</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2000.0019</t>
+          <t>6999.972</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>2000.0</t>
+          <t>7000.0</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>0.0019</t>
+          <t>-0.028</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -5223,34 +5478,34 @@
       <c r="B98" t="inlineStr"/>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>杭州达晨创程股权投资基金合伙企业(有限合伙)</t>
+          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr">
         <is>
-          <t>51.959</t>
+          <t>360.0</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>1747.5007</t>
+          <t>2999.988</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>1747.5</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>0.0007</t>
+          <t>-0.012</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -5273,34 +5528,34 @@
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙)</t>
+          <t>上海骁墨信息技术服务中心(有限合伙)</t>
         </is>
       </c>
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>999.9993</t>
+          <t>1499.994</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>1000.0</t>
+          <t>1500.0</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>-0.0007</t>
+          <t>-0.006</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -5328,29 +5583,29 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>深圳市达晨财智创业投资管理有限公司</t>
+          <t>深圳市杉晖创业投资合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>999.9993</t>
+          <t>10000.0027</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>1000.0</t>
+          <t>10000.0</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>-0.0007</t>
+          <t>0.0027</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -5378,29 +5633,29 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>深圳市财智创赢私募股权投资企业(有限合伙)</t>
+          <t>上海联炻企业管理中心(有限合伙)</t>
         </is>
       </c>
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr">
         <is>
-          <t>10.1093</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>339.999</t>
+          <t>10000.0027</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>340.0</t>
+          <t>10000.0</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>-0.001</t>
+          <t>0.0027</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -5420,35 +5675,39 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>1992-12-04</t>
-        </is>
-      </c>
+      <c r="B102" t="inlineStr"/>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
+          <t>安吉璞颉企业管理合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr">
         <is>
-          <t>1020.0</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr"/>
+          <t>148.6667</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>5000.0031</t>
+        </is>
+      </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>1020.0</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr"/>
+          <t>5000.0</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>0.0031</t>
+        </is>
+      </c>
       <c r="K102" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5456,7 +5715,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
@@ -5466,35 +5725,39 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>1992-12-04</t>
-        </is>
-      </c>
+      <c r="B103" t="inlineStr"/>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
+          <t>江西赣江新区财投晨源股权投资中心(有限合伙)</t>
         </is>
       </c>
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr">
         <is>
-          <t>1800.0</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr"/>
+          <t>89.2</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>3000.0012</t>
+        </is>
+      </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>1800.0</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr"/>
+          <t>3000.0</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>0.0012</t>
+        </is>
+      </c>
       <c r="K103" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5502,7 +5765,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
@@ -5512,27 +5775,39 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>1992-12-04</t>
-        </is>
-      </c>
+      <c r="B104" t="inlineStr"/>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>友升太平洋(美国)投资有限公司</t>
+          <t>深圳市达晨创程私募股权投资基金企业(有限合伙)</t>
         </is>
       </c>
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr"/>
-      <c r="G104" t="inlineStr"/>
-      <c r="H104" t="inlineStr"/>
-      <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>86.5984</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>2912.5034</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>2912.5</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>0.0034</t>
+        </is>
+      </c>
       <c r="K104" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5540,7 +5815,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
@@ -5550,35 +5825,39 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>1992-12-04</t>
-        </is>
-      </c>
+      <c r="B105" t="inlineStr"/>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>上海泽升贸易有限公司</t>
+          <t>上海杉创智至创业投资合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr">
         <is>
-          <t>8976.0</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr"/>
+          <t>59.4667</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>2000.0019</t>
+        </is>
+      </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>8976.0</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr"/>
+          <t>2000.0</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>0.0019</t>
+        </is>
+      </c>
       <c r="K105" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5586,7 +5865,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
@@ -5596,27 +5875,39 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>1992-12-04</t>
-        </is>
-      </c>
+      <c r="B106" t="inlineStr"/>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>上海市青浦县徐泾乡工业公司</t>
+          <t>杭州达晨创程股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr"/>
-      <c r="G106" t="inlineStr"/>
-      <c r="H106" t="inlineStr"/>
-      <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>51.959</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>1747.5007</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>1747.5</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>0.0007</t>
+        </is>
+      </c>
       <c r="K106" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5624,7 +5915,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
@@ -5634,35 +5925,39 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>1992-12-04</t>
-        </is>
-      </c>
+      <c r="B107" t="inlineStr"/>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>罗世兵</t>
+          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr">
         <is>
-          <t>204.0</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr"/>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>999.9993</t>
+        </is>
+      </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>204.0</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr"/>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>-0.0007</t>
+        </is>
+      </c>
       <c r="K107" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5670,7 +5965,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
@@ -5680,39 +5975,39 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>2020-09-09</t>
-        </is>
-      </c>
+      <c r="B108" t="inlineStr"/>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>1020.0</t>
-        </is>
-      </c>
+          <t>深圳市达晨财智创业投资管理有限公司</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr">
         <is>
-          <t>1020.0</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2040.0</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
+          <t>999.9993</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>-0.0007</t>
+        </is>
+      </c>
       <c r="K108" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5720,7 +6015,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
@@ -5730,39 +6025,39 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>2020-09-09</t>
-        </is>
-      </c>
+      <c r="B109" t="inlineStr"/>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
+          <t>深圳市财智创赢私募股权投资企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>10.1093</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>3600.0</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
+          <t>339.999</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>340.0</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>-0.001</t>
+        </is>
+      </c>
       <c r="K109" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5770,7 +6065,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
@@ -5782,30 +6077,30 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
+          <t>1992-12-04</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
           <t>2020-09-09</t>
         </is>
       </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>2020-09-27</t>
-        </is>
-      </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
+          <t>上海泽升贸易有限公司</t>
         </is>
       </c>
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr">
         <is>
-          <t>840.0</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="H110" t="inlineStr"/>
       <c r="I110" t="inlineStr">
         <is>
-          <t>840.0</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="J110" t="inlineStr"/>
@@ -5828,36 +6123,32 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
+          <t>1992-12-04</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
           <t>2020-09-09</t>
         </is>
       </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>2020-09-27</t>
-        </is>
-      </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>上海泽升贸易有限公司</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>8976.0</t>
-        </is>
-      </c>
+          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr">
         <is>
-          <t>8976.0</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>17952.0</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr"/>
+          <t>1800.0</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr">
         <is>
@@ -5866,7 +6157,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5878,32 +6169,24 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
+          <t>1992-12-04</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
           <t>2020-09-09</t>
         </is>
       </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>2020-09-27</t>
-        </is>
-      </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>上海骁墨信息技术服务中心(有限合伙)</t>
+          <t>上海市青浦县徐泾乡工业公司</t>
         </is>
       </c>
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr"/>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
+      <c r="G112" t="inlineStr"/>
       <c r="H112" t="inlineStr"/>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
+      <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr">
         <is>
@@ -5912,7 +6195,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5924,36 +6207,32 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
+          <t>1992-12-04</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
           <t>2020-09-09</t>
         </is>
       </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>2020-09-27</t>
-        </is>
-      </c>
       <c r="D113" t="inlineStr">
         <is>
           <t>罗世兵</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>204.0</t>
-        </is>
-      </c>
+      <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr">
         <is>
           <t>204.0</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>408.0</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr"/>
+      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>204.0</t>
+        </is>
+      </c>
       <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr">
         <is>
@@ -5962,7 +6241,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5974,32 +6253,24 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
+          <t>1992-12-04</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
           <t>2020-09-09</t>
         </is>
       </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>2020-09-27</t>
-        </is>
-      </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
+          <t>友升太平洋(美国)投资有限公司</t>
         </is>
       </c>
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr"/>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
+      <c r="G114" t="inlineStr"/>
       <c r="H114" t="inlineStr"/>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
+      <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr">
         <is>
@@ -6008,7 +6279,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -6020,40 +6291,32 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>1992-12-04</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>840.0</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>7000.0</t>
-        </is>
-      </c>
+          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr"/>
+      <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr">
         <is>
-          <t>840.0</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>1680.0</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr"/>
+          <t>1020.0</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>1020.0</t>
+        </is>
+      </c>
       <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr">
         <is>
@@ -6062,7 +6325,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6074,32 +6337,36 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
+          <t>2020-09-09</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
           <t>2020-09-27</t>
         </is>
       </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>2022-12-19</t>
-        </is>
-      </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>江西赣江新区财投晨源股权投资中心(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr"/>
+          <t>上海泽升贸易有限公司</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>8976.0</t>
+        </is>
+      </c>
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr">
         <is>
-          <t>89.2</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr"/>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>89.2</t>
-        </is>
-      </c>
+          <t>8976.0</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>17952.0</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr">
         <is>
@@ -6108,7 +6375,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -6120,30 +6387,30 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
+          <t>2020-09-09</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
           <t>2020-09-27</t>
         </is>
       </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>2022-12-19</t>
-        </is>
-      </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>杭州达晨创程股权投资基金合伙企业(有限合伙)</t>
+          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr">
         <is>
-          <t>51.959</t>
+          <t>360.0</t>
         </is>
       </c>
       <c r="H117" t="inlineStr"/>
       <c r="I117" t="inlineStr">
         <is>
-          <t>51.959</t>
+          <t>360.0</t>
         </is>
       </c>
       <c r="J117" t="inlineStr"/>
@@ -6166,32 +6433,36 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
+          <t>2020-09-09</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
           <t>2020-09-27</t>
         </is>
       </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>2022-12-19</t>
-        </is>
-      </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>上海联炻企业管理中心(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr"/>
+          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr">
         <is>
-          <t>297.3333</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr"/>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>297.3333</t>
-        </is>
-      </c>
+          <t>1800.0</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>3600.0</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr">
         <is>
@@ -6200,7 +6471,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -6212,40 +6483,32 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
+          <t>2020-09-09</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
           <t>2020-09-27</t>
         </is>
       </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>2022-12-19</t>
-        </is>
-      </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>3000.0</t>
-        </is>
-      </c>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr"/>
+      <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr">
         <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>720.0</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr"/>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr">
         <is>
@@ -6254,7 +6517,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6266,32 +6529,36 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
+          <t>2020-09-09</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
           <t>2020-09-27</t>
         </is>
       </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>2022-12-19</t>
-        </is>
-      </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>深圳市达晨财智创业投资管理有限公司</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr"/>
+          <t>罗世兵</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>204.0</t>
+        </is>
+      </c>
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr">
         <is>
-          <t>29.7333</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr"/>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>29.7333</t>
-        </is>
-      </c>
+          <t>204.0</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>408.0</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr">
         <is>
@@ -6300,7 +6567,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -6312,30 +6579,30 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
+          <t>2020-09-09</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
           <t>2020-09-27</t>
         </is>
       </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>2022-12-19</t>
-        </is>
-      </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙)</t>
+          <t>上海骁墨信息技术服务中心(有限合伙)</t>
         </is>
       </c>
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="H121" t="inlineStr"/>
       <c r="I121" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="J121" t="inlineStr"/>
@@ -6358,37 +6625,33 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
+          <t>2020-09-09</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
           <t>2020-09-27</t>
         </is>
       </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>2022-12-19</t>
-        </is>
-      </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>上海骁墨信息技术服务中心(有限合伙)</t>
+          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>1500.0</t>
-        </is>
-      </c>
+          <t>1020.0</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr"/>
       <c r="G122" t="inlineStr">
         <is>
-          <t>180.0</t>
+          <t>1020.0</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>360.0</t>
+          <t>2040.0</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -6422,20 +6685,20 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>深圳市杉晖创业投资合伙企业(有限合伙)</t>
+          <t>江西赣江新区财投晨源股权投资中心(有限合伙)</t>
         </is>
       </c>
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="H123" t="inlineStr"/>
       <c r="I123" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="J123" t="inlineStr"/>
@@ -6468,20 +6731,20 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>深圳市达晨创程私募股权投资基金企业(有限合伙)</t>
+          <t>上海联炻企业管理中心(有限合伙)</t>
         </is>
       </c>
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr">
         <is>
-          <t>86.5984</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr">
         <is>
-          <t>86.5984</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="J124" t="inlineStr"/>
@@ -6514,20 +6777,20 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>上海杉创智至创业投资合伙企业(有限合伙)</t>
+          <t>深圳市达晨创程私募股权投资基金企业(有限合伙)</t>
         </is>
       </c>
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr"/>
       <c r="G125" t="inlineStr">
         <is>
-          <t>59.4667</t>
+          <t>86.5984</t>
         </is>
       </c>
       <c r="H125" t="inlineStr"/>
       <c r="I125" t="inlineStr">
         <is>
-          <t>59.4667</t>
+          <t>86.5984</t>
         </is>
       </c>
       <c r="J125" t="inlineStr"/>
@@ -6560,20 +6823,20 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>深圳市财智创赢私募股权投资企业(有限合伙)</t>
+          <t>深圳市达晨财智创业投资管理有限公司</t>
         </is>
       </c>
       <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr">
         <is>
-          <t>10.1093</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="H126" t="inlineStr"/>
       <c r="I126" t="inlineStr">
         <is>
-          <t>10.1093</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="J126" t="inlineStr"/>
@@ -6606,20 +6869,20 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>安吉璞颉企业管理合伙企业(有限合伙)</t>
+          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr"/>
       <c r="G127" t="inlineStr">
         <is>
-          <t>148.6667</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="H127" t="inlineStr"/>
       <c r="I127" t="inlineStr">
         <is>
-          <t>148.6667</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="J127" t="inlineStr"/>
@@ -6640,39 +6903,43 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B128" t="inlineStr"/>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>上海泽升贸易有限公司 (认缴→存量)</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr"/>
-      <c r="F128" t="inlineStr"/>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>7000.0</t>
+        </is>
+      </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>8976.0</t>
+          <t>840.0</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>8976.0</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>8976.0</t>
-        </is>
-      </c>
-      <c r="J128" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>1680.0</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -6680,7 +6947,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -6690,39 +6957,35 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B129" t="inlineStr"/>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
+          <t>杭州达晨创程股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr">
         <is>
-          <t>1800.0</t>
-        </is>
-      </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
+          <t>51.959</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr"/>
       <c r="I129" t="inlineStr">
         <is>
-          <t>1800.0</t>
-        </is>
-      </c>
-      <c r="J129" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>51.959</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr"/>
       <c r="K129" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -6730,7 +6993,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6740,39 +7003,35 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B130" t="inlineStr"/>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>共青城泽升投资管理合伙企业(有限合伙) (认缴→存量)</t>
+          <t>上海杉创智至创业投资合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr"/>
       <c r="G130" t="inlineStr">
         <is>
-          <t>1020.0</t>
-        </is>
-      </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>1020.0</t>
-        </is>
-      </c>
+          <t>59.4667</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr"/>
       <c r="I130" t="inlineStr">
         <is>
-          <t>1020.0</t>
-        </is>
-      </c>
-      <c r="J130" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>59.4667</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -6780,7 +7039,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6790,39 +7049,35 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B131" t="inlineStr"/>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>罗世兵 (认缴→存量)</t>
+          <t>深圳市财智创赢私募股权投资企业(有限合伙)</t>
         </is>
       </c>
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr"/>
       <c r="G131" t="inlineStr">
         <is>
-          <t>204.0</t>
-        </is>
-      </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>204.0</t>
-        </is>
-      </c>
+          <t>10.1093</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr"/>
       <c r="I131" t="inlineStr">
         <is>
-          <t>204.0</t>
-        </is>
-      </c>
-      <c r="J131" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>10.1093</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr"/>
       <c r="K131" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -6830,7 +7085,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6840,39 +7095,43 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B132" t="inlineStr"/>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr"/>
-      <c r="F132" t="inlineStr"/>
+          <t>上海骁墨信息技术服务中心(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>1500.0</t>
+        </is>
+      </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>840.0</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>840.0</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>840.0</t>
-        </is>
-      </c>
-      <c r="J132" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -6880,7 +7139,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -6890,39 +7149,35 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B133" t="inlineStr"/>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
+          <t>深圳市杉晖创业投资合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr"/>
       <c r="G133" t="inlineStr">
         <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
+          <t>297.3333</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr"/>
       <c r="I133" t="inlineStr">
         <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="J133" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>297.3333</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -6930,7 +7185,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6940,39 +7195,35 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B134" t="inlineStr"/>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>上海骁墨信息技术服务中心(有限合伙) (认缴→存量)</t>
+          <t>安吉璞颉企业管理合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr">
         <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
+          <t>148.6667</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr"/>
       <c r="I134" t="inlineStr">
         <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="J134" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>148.6667</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr"/>
       <c r="K134" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -6980,7 +7231,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6990,7 +7241,11 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B135" t="inlineStr"/>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
       <c r="C135" t="inlineStr">
         <is>
           <t>2022-12-19</t>
@@ -6998,31 +7253,31 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>深圳市杉晖创业投资合伙企业(有限合伙) (认缴→存量)</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr"/>
-      <c r="F135" t="inlineStr"/>
+          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>3000.0</t>
+        </is>
+      </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>360.0</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>297.3333</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>297.3333</t>
-        </is>
-      </c>
-      <c r="J135" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>720.0</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
+      <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -7030,7 +7285,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -7043,29 +7298,29 @@
       <c r="B136" t="inlineStr"/>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>上海联炻企业管理中心(有限合伙) (认缴→存量)</t>
+          <t>上海泽升贸易有限公司 (认缴→存量)</t>
         </is>
       </c>
       <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr"/>
       <c r="G136" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -7093,29 +7348,29 @@
       <c r="B137" t="inlineStr"/>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>安吉璞颉企业管理合伙企业(有限合伙) (认缴→存量)</t>
+          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr"/>
       <c r="G137" t="inlineStr">
         <is>
-          <t>148.6667</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>148.6667</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>148.6667</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -7143,29 +7398,29 @@
       <c r="B138" t="inlineStr"/>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>江西赣江新区财投晨源股权投资中心(有限合伙) (认缴→存量)</t>
+          <t>共青城泽升投资管理合伙企业(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr"/>
       <c r="G138" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>1020.0</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>1020.0</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>1020.0</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -7193,29 +7448,29 @@
       <c r="B139" t="inlineStr"/>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>深圳市达晨创程私募股权投资基金企业(有限合伙) (认缴→存量)</t>
+          <t>罗世兵 (认缴→存量)</t>
         </is>
       </c>
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr"/>
       <c r="G139" t="inlineStr">
         <is>
-          <t>86.5984</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>86.5984</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>86.5984</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -7243,29 +7498,29 @@
       <c r="B140" t="inlineStr"/>
       <c r="C140" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>上海杉创智至创业投资合伙企业(有限合伙) (认缴→存量)</t>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr"/>
       <c r="G140" t="inlineStr">
         <is>
-          <t>59.4667</t>
+          <t>840.0</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>59.4667</t>
+          <t>840.0</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>59.4667</t>
+          <t>840.0</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -7293,29 +7548,29 @@
       <c r="B141" t="inlineStr"/>
       <c r="C141" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>杭州达晨创程股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
+          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr"/>
       <c r="G141" t="inlineStr">
         <is>
-          <t>51.959</t>
+          <t>360.0</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>51.959</t>
+          <t>360.0</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>51.959</t>
+          <t>360.0</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -7343,29 +7598,29 @@
       <c r="B142" t="inlineStr"/>
       <c r="C142" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
+          <t>上海骁墨信息技术服务中心(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr"/>
       <c r="G142" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -7398,24 +7653,24 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>深圳市达晨财智创业投资管理有限公司 (认缴→存量)</t>
+          <t>深圳市杉晖创业投资合伙企业(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr"/>
       <c r="G143" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -7448,24 +7703,24 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>深圳市财智创赢私募股权投资企业(有限合伙) (认缴→存量)</t>
+          <t>上海联炻企业管理中心(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr"/>
       <c r="G144" t="inlineStr">
         <is>
-          <t>10.1093</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>10.1093</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>10.1093</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -7487,30 +7742,42 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>688758_赛分科技</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>2011-10</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr"/>
       <c r="C145" t="inlineStr">
         <is>
-          <t>2021-09-16</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>高新同华</t>
+          <t>安吉璞颉企业管理合伙企业(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr"/>
-      <c r="G145" t="inlineStr"/>
-      <c r="H145" t="inlineStr"/>
-      <c r="I145" t="inlineStr"/>
-      <c r="J145" t="inlineStr"/>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>148.6667</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>148.6667</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>148.6667</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K145" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -7518,37 +7785,49 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>认购数 vs 存量持股数</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>688758_赛分科技</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>2011-10</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr"/>
       <c r="C146" t="inlineStr">
         <is>
-          <t>2021-09-16</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>黄学英</t>
+          <t>江西赣江新区财投晨源股权投资中心(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr"/>
-      <c r="G146" t="inlineStr"/>
-      <c r="H146" t="inlineStr"/>
-      <c r="I146" t="inlineStr"/>
-      <c r="J146" t="inlineStr"/>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>89.2</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>89.2</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>89.2</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K146" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -7556,37 +7835,49 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>认购数 vs 存量持股数</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>688758_赛分科技</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>2011-10</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr"/>
       <c r="C147" t="inlineStr">
         <is>
-          <t>2021-09-16</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>周乃鼎</t>
+          <t>深圳市达晨创程私募股权投资基金企业(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr"/>
-      <c r="G147" t="inlineStr"/>
-      <c r="H147" t="inlineStr"/>
-      <c r="I147" t="inlineStr"/>
-      <c r="J147" t="inlineStr"/>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>86.5984</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>86.5984</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>86.5984</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K147" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -7594,71 +7885,99 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>认购数 vs 存量持股数</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>688758_赛分科技</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>2011-10</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr"/>
       <c r="C148" t="inlineStr">
         <is>
-          <t>2021-09-16</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>陆民</t>
+          <t>上海杉创智至创业投资合伙企业(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr"/>
-      <c r="G148" t="inlineStr"/>
-      <c r="H148" t="inlineStr"/>
-      <c r="I148" t="inlineStr"/>
-      <c r="J148" t="inlineStr"/>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>59.4667</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>59.4667</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>59.4667</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K148" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="L148" t="inlineStr"/>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>688758_赛分科技</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>2011-10</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr"/>
       <c r="C149" t="inlineStr">
         <is>
-          <t>2021-09-16</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>华泰大健康一号</t>
+          <t>杭州达晨创程股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr"/>
-      <c r="G149" t="inlineStr"/>
-      <c r="H149" t="inlineStr"/>
-      <c r="I149" t="inlineStr"/>
-      <c r="J149" t="inlineStr"/>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>51.959</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>51.959</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>51.959</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K149" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -7666,37 +7985,49 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>认购数 vs 存量持股数</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>688758_赛分科技</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>2011-10</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr"/>
       <c r="C150" t="inlineStr">
         <is>
-          <t>2021-09-16</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>复星惟盈</t>
+          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr"/>
-      <c r="G150" t="inlineStr"/>
-      <c r="H150" t="inlineStr"/>
-      <c r="I150" t="inlineStr"/>
-      <c r="J150" t="inlineStr"/>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K150" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -7704,37 +8035,49 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>认购数 vs 存量持股数</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>688758_赛分科技</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>2011-10</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr"/>
       <c r="C151" t="inlineStr">
         <is>
-          <t>2021-09-16</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>国寿疌泉</t>
+          <t>深圳市达晨财智创业投资管理有限公司 (认缴→存量)</t>
         </is>
       </c>
       <c r="E151" t="inlineStr"/>
       <c r="F151" t="inlineStr"/>
-      <c r="G151" t="inlineStr"/>
-      <c r="H151" t="inlineStr"/>
-      <c r="I151" t="inlineStr"/>
-      <c r="J151" t="inlineStr"/>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K151" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -7742,37 +8085,49 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>认购数 vs 存量持股数</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>688758_赛分科技</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>2011-10</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr"/>
       <c r="C152" t="inlineStr">
         <is>
-          <t>2021-09-16</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>史建伟</t>
+          <t>深圳市财智创赢私募股权投资企业(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr"/>
-      <c r="G152" t="inlineStr"/>
-      <c r="H152" t="inlineStr"/>
-      <c r="I152" t="inlineStr"/>
-      <c r="J152" t="inlineStr"/>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>10.1093</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>10.1093</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>10.1093</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K152" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -7780,7 +8135,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>认购数 vs 存量持股数</t>
         </is>
       </c>
     </row>
@@ -7802,7 +8157,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>黄学英/刘鸿雁</t>
+          <t>周乃鼎</t>
         </is>
       </c>
       <c r="E153" t="inlineStr"/>
@@ -7840,7 +8195,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>周金清</t>
+          <t>黄学英</t>
         </is>
       </c>
       <c r="E154" t="inlineStr"/>
@@ -7878,7 +8233,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Cheer Rise Consultants Limited</t>
+          <t>周金清</t>
         </is>
       </c>
       <c r="E155" t="inlineStr"/>
@@ -7894,7 +8249,7 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -7916,7 +8271,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>苏州贤达</t>
+          <t>国寿疌泉</t>
         </is>
       </c>
       <c r="E156" t="inlineStr"/>
@@ -7939,22 +8294,22 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
+          <t>688758_赛分科技</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2015-01</t>
+          <t>2011-10</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2021-09-16</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>陆民</t>
         </is>
       </c>
       <c r="E157" t="inlineStr"/>
@@ -7968,31 +8323,27 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L157" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
+      <c r="L157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
+          <t>688758_赛分科技</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2015-01</t>
+          <t>2011-10</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2021-09-16</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>QM101 Limited</t>
+          <t>Cheer Rise Consultants Limited</t>
         </is>
       </c>
       <c r="E158" t="inlineStr"/>
@@ -8015,22 +8366,22 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
+          <t>688758_赛分科技</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2015-01</t>
+          <t>2011-10</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2021-09-16</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>华金同达（深圳）投资合伙企业（有限合伙）</t>
+          <t>复星惟盈</t>
         </is>
       </c>
       <c r="E159" t="inlineStr"/>
@@ -8046,29 +8397,29 @@
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
+          <t>688758_赛分科技</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2015-01</t>
+          <t>2011-10</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2021-09-16</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>深圳市伊敦传媒投资基金合伙企业（有限合伙）</t>
+          <t>高新同华</t>
         </is>
       </c>
       <c r="E160" t="inlineStr"/>
@@ -8084,29 +8435,29 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
+          <t>688758_赛分科技</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2015-01</t>
+          <t>2011-10</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2021-09-16</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>苏州贤达</t>
         </is>
       </c>
       <c r="E161" t="inlineStr"/>
@@ -8122,29 +8473,29 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
+          <t>688758_赛分科技</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2015-01</t>
+          <t>2011-10</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2021-09-16</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>金石智娱股权投资（深圳）合伙企业（有限合伙）</t>
+          <t>黄学英/刘鸿雁</t>
         </is>
       </c>
       <c r="E162" t="inlineStr"/>
@@ -8167,22 +8518,22 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
+          <t>688758_赛分科技</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2015-01</t>
+          <t>2011-10</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2021-09-16</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>华泰大健康一号</t>
         </is>
       </c>
       <c r="E163" t="inlineStr"/>
@@ -8205,22 +8556,22 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
+          <t>688758_赛分科技</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2015-01</t>
+          <t>2011-10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2021-09-16</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>深圳中证投资有限责任公司</t>
+          <t>史建伟</t>
         </is>
       </c>
       <c r="E164" t="inlineStr"/>
@@ -8258,7 +8609,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>厦门富凯海创投资管理有限责任公司</t>
+          <t>深圳中证投资有限责任公司</t>
         </is>
       </c>
       <c r="E165" t="inlineStr"/>
@@ -8286,17 +8637,17 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
           <t>2015-07-09</t>
         </is>
       </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>2020-02-26</t>
-        </is>
-      </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>QM101 Limited</t>
         </is>
       </c>
       <c r="E166" t="inlineStr"/>
@@ -8312,7 +8663,7 @@
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -8324,17 +8675,17 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
           <t>2015-07-09</t>
         </is>
       </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>2020-02-26</t>
-        </is>
-      </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>QM101 Limited</t>
+          <t>深圳市伊敦传媒投资基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E167" t="inlineStr"/>
@@ -8350,7 +8701,7 @@
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -8362,25 +8713,21 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
           <t>2015-07-09</t>
         </is>
       </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>2020-02-26</t>
-        </is>
-      </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>香港迅雷有限公司</t>
         </is>
       </c>
       <c r="E168" t="inlineStr"/>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F168" t="inlineStr"/>
       <c r="G168" t="inlineStr"/>
       <c r="H168" t="inlineStr"/>
       <c r="I168" t="inlineStr"/>
@@ -8390,7 +8737,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L168" t="inlineStr"/>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -8400,17 +8751,17 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
           <t>2015-07-09</t>
         </is>
       </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>2020-02-26</t>
-        </is>
-      </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>华金同达（深圳）投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E169" t="inlineStr"/>
@@ -8426,7 +8777,7 @@
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -8438,17 +8789,17 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>2015-01</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>2023-03-24</t>
+          <t>2015-07-09</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>厦门富凯海创投资管理有限责任公司</t>
         </is>
       </c>
       <c r="E170" t="inlineStr"/>
@@ -8476,17 +8827,17 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>2015-01</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>2023-03-24</t>
+          <t>2015-07-09</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>QM101 Limited</t>
+          <t>北京岚锋创视网络科技有限公司</t>
         </is>
       </c>
       <c r="E171" t="inlineStr"/>
@@ -8502,7 +8853,7 @@
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -8514,17 +8865,17 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>2015-01</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>2023-03-24</t>
+          <t>2015-07-09</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>汇智同裕（深圳）投资合伙企业（有限合伙）</t>
+          <t>金石智娱股权投资（深圳）合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E172" t="inlineStr"/>
@@ -8540,7 +8891,7 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -8552,17 +8903,17 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>2015-01</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>2023-03-24</t>
+          <t>2015-07-09</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>EARN ACE LIMITED</t>
         </is>
       </c>
       <c r="E173" t="inlineStr"/>
@@ -8590,21 +8941,25 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
           <t>2020-02-26</t>
         </is>
       </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>2023-03-24</t>
-        </is>
-      </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>北京岚锋创视网络科技有限公司</t>
         </is>
       </c>
       <c r="E174" t="inlineStr"/>
-      <c r="F174" t="inlineStr"/>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G174" t="inlineStr"/>
       <c r="H174" t="inlineStr"/>
       <c r="I174" t="inlineStr"/>
@@ -8614,51 +8969,35 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L174" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
+      <c r="L174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>920100_三协电机</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr"/>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>2023-09-06</t>
+          <t>2020-02-26</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>盛祎等15名自然人</t>
+          <t>QM101 Limited</t>
         </is>
       </c>
       <c r="E175" t="inlineStr"/>
       <c r="F175" t="inlineStr"/>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>321.5</t>
-        </is>
-      </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>1739.315</t>
-        </is>
-      </c>
-      <c r="I175" t="inlineStr">
-        <is>
-          <t>1723.09</t>
-        </is>
-      </c>
-      <c r="J175" t="inlineStr">
-        <is>
-          <t>16.225</t>
-        </is>
-      </c>
+      <c r="G175" t="inlineStr"/>
+      <c r="H175" t="inlineStr"/>
+      <c r="I175" t="inlineStr"/>
+      <c r="J175" t="inlineStr"/>
       <c r="K175" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -8666,29 +9005,29 @@
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>price×shares vs amount diff=0.9%</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>920100_三协电机</t>
+          <t>688775_影石创新</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2002-11-07</t>
+          <t>2015-07-09</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>2022-08-09</t>
+          <t>2020-02-26</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>深圳市稳正景明创业投资企业(有限合伙)</t>
+          <t>EARN ACE LIMITED</t>
         </is>
       </c>
       <c r="E176" t="inlineStr"/>
@@ -8711,22 +9050,22 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>920100_三协电机</t>
+          <t>688775_影石创新</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2002-11-07</t>
+          <t>2015-07-09</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>2022-08-09</t>
+          <t>2020-02-26</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>盛祎</t>
+          <t>香港迅雷有限公司</t>
         </is>
       </c>
       <c r="E177" t="inlineStr"/>
@@ -8742,29 +9081,29 @@
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>920100_三协电机</t>
+          <t>688775_影石创新</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2002-11-07</t>
+          <t>2020-02-26</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>2022-08-09</t>
+          <t>2023-03-24</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>朱绶青</t>
+          <t>汇智同裕（深圳）投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E178" t="inlineStr"/>
@@ -8780,29 +9119,29 @@
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>688775_影石创新</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2016-12-14</t>
+          <t>2020-02-26</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2023-03-24</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>牛威</t>
+          <t>北京岚锋创视网络科技有限公司</t>
         </is>
       </c>
       <c r="E179" t="inlineStr"/>
@@ -8818,29 +9157,29 @@
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>688775_影石创新</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2016-12-14</t>
+          <t>2020-02-26</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2023-03-24</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>吴功友</t>
+          <t>QM101 Limited</t>
         </is>
       </c>
       <c r="E180" t="inlineStr"/>
@@ -8856,37 +9195,33 @@
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>688775_影石创新</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2016-12-14</t>
+          <t>2020-02-26</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2023-03-24</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>吴功友(王金林代持)</t>
+          <t>EARN ACE LIMITED</t>
         </is>
       </c>
       <c r="E181" t="inlineStr"/>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>400.0</t>
-        </is>
-      </c>
+      <c r="F181" t="inlineStr"/>
       <c r="G181" t="inlineStr"/>
       <c r="H181" t="inlineStr"/>
       <c r="I181" t="inlineStr"/>
@@ -8905,30 +9240,26 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>688775_影石创新</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2016-12-14</t>
+          <t>2020-02-26</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2023-03-24</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>四方股份</t>
+          <t>香港迅雷有限公司</t>
         </is>
       </c>
       <c r="E182" t="inlineStr"/>
-      <c r="F182" t="inlineStr">
-        <is>
-          <t>1200.0</t>
-        </is>
-      </c>
+      <c r="F182" t="inlineStr"/>
       <c r="G182" t="inlineStr"/>
       <c r="H182" t="inlineStr"/>
       <c r="I182" t="inlineStr"/>
@@ -8947,34 +9278,42 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>2016-12-14</t>
-        </is>
-      </c>
+          <t>920100_三协电机</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr"/>
       <c r="C183" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2023-09-06</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>牛威(罗永红代持)</t>
+          <t>盛祎等15名自然人</t>
         </is>
       </c>
       <c r="E183" t="inlineStr"/>
-      <c r="F183" t="inlineStr">
-        <is>
-          <t>400.0</t>
-        </is>
-      </c>
-      <c r="G183" t="inlineStr"/>
-      <c r="H183" t="inlineStr"/>
-      <c r="I183" t="inlineStr"/>
-      <c r="J183" t="inlineStr"/>
+      <c r="F183" t="inlineStr"/>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>321.5</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>1739.315</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>1723.09</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>16.225</t>
+        </is>
+      </c>
       <c r="K183" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -8982,44 +9321,36 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>price×shares vs amount diff=0.9%</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>920100_三协电机</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2002-11-07</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-08-09</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>幸福二期</t>
+          <t>朱绶青</t>
         </is>
       </c>
       <c r="E184" t="inlineStr"/>
       <c r="F184" t="inlineStr"/>
-      <c r="G184" t="inlineStr">
-        <is>
-          <t>300.0</t>
-        </is>
-      </c>
+      <c r="G184" t="inlineStr"/>
       <c r="H184" t="inlineStr"/>
-      <c r="I184" t="inlineStr">
-        <is>
-          <t>300.0</t>
-        </is>
-      </c>
+      <c r="I184" t="inlineStr"/>
       <c r="J184" t="inlineStr"/>
       <c r="K184" t="inlineStr">
         <is>
@@ -9028,37 +9359,33 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>920100_三协电机</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2002-11-07</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-08-09</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>牛威</t>
+          <t>盛祎</t>
         </is>
       </c>
       <c r="E185" t="inlineStr"/>
-      <c r="F185" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+      <c r="F185" t="inlineStr"/>
       <c r="G185" t="inlineStr"/>
       <c r="H185" t="inlineStr"/>
       <c r="I185" t="inlineStr"/>
@@ -9077,37 +9404,29 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>920100_三协电机</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2002-11-07</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-08-09</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>策星九天</t>
+          <t>深圳市稳正景明创业投资企业(有限合伙)</t>
         </is>
       </c>
       <c r="E186" t="inlineStr"/>
       <c r="F186" t="inlineStr"/>
-      <c r="G186" t="inlineStr">
-        <is>
-          <t>2345.0781</t>
-        </is>
-      </c>
+      <c r="G186" t="inlineStr"/>
       <c r="H186" t="inlineStr"/>
-      <c r="I186" t="inlineStr">
-        <is>
-          <t>2345.0781</t>
-        </is>
-      </c>
+      <c r="I186" t="inlineStr"/>
       <c r="J186" t="inlineStr"/>
       <c r="K186" t="inlineStr">
         <is>
@@ -9128,32 +9447,28 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
+          <t>2016-12-14</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
           <t>2017-10-25</t>
         </is>
       </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>2024-06-30</t>
-        </is>
-      </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>中科星图股份有限公司</t>
+          <t>四方股份</t>
         </is>
       </c>
       <c r="E187" t="inlineStr"/>
-      <c r="F187" t="inlineStr"/>
-      <c r="G187" t="inlineStr">
-        <is>
-          <t>3825.0</t>
-        </is>
-      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>1200.0</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr"/>
       <c r="H187" t="inlineStr"/>
-      <c r="I187" t="inlineStr">
-        <is>
-          <t>3825.0</t>
-        </is>
-      </c>
+      <c r="I187" t="inlineStr"/>
       <c r="J187" t="inlineStr"/>
       <c r="K187" t="inlineStr">
         <is>
@@ -9162,7 +9477,7 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -9174,23 +9489,23 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
+          <t>2016-12-14</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
           <t>2017-10-25</t>
         </is>
       </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>2024-06-30</t>
-        </is>
-      </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>吴功友</t>
+          <t>吴功友(王金林代持)</t>
         </is>
       </c>
       <c r="E188" t="inlineStr"/>
       <c r="F188" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>400.0</t>
         </is>
       </c>
       <c r="G188" t="inlineStr"/>
@@ -9216,32 +9531,24 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
+          <t>2016-12-14</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
           <t>2017-10-25</t>
         </is>
       </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>2024-06-30</t>
-        </is>
-      </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>策星揽月</t>
+          <t>牛威</t>
         </is>
       </c>
       <c r="E189" t="inlineStr"/>
       <c r="F189" t="inlineStr"/>
-      <c r="G189" t="inlineStr">
-        <is>
-          <t>412.5</t>
-        </is>
-      </c>
+      <c r="G189" t="inlineStr"/>
       <c r="H189" t="inlineStr"/>
-      <c r="I189" t="inlineStr">
-        <is>
-          <t>412.5</t>
-        </is>
-      </c>
+      <c r="I189" t="inlineStr"/>
       <c r="J189" t="inlineStr"/>
       <c r="K189" t="inlineStr">
         <is>
@@ -9262,32 +9569,24 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
+          <t>2016-12-14</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
           <t>2017-10-25</t>
         </is>
       </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>2024-06-30</t>
-        </is>
-      </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>幸福一期</t>
+          <t>吴功友</t>
         </is>
       </c>
       <c r="E190" t="inlineStr"/>
       <c r="F190" t="inlineStr"/>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>917.4219</t>
-        </is>
-      </c>
+      <c r="G190" t="inlineStr"/>
       <c r="H190" t="inlineStr"/>
-      <c r="I190" t="inlineStr">
-        <is>
-          <t>917.4219</t>
-        </is>
-      </c>
+      <c r="I190" t="inlineStr"/>
       <c r="J190" t="inlineStr"/>
       <c r="K190" t="inlineStr">
         <is>
@@ -9308,32 +9607,28 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
+          <t>2016-12-14</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
           <t>2017-10-25</t>
         </is>
       </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>2024-06-30</t>
-        </is>
-      </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>策星银河</t>
+          <t>牛威(罗永红代持)</t>
         </is>
       </c>
       <c r="E191" t="inlineStr"/>
-      <c r="F191" t="inlineStr"/>
-      <c r="G191" t="inlineStr">
-        <is>
-          <t>279.0</t>
-        </is>
-      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>400.0</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr"/>
       <c r="H191" t="inlineStr"/>
-      <c r="I191" t="inlineStr">
-        <is>
-          <t>279.0</t>
-        </is>
-      </c>
+      <c r="I191" t="inlineStr"/>
       <c r="J191" t="inlineStr"/>
       <c r="K191" t="inlineStr">
         <is>
@@ -9342,7 +9637,7 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -9364,22 +9659,18 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>策星逐日</t>
+          <t>牛威</t>
         </is>
       </c>
       <c r="E192" t="inlineStr"/>
-      <c r="F192" t="inlineStr"/>
-      <c r="G192" t="inlineStr">
-        <is>
-          <t>171.0</t>
-        </is>
-      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr"/>
       <c r="H192" t="inlineStr"/>
-      <c r="I192" t="inlineStr">
-        <is>
-          <t>171.0</t>
-        </is>
-      </c>
+      <c r="I192" t="inlineStr"/>
       <c r="J192" t="inlineStr"/>
       <c r="K192" t="inlineStr">
         <is>
@@ -9388,7 +9679,7 @@
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -9398,7 +9689,11 @@
           <t>920116_星图测控</t>
         </is>
       </c>
-      <c r="B193" t="inlineStr"/>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
       <c r="C193" t="inlineStr">
         <is>
           <t>2024-06-30</t>
@@ -9406,31 +9701,23 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>中科星图股份有限公司 (认缴→存量)</t>
+          <t>策星揽月</t>
         </is>
       </c>
       <c r="E193" t="inlineStr"/>
       <c r="F193" t="inlineStr"/>
       <c r="G193" t="inlineStr">
         <is>
-          <t>3825.0</t>
-        </is>
-      </c>
-      <c r="H193" t="inlineStr">
-        <is>
-          <t>3825.0</t>
-        </is>
-      </c>
+          <t>412.5</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr"/>
       <c r="I193" t="inlineStr">
         <is>
-          <t>3825.0</t>
-        </is>
-      </c>
-      <c r="J193" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>412.5</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr"/>
       <c r="K193" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -9438,7 +9725,7 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -9448,7 +9735,11 @@
           <t>920116_星图测控</t>
         </is>
       </c>
-      <c r="B194" t="inlineStr"/>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
       <c r="C194" t="inlineStr">
         <is>
           <t>2024-06-30</t>
@@ -9456,7 +9747,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>策星九天 (认缴→存量)</t>
+          <t>策星九天</t>
         </is>
       </c>
       <c r="E194" t="inlineStr"/>
@@ -9466,21 +9757,13 @@
           <t>2345.0781</t>
         </is>
       </c>
-      <c r="H194" t="inlineStr">
+      <c r="H194" t="inlineStr"/>
+      <c r="I194" t="inlineStr">
         <is>
           <t>2345.0781</t>
         </is>
       </c>
-      <c r="I194" t="inlineStr">
-        <is>
-          <t>2345.0781</t>
-        </is>
-      </c>
-      <c r="J194" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+      <c r="J194" t="inlineStr"/>
       <c r="K194" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -9488,7 +9771,7 @@
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -9498,7 +9781,11 @@
           <t>920116_星图测控</t>
         </is>
       </c>
-      <c r="B195" t="inlineStr"/>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
       <c r="C195" t="inlineStr">
         <is>
           <t>2024-06-30</t>
@@ -9506,31 +9793,23 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>幸福一期 (认缴→存量)</t>
+          <t>幸福二期</t>
         </is>
       </c>
       <c r="E195" t="inlineStr"/>
       <c r="F195" t="inlineStr"/>
       <c r="G195" t="inlineStr">
         <is>
-          <t>917.4219</t>
-        </is>
-      </c>
-      <c r="H195" t="inlineStr">
-        <is>
-          <t>917.4219</t>
-        </is>
-      </c>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr"/>
       <c r="I195" t="inlineStr">
         <is>
-          <t>917.4219</t>
-        </is>
-      </c>
-      <c r="J195" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr"/>
       <c r="K195" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -9538,7 +9817,7 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -9548,7 +9827,11 @@
           <t>920116_星图测控</t>
         </is>
       </c>
-      <c r="B196" t="inlineStr"/>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
       <c r="C196" t="inlineStr">
         <is>
           <t>2024-06-30</t>
@@ -9556,31 +9839,23 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>策星揽月 (认缴→存量)</t>
+          <t>幸福一期</t>
         </is>
       </c>
       <c r="E196" t="inlineStr"/>
       <c r="F196" t="inlineStr"/>
       <c r="G196" t="inlineStr">
         <is>
-          <t>412.5</t>
-        </is>
-      </c>
-      <c r="H196" t="inlineStr">
-        <is>
-          <t>412.5</t>
-        </is>
-      </c>
+          <t>917.4219</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr"/>
       <c r="I196" t="inlineStr">
         <is>
-          <t>412.5</t>
-        </is>
-      </c>
-      <c r="J196" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>917.4219</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr"/>
       <c r="K196" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -9588,7 +9863,7 @@
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -9598,7 +9873,11 @@
           <t>920116_星图测控</t>
         </is>
       </c>
-      <c r="B197" t="inlineStr"/>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
       <c r="C197" t="inlineStr">
         <is>
           <t>2024-06-30</t>
@@ -9606,31 +9885,23 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>幸福二期 (认缴→存量)</t>
+          <t>中科星图股份有限公司</t>
         </is>
       </c>
       <c r="E197" t="inlineStr"/>
       <c r="F197" t="inlineStr"/>
       <c r="G197" t="inlineStr">
         <is>
-          <t>300.0</t>
-        </is>
-      </c>
-      <c r="H197" t="inlineStr">
-        <is>
-          <t>300.0</t>
-        </is>
-      </c>
+          <t>3825.0</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr"/>
       <c r="I197" t="inlineStr">
         <is>
-          <t>300.0</t>
-        </is>
-      </c>
-      <c r="J197" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>3825.0</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr"/>
       <c r="K197" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -9638,7 +9909,7 @@
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -9648,7 +9919,11 @@
           <t>920116_星图测控</t>
         </is>
       </c>
-      <c r="B198" t="inlineStr"/>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
       <c r="C198" t="inlineStr">
         <is>
           <t>2024-06-30</t>
@@ -9656,31 +9931,23 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>策星银河 (认缴→存量)</t>
+          <t>策星逐日</t>
         </is>
       </c>
       <c r="E198" t="inlineStr"/>
       <c r="F198" t="inlineStr"/>
       <c r="G198" t="inlineStr">
         <is>
-          <t>279.0</t>
-        </is>
-      </c>
-      <c r="H198" t="inlineStr">
-        <is>
-          <t>279.0</t>
-        </is>
-      </c>
+          <t>171.0</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr"/>
       <c r="I198" t="inlineStr">
         <is>
-          <t>279.0</t>
-        </is>
-      </c>
-      <c r="J198" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>171.0</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr"/>
       <c r="K198" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -9688,7 +9955,7 @@
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -9698,7 +9965,11 @@
           <t>920116_星图测控</t>
         </is>
       </c>
-      <c r="B199" t="inlineStr"/>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
       <c r="C199" t="inlineStr">
         <is>
           <t>2024-06-30</t>
@@ -9706,31 +9977,19 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>策星逐日 (认缴→存量)</t>
+          <t>吴功友</t>
         </is>
       </c>
       <c r="E199" t="inlineStr"/>
-      <c r="F199" t="inlineStr"/>
-      <c r="G199" t="inlineStr">
-        <is>
-          <t>171.0</t>
-        </is>
-      </c>
-      <c r="H199" t="inlineStr">
-        <is>
-          <t>171.0</t>
-        </is>
-      </c>
-      <c r="I199" t="inlineStr">
-        <is>
-          <t>171.0</t>
-        </is>
-      </c>
-      <c r="J199" t="inlineStr">
+      <c r="F199" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
+      <c r="G199" t="inlineStr"/>
+      <c r="H199" t="inlineStr"/>
+      <c r="I199" t="inlineStr"/>
+      <c r="J199" t="inlineStr"/>
       <c r="K199" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -9738,35 +9997,431 @@
       </c>
       <c r="L199" t="inlineStr">
         <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>策星银河</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr"/>
+      <c r="F200" t="inlineStr"/>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr"/>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr"/>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>中科星图股份有限公司 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr"/>
+      <c r="F201" t="inlineStr"/>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>3825.0</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>3825.0</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>3825.0</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
           <t>认购数 vs 存量持股数</t>
         </is>
       </c>
     </row>
-    <row r="201">
-      <c r="A201" s="3" t="inlineStr">
-        <is>
-          <t>认缴流量: 19 条</t>
-        </is>
-      </c>
-    </row>
     <row r="202">
-      <c r="A202" s="3" t="inlineStr">
-        <is>
-          <t>股权存量: 19 条</t>
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr"/>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>策星九天 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr"/>
+      <c r="F202" t="inlineStr"/>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>2345.0781</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>2345.0781</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>2345.0781</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>生成时间: 2026-06-12T14:44:15.828372</t>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr"/>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>幸福一期 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr"/>
+      <c r="F203" t="inlineStr"/>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>917.4219</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>917.4219</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>917.4219</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr"/>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>策星揽月 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr"/>
+      <c r="F204" t="inlineStr"/>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>412.5</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>412.5</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>412.5</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr"/>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>幸福二期 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr"/>
+      <c r="F205" t="inlineStr"/>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr"/>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>策星银河 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr"/>
+      <c r="F206" t="inlineStr"/>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr"/>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>策星逐日 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr"/>
+      <c r="F207" t="inlineStr"/>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>171.0</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>171.0</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>171.0</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="3" t="inlineStr">
+        <is>
+          <t>认缴流量: 19 条</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="3" t="inlineStr">
+        <is>
+          <t>股权存量: 19 条</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>生成时间: 2026-06-12T15:16:11.014744</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A22:L22"/>
+    <mergeCell ref="A30:L30"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/week2_excel/603418_友升股份_三表抽取.xlsx
+++ b/outputs/week2_excel/603418_友升股份_三表抽取.xlsx
@@ -2999,7 +2999,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>孙国敏</t>
+          <t>张松满</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
@@ -3017,11 +3017,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
+      <c r="L34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3041,7 +3037,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>张松满</t>
+          <t>孙国敏</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
@@ -3059,7 +3055,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3079,11 +3079,15 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
+          <t>深圳市云汉电子有限公司</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>25.0</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
@@ -3095,7 +3099,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3117,15 +3121,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>刘云锋</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>25.0</t>
-        </is>
-      </c>
+      <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
@@ -3137,7 +3137,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3197,7 +3197,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
@@ -3235,7 +3235,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>深圳市云汉电子有限公司</t>
+          <t>刘云锋</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
@@ -3277,7 +3277,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>丰利财富（北京）国际资本管理股份有限公司</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
@@ -3293,7 +3293,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3315,7 +3315,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
+          <t>东方富海（上海）创业投资企业（有限合伙）</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
@@ -3331,7 +3331,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3353,7 +3353,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>镇江红土创业投资有限公司</t>
+          <t>深圳市创新投资集团有限公司</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
@@ -3391,7 +3391,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
+          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
@@ -3407,7 +3407,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3429,7 +3429,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>东方富海（上海）创业投资企业（有限合伙）</t>
+          <t>丰利财富（北京）国际资本管理股份有限公司</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
@@ -3445,7 +3445,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3505,7 +3505,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
@@ -3543,7 +3543,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>深圳市创新投资集团有限公司</t>
+          <t>镇江红土创业投资有限公司</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
@@ -3581,15 +3581,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>丰利财富（北京）国际资本管理股份有限公司</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
@@ -3601,7 +3597,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3623,7 +3619,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>刘云锋</t>
+          <t>深圳市创新投资集团有限公司</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
@@ -3639,7 +3635,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3661,7 +3657,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>昆山红土高新创业投资有限公司</t>
+          <t>刘云锋</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
@@ -3677,7 +3673,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3699,7 +3695,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>镇江红土创业投资有限公司</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
@@ -3715,7 +3711,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3737,7 +3733,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>曾烨</t>
+          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
@@ -3753,7 +3749,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3775,11 +3771,15 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
+          <t>丰利财富（北京）国际资本管理股份有限公司</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
@@ -3813,7 +3813,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>深圳市创新投资集团有限公司</t>
+          <t>曾烨</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
@@ -3829,7 +3829,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3851,7 +3851,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>镇江红土创业投资有限公司</t>
+          <t>昆山红土高新创业投资有限公司</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
@@ -3889,7 +3889,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>曾烨</t>
+          <t>珠海拓域投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3927,7 +3927,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>珠海拓域投资合伙企业（有限合伙）</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -4003,7 +4003,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
+          <t>夏东</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
@@ -4041,7 +4041,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>刘云锋</t>
+          <t>CASREV FUND</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
@@ -4057,7 +4057,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -4079,7 +4079,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>CASREV FUND</t>
+          <t>刘云锋</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
@@ -4095,7 +4095,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -4117,7 +4117,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>夏东</t>
+          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
@@ -4155,7 +4155,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
@@ -4171,7 +4171,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
+          <t>曾烨</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
@@ -4209,7 +4209,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -4231,13 +4231,13 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>CASREV FUND</t>
+          <t>珠海拓域投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>1000.0</t>
         </is>
       </c>
       <c r="G66" t="inlineStr"/>
@@ -4273,13 +4273,13 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
+          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
-          <t>7412.0</t>
+          <t>1584.0</t>
         </is>
       </c>
       <c r="G67" t="inlineStr"/>
@@ -4315,13 +4315,13 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>夏东</t>
+          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="G68" t="inlineStr"/>
@@ -4357,13 +4357,13 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
+          <t>夏东</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="G69" t="inlineStr"/>
@@ -4399,13 +4399,13 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>珠海拓域投资合伙企业（有限合伙）</t>
+          <t>CASREV FUND</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
-          <t>1000.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="G70" t="inlineStr"/>
@@ -4479,13 +4479,13 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
+          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
-          <t>1584.0</t>
+          <t>7412.0</t>
         </is>
       </c>
       <c r="G72" t="inlineStr"/>
@@ -4559,15 +4559,11 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>火炬电子科技股份有限公司</t>
+          <t>中小企业发展基金（深圳有限合伙）</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>5000.0</t>
-        </is>
-      </c>
+      <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr"/>
@@ -4579,7 +4575,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -4601,11 +4597,15 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>中小企业发展基金（深圳有限合伙）</t>
+          <t>火炬电子科技股份有限公司</t>
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
-      <c r="F75" t="inlineStr"/>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>5000.0</t>
+        </is>
+      </c>
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr"/>
@@ -4617,7 +4617,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -4677,15 +4677,11 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>昆山谷捷金属制品有限公司</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr"/>
@@ -4697,7 +4693,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -4719,11 +4715,15 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>昆山谷捷金属制品有限公司</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
-      <c r="F78" t="inlineStr"/>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr"/>
@@ -4735,7 +4735,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -4935,7 +4935,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
@@ -4951,7 +4951,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -4973,7 +4973,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>上海广弘实业有限公司</t>
         </is>
       </c>
       <c r="E85" t="inlineStr"/>
@@ -4989,7 +4989,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5011,7 +5011,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>上海广弘实业有限公司</t>
+          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
@@ -5087,15 +5087,11 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
+          <t>黄山佳捷股权管理中心（有限合伙）</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>1153.0</t>
-        </is>
-      </c>
+      <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr"/>
@@ -5107,7 +5103,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5171,11 +5167,15 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>黄山佳捷股权管理中心（有限合伙）</t>
+          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
         </is>
       </c>
       <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr"/>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>1153.0</t>
+        </is>
+      </c>
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr"/>
@@ -5187,7 +5187,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5247,11 +5247,15 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
+          <t>黄山佳捷股权管理中心（有限合伙）</t>
         </is>
       </c>
       <c r="E92" t="inlineStr"/>
-      <c r="F92" t="inlineStr"/>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2124.81</t>
+        </is>
+      </c>
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr"/>
@@ -5261,11 +5265,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L92" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
+      <c r="L92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -5361,15 +5361,11 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>黄山佳捷股权管理中心（有限合伙）</t>
+          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
         </is>
       </c>
       <c r="E95" t="inlineStr"/>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2124.81</t>
-        </is>
-      </c>
+      <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr"/>
@@ -5379,7 +5375,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L95" t="inlineStr"/>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -6087,14 +6087,22 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>友升太平洋(美国)投资有限公司</t>
+          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr"/>
-      <c r="G110" t="inlineStr"/>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>1020.0</t>
+        </is>
+      </c>
       <c r="H110" t="inlineStr"/>
-      <c r="I110" t="inlineStr"/>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>1020.0</t>
+        </is>
+      </c>
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr">
         <is>
@@ -6103,7 +6111,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6125,20 +6133,20 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>罗世兵</t>
+          <t>上海泽升贸易有限公司</t>
         </is>
       </c>
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="H111" t="inlineStr"/>
       <c r="I111" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="J111" t="inlineStr"/>
@@ -6171,22 +6179,14 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
+          <t>友升太平洋(美国)投资有限公司</t>
         </is>
       </c>
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr"/>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
+      <c r="G112" t="inlineStr"/>
       <c r="H112" t="inlineStr"/>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
+      <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr">
         <is>
@@ -6195,7 +6195,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -6217,22 +6217,14 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>上海泽升贸易有限公司</t>
+          <t>上海市青浦县徐泾乡工业公司</t>
         </is>
       </c>
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr"/>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>8976.0</t>
-        </is>
-      </c>
+      <c r="G113" t="inlineStr"/>
       <c r="H113" t="inlineStr"/>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>8976.0</t>
-        </is>
-      </c>
+      <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr">
         <is>
@@ -6241,7 +6233,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -6263,20 +6255,20 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
+          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr">
         <is>
-          <t>1020.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="H114" t="inlineStr"/>
       <c r="I114" t="inlineStr">
         <is>
-          <t>1020.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="J114" t="inlineStr"/>
@@ -6309,14 +6301,22 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>上海市青浦县徐泾乡工业公司</t>
+          <t>罗世兵</t>
         </is>
       </c>
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr"/>
-      <c r="G115" t="inlineStr"/>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>204.0</t>
+        </is>
+      </c>
       <c r="H115" t="inlineStr"/>
-      <c r="I115" t="inlineStr"/>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>204.0</t>
+        </is>
+      </c>
       <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr">
         <is>
@@ -6325,7 +6325,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6347,22 +6347,26 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr"/>
+          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>1020.0</t>
+        </is>
+      </c>
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr">
         <is>
-          <t>840.0</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr"/>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>840.0</t>
-        </is>
-      </c>
+          <t>1020.0</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>2040.0</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr">
         <is>
@@ -6371,7 +6375,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -6393,23 +6397,23 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>罗世兵</t>
+          <t>上海泽升贸易有限公司</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>408.0</t>
+          <t>17952.0</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -6443,26 +6447,22 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr">
         <is>
-          <t>1800.0</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>3600.0</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr"/>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
       <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr">
         <is>
@@ -6471,7 +6471,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6493,26 +6493,22 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>上海泽升贸易有限公司</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>8976.0</t>
-        </is>
-      </c>
+          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr">
         <is>
-          <t>8976.0</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>17952.0</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr"/>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr">
         <is>
@@ -6521,7 +6517,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6543,22 +6539,26 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>上海骁墨信息技术服务中心(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr"/>
+          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr">
         <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr"/>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
+          <t>1800.0</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>3600.0</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -6589,26 +6589,22 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>1020.0</t>
-        </is>
-      </c>
+          <t>上海骁墨信息技术服务中心(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr">
         <is>
-          <t>1020.0</t>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>2040.0</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr"/>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr">
         <is>
@@ -6617,7 +6613,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6639,22 +6635,26 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr"/>
+          <t>罗世兵</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>204.0</t>
+        </is>
+      </c>
       <c r="F122" t="inlineStr"/>
       <c r="G122" t="inlineStr">
         <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="H122" t="inlineStr"/>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
+          <t>204.0</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>408.0</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
       <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr">
         <is>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -6685,30 +6685,22 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>840.0</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>7000.0</t>
-        </is>
-      </c>
+          <t>上海杉创智至创业投资合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr"/>
+      <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr">
         <is>
-          <t>840.0</t>
-        </is>
-      </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>1680.0</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr"/>
+          <t>59.4667</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>59.4667</t>
+        </is>
+      </c>
       <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr">
         <is>
@@ -6717,7 +6709,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6885,22 +6877,30 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>深圳市财智创赢私募股权投资企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr"/>
-      <c r="F127" t="inlineStr"/>
+          <t>上海骁墨信息技术服务中心(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>1500.0</t>
+        </is>
+      </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>10.1093</t>
-        </is>
-      </c>
-      <c r="H127" t="inlineStr"/>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>10.1093</t>
-        </is>
-      </c>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
       <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr">
         <is>
@@ -6909,7 +6909,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -6931,30 +6931,22 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>上海骁墨信息技术服务中心(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>1500.0</t>
-        </is>
-      </c>
+          <t>深圳市杉晖创业投资合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr"/>
+      <c r="F128" t="inlineStr"/>
       <c r="G128" t="inlineStr">
         <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr"/>
+          <t>297.3333</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr"/>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>297.3333</t>
+        </is>
+      </c>
       <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr">
         <is>
@@ -6963,7 +6955,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6985,20 +6977,20 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>深圳市杉晖创业投资合伙企业(有限合伙)</t>
+          <t>深圳市财智创赢私募股权投资企业(有限合伙)</t>
         </is>
       </c>
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>10.1093</t>
         </is>
       </c>
       <c r="H129" t="inlineStr"/>
       <c r="I129" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>10.1093</t>
         </is>
       </c>
       <c r="J129" t="inlineStr"/>
@@ -7031,20 +7023,20 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>江西赣江新区财投晨源股权投资中心(有限合伙)</t>
+          <t>杭州达晨创程股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr"/>
       <c r="G130" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>51.959</t>
         </is>
       </c>
       <c r="H130" t="inlineStr"/>
       <c r="I130" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>51.959</t>
         </is>
       </c>
       <c r="J130" t="inlineStr"/>
@@ -7077,20 +7069,20 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>上海联炻企业管理中心(有限合伙)</t>
+          <t>江西赣江新区财投晨源股权投资中心(有限合伙)</t>
         </is>
       </c>
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr"/>
       <c r="G131" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="H131" t="inlineStr"/>
       <c r="I131" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="J131" t="inlineStr"/>
@@ -7123,20 +7115,20 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>上海杉创智至创业投资合伙企业(有限合伙)</t>
+          <t>安吉璞颉企业管理合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr"/>
       <c r="G132" t="inlineStr">
         <is>
-          <t>59.4667</t>
+          <t>148.6667</t>
         </is>
       </c>
       <c r="H132" t="inlineStr"/>
       <c r="I132" t="inlineStr">
         <is>
-          <t>59.4667</t>
+          <t>148.6667</t>
         </is>
       </c>
       <c r="J132" t="inlineStr"/>
@@ -7169,22 +7161,30 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr"/>
-      <c r="F133" t="inlineStr"/>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>7000.0</t>
+        </is>
+      </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>29.7333</t>
-        </is>
-      </c>
-      <c r="H133" t="inlineStr"/>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>29.7333</t>
-        </is>
-      </c>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>1680.0</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
       <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr">
         <is>
@@ -7193,7 +7193,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -7215,20 +7215,20 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>安吉璞颉企业管理合伙企业(有限合伙)</t>
+          <t>上海联炻企业管理中心(有限合伙)</t>
         </is>
       </c>
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr">
         <is>
-          <t>148.6667</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="H134" t="inlineStr"/>
       <c r="I134" t="inlineStr">
         <is>
-          <t>148.6667</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="J134" t="inlineStr"/>
@@ -7261,20 +7261,20 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>杭州达晨创程股权投资基金合伙企业(有限合伙)</t>
+          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr"/>
       <c r="G135" t="inlineStr">
         <is>
-          <t>51.959</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="H135" t="inlineStr"/>
       <c r="I135" t="inlineStr">
         <is>
-          <t>51.959</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="J135" t="inlineStr"/>
@@ -8157,7 +8157,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>黄学英</t>
+          <t>高新同华</t>
         </is>
       </c>
       <c r="E153" t="inlineStr"/>
@@ -8195,7 +8195,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>华泰大健康一号</t>
+          <t>周乃鼎</t>
         </is>
       </c>
       <c r="E154" t="inlineStr"/>
@@ -8211,7 +8211,7 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -8233,7 +8233,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>复星惟盈</t>
+          <t>Cheer Rise Consultants Limited</t>
         </is>
       </c>
       <c r="E155" t="inlineStr"/>
@@ -8249,7 +8249,7 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -8305,7 +8305,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>黄学英/刘鸿雁</t>
+          <t>黄学英</t>
         </is>
       </c>
       <c r="E157" t="inlineStr"/>
@@ -8321,7 +8321,7 @@
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -8343,7 +8343,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>周乃鼎</t>
+          <t>周金清</t>
         </is>
       </c>
       <c r="E158" t="inlineStr"/>
@@ -8359,7 +8359,7 @@
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -8381,7 +8381,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>国寿疌泉</t>
+          <t>苏州贤达</t>
         </is>
       </c>
       <c r="E159" t="inlineStr"/>
@@ -8419,7 +8419,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>史建伟</t>
+          <t>国寿疌泉</t>
         </is>
       </c>
       <c r="E160" t="inlineStr"/>
@@ -8435,7 +8435,7 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -8457,7 +8457,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>高新同华</t>
+          <t>黄学英/刘鸿雁</t>
         </is>
       </c>
       <c r="E161" t="inlineStr"/>
@@ -8473,7 +8473,7 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -8495,7 +8495,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Cheer Rise Consultants Limited</t>
+          <t>复星惟盈</t>
         </is>
       </c>
       <c r="E162" t="inlineStr"/>
@@ -8511,7 +8511,7 @@
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -8533,7 +8533,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>周金清</t>
+          <t>史建伟</t>
         </is>
       </c>
       <c r="E163" t="inlineStr"/>
@@ -8549,7 +8549,7 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -8571,7 +8571,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>苏州贤达</t>
+          <t>华泰大健康一号</t>
         </is>
       </c>
       <c r="E164" t="inlineStr"/>
@@ -8609,7 +8609,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>深圳中证投资有限责任公司</t>
         </is>
       </c>
       <c r="E165" t="inlineStr"/>
@@ -8647,7 +8647,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>QM101 Limited</t>
+          <t>金石智娱股权投资（深圳）合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E166" t="inlineStr"/>
@@ -8685,7 +8685,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>厦门富凯海创投资管理有限责任公司</t>
+          <t>北京岚锋创视网络科技有限公司</t>
         </is>
       </c>
       <c r="E167" t="inlineStr"/>
@@ -8701,7 +8701,7 @@
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -8723,7 +8723,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>香港迅雷有限公司</t>
         </is>
       </c>
       <c r="E168" t="inlineStr"/>
@@ -8739,7 +8739,7 @@
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -8761,7 +8761,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>华金同达（深圳）投资合伙企业（有限合伙）</t>
+          <t>厦门富凯海创投资管理有限责任公司</t>
         </is>
       </c>
       <c r="E169" t="inlineStr"/>
@@ -8799,7 +8799,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>金石智娱股权投资（深圳）合伙企业（有限合伙）</t>
+          <t>华金同达（深圳）投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E170" t="inlineStr"/>
@@ -8837,7 +8837,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>深圳中证投资有限责任公司</t>
+          <t>QM101 Limited</t>
         </is>
       </c>
       <c r="E171" t="inlineStr"/>
@@ -8913,7 +8913,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>EARN ACE LIMITED</t>
         </is>
       </c>
       <c r="E173" t="inlineStr"/>
@@ -8951,7 +8951,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>香港迅雷有限公司</t>
         </is>
       </c>
       <c r="E174" t="inlineStr"/>
@@ -8989,11 +8989,15 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>QM101 Limited</t>
+          <t>北京岚锋创视网络科技有限公司</t>
         </is>
       </c>
       <c r="E175" t="inlineStr"/>
-      <c r="F175" t="inlineStr"/>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G175" t="inlineStr"/>
       <c r="H175" t="inlineStr"/>
       <c r="I175" t="inlineStr"/>
@@ -9003,11 +9007,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L175" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
+      <c r="L175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -9027,15 +9027,11 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>QM101 Limited</t>
         </is>
       </c>
       <c r="E176" t="inlineStr"/>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F176" t="inlineStr"/>
       <c r="G176" t="inlineStr"/>
       <c r="H176" t="inlineStr"/>
       <c r="I176" t="inlineStr"/>
@@ -9045,7 +9041,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L176" t="inlineStr"/>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -9065,7 +9065,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>EARN ACE LIMITED</t>
         </is>
       </c>
       <c r="E177" t="inlineStr"/>
@@ -9103,7 +9103,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>汇智同裕（深圳）投资合伙企业（有限合伙）</t>
+          <t>香港迅雷有限公司</t>
         </is>
       </c>
       <c r="E178" t="inlineStr"/>
@@ -9119,7 +9119,7 @@
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -9141,7 +9141,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>北京岚锋创视网络科技有限公司</t>
         </is>
       </c>
       <c r="E179" t="inlineStr"/>
@@ -9179,7 +9179,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>QM101 Limited</t>
+          <t>汇智同裕（深圳）投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E180" t="inlineStr"/>
@@ -9195,7 +9195,7 @@
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -9217,7 +9217,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>QM101 Limited</t>
         </is>
       </c>
       <c r="E181" t="inlineStr"/>
@@ -9255,7 +9255,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>EARN ACE LIMITED</t>
         </is>
       </c>
       <c r="E182" t="inlineStr"/>
@@ -9343,7 +9343,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>深圳市稳正景明创业投资企业(有限合伙)</t>
+          <t>朱绶青</t>
         </is>
       </c>
       <c r="E184" t="inlineStr"/>
@@ -9359,7 +9359,7 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -9381,7 +9381,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>盛祎</t>
+          <t>深圳市稳正景明创业投资企业(有限合伙)</t>
         </is>
       </c>
       <c r="E185" t="inlineStr"/>
@@ -9397,7 +9397,7 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -9419,7 +9419,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>朱绶青</t>
+          <t>盛祎</t>
         </is>
       </c>
       <c r="E186" t="inlineStr"/>
@@ -9541,11 +9541,15 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>牛威</t>
+          <t>四方股份</t>
         </is>
       </c>
       <c r="E189" t="inlineStr"/>
-      <c r="F189" t="inlineStr"/>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>1200.0</t>
+        </is>
+      </c>
       <c r="G189" t="inlineStr"/>
       <c r="H189" t="inlineStr"/>
       <c r="I189" t="inlineStr"/>
@@ -9557,7 +9561,7 @@
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -9579,7 +9583,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>吴功友</t>
+          <t>牛威</t>
         </is>
       </c>
       <c r="E190" t="inlineStr"/>
@@ -9617,15 +9621,11 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>四方股份</t>
+          <t>吴功友</t>
         </is>
       </c>
       <c r="E191" t="inlineStr"/>
-      <c r="F191" t="inlineStr">
-        <is>
-          <t>1200.0</t>
-        </is>
-      </c>
+      <c r="F191" t="inlineStr"/>
       <c r="G191" t="inlineStr"/>
       <c r="H191" t="inlineStr"/>
       <c r="I191" t="inlineStr"/>
@@ -9637,7 +9637,7 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -9659,20 +9659,20 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>策星九天</t>
+          <t>幸福二期</t>
         </is>
       </c>
       <c r="E192" t="inlineStr"/>
       <c r="F192" t="inlineStr"/>
       <c r="G192" t="inlineStr">
         <is>
-          <t>2345.0781</t>
+          <t>300.0</t>
         </is>
       </c>
       <c r="H192" t="inlineStr"/>
       <c r="I192" t="inlineStr">
         <is>
-          <t>2345.0781</t>
+          <t>300.0</t>
         </is>
       </c>
       <c r="J192" t="inlineStr"/>
@@ -9705,18 +9705,22 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>牛威</t>
+          <t>策星银河</t>
         </is>
       </c>
       <c r="E193" t="inlineStr"/>
-      <c r="F193" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="G193" t="inlineStr"/>
+      <c r="F193" t="inlineStr"/>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
       <c r="H193" t="inlineStr"/>
-      <c r="I193" t="inlineStr"/>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
       <c r="J193" t="inlineStr"/>
       <c r="K193" t="inlineStr">
         <is>
@@ -9725,7 +9729,7 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -9747,20 +9751,20 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>幸福一期</t>
+          <t>策星逐日</t>
         </is>
       </c>
       <c r="E194" t="inlineStr"/>
       <c r="F194" t="inlineStr"/>
       <c r="G194" t="inlineStr">
         <is>
-          <t>917.4219</t>
+          <t>171.0</t>
         </is>
       </c>
       <c r="H194" t="inlineStr"/>
       <c r="I194" t="inlineStr">
         <is>
-          <t>917.4219</t>
+          <t>171.0</t>
         </is>
       </c>
       <c r="J194" t="inlineStr"/>
@@ -9793,20 +9797,20 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>策星逐日</t>
+          <t>策星揽月</t>
         </is>
       </c>
       <c r="E195" t="inlineStr"/>
       <c r="F195" t="inlineStr"/>
       <c r="G195" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>412.5</t>
         </is>
       </c>
       <c r="H195" t="inlineStr"/>
       <c r="I195" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>412.5</t>
         </is>
       </c>
       <c r="J195" t="inlineStr"/>
@@ -9839,22 +9843,18 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>策星银河</t>
+          <t>牛威</t>
         </is>
       </c>
       <c r="E196" t="inlineStr"/>
-      <c r="F196" t="inlineStr"/>
-      <c r="G196" t="inlineStr">
-        <is>
-          <t>279.0</t>
-        </is>
-      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr"/>
       <c r="H196" t="inlineStr"/>
-      <c r="I196" t="inlineStr">
-        <is>
-          <t>279.0</t>
-        </is>
-      </c>
+      <c r="I196" t="inlineStr"/>
       <c r="J196" t="inlineStr"/>
       <c r="K196" t="inlineStr">
         <is>
@@ -9863,7 +9863,7 @@
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -9885,20 +9885,20 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>中科星图股份有限公司</t>
+          <t>幸福一期</t>
         </is>
       </c>
       <c r="E197" t="inlineStr"/>
       <c r="F197" t="inlineStr"/>
       <c r="G197" t="inlineStr">
         <is>
-          <t>3825.0</t>
+          <t>917.4219</t>
         </is>
       </c>
       <c r="H197" t="inlineStr"/>
       <c r="I197" t="inlineStr">
         <is>
-          <t>3825.0</t>
+          <t>917.4219</t>
         </is>
       </c>
       <c r="J197" t="inlineStr"/>
@@ -9931,20 +9931,20 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>幸福二期</t>
+          <t>策星九天</t>
         </is>
       </c>
       <c r="E198" t="inlineStr"/>
       <c r="F198" t="inlineStr"/>
       <c r="G198" t="inlineStr">
         <is>
-          <t>300.0</t>
+          <t>2345.0781</t>
         </is>
       </c>
       <c r="H198" t="inlineStr"/>
       <c r="I198" t="inlineStr">
         <is>
-          <t>300.0</t>
+          <t>2345.0781</t>
         </is>
       </c>
       <c r="J198" t="inlineStr"/>
@@ -9977,20 +9977,20 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>策星揽月</t>
+          <t>中科星图股份有限公司</t>
         </is>
       </c>
       <c r="E199" t="inlineStr"/>
       <c r="F199" t="inlineStr"/>
       <c r="G199" t="inlineStr">
         <is>
-          <t>412.5</t>
+          <t>3825.0</t>
         </is>
       </c>
       <c r="H199" t="inlineStr"/>
       <c r="I199" t="inlineStr">
         <is>
-          <t>412.5</t>
+          <t>3825.0</t>
         </is>
       </c>
       <c r="J199" t="inlineStr"/>
@@ -10414,7 +10414,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>生成时间: 2026-06-12T16:09:12.683764</t>
+          <t>生成时间: 2026-06-12T16:30:01.120408</t>
         </is>
       </c>
     </row>

--- a/outputs/week2_excel/603418_友升股份_三表抽取.xlsx
+++ b/outputs/week2_excel/603418_友升股份_三表抽取.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -513,509 +513,737 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>auto_extract:友升股份</t>
+          <t>友声股份2.md 第695-730行</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2020-09</t>
+          <t>1992-12-04</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>金浦科创基金</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>12000</v>
+          <t>上海市青浦县徐泾乡工业公司</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>增资</t>
+          <t>设立</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>60.00%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>ea15746ec0381a6c0.jpg)
-&lt;details&gt;
-&lt;summary&gt;flowchart&lt;/summary&gt;
-```mermaid
-graph TD
-    A["友升股份设立\n(2020年9月, 股本12,000.00万元)"] --&gt; B["友升股份增资1,380万元\n(2020年9月, 股本13,380.00万元)"]
-    B --&gt; C["友升股份增资1,100.1333万元\n(2022年12月, 股本14,480.1333万元)"]
-    D["金浦临港基金增资840.00万元, 金浦科创基金增资360.00万元, 上海骁墨增资180.00万元"] -.-&gt; E["杉晖创业、上海联炻、安吉璞颉、深圳达晨创程等增资1,100.1333万元"]
-```
-&lt;/details&gt;
-# （一）有限责任公司的设立情况
-友升有限成立于 1992 年 12 月 4 日，由徐泾工业公司、友升太平洋美国共同出资设立的中外合资有限责任公司，注册资</t>
+          <t>友升有限成立于1992年12月4日，由徐泾工业公司、友升太平洋美国共同出资设立的中外合资有限责任公司，注册资本为400万美元。徐泾工业公司出资240万美元(60%)，友升太平洋美国出资160万美元(40%)。上海青浦会计师事务所分别于1993年8月20日、1996年12月31日出具验资报告，确认友升有限400万美元注册资金已全部到位。</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>auto_extract:友升股份</t>
+          <t>友声股份2.md 第695-730行</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2020-09</t>
+          <t>1992-12-04</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>（一）有限责任公司</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>1380</v>
+          <t>友升太平洋(美国)投资有限公司</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>增资</t>
+          <t>设立</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>40.00%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>ea15746ec0381a6c0.jpg)
-&lt;details&gt;
-&lt;summary&gt;flowchart&lt;/summary&gt;
-```mermaid
-graph TD
-    A["友升股份设立\n(2020年9月, 股本12,000.00万元)"] --&gt; B["友升股份增资1,380万元\n(2020年9月, 股本13,380.00万元)"]
-    B --&gt; C["友升股份增资1,100.1333万元\n(2022年12月, 股本14,480.1333万元)"]
-    D["金浦临港基金增资840.00万元, 金浦科创基金增资360.00万元, 上海骁墨增资180.00万元"] -.-&gt; E["杉晖创业、上海联炻、安吉璞颉、深圳达晨创程等增资1,100.1333万元"]
-```
-&lt;/details&gt;
-# （一）有限责任公司的设立情况
-友升有限成立于 1992 年 12 月 4 日，由徐泾工业公司、友升太平洋美国共同出资设立的中外合资有限责任公司，注册资</t>
+          <t>友升有限成立于1992年12月4日，由徐泾工业公司、友升太平洋美国共同出资设立的中外合资有限责任公司，注册资本为400万美元。徐泾工业公司出资240万美元(60%)，友升太平洋美国出资160万美元(40%)。上海青浦会计师事务所分别于1993年8月20日、1996年12月31日出具验资报告，确认友升有限400万美元注册资金已全部到位。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>auto_extract:友升股份</t>
+          <t>友声股份2.md 第731-768行</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2020-09</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>金浦临港基金</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>13380</v>
+          <t>上海泽升贸易有限公司</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>8976</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>增资</t>
+          <t>整体变更</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>74.80%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>ea15746ec0381a6c0.jpg)
-&lt;details&gt;
-&lt;summary&gt;flowchart&lt;/summary&gt;
-```mermaid
-graph TD
-    A["友升股份设立\n(2020年9月, 股本12,000.00万元)"] --&gt; B["友升股份增资1,380万元\n(2020年9月, 股本13,380.00万元)"]
-    B --&gt; C["友升股份增资1,100.1333万元\n(2022年12月, 股本14,480.1333万元)"]
-    D["金浦临港基金增资840.00万元, 金浦科创基金增资360.00万元, 上海骁墨增资180.00万元"] -.-&gt; E["杉晖创业、上海联炻、安吉璞颉、深圳达晨创程等增资1,100.1333万元"]
-```
-&lt;/details&gt;
-# （一）有限责任公司的设立情况
-友升有限成立于 1992 年 12 月 4 日，由徐泾工业公司、友升太平洋美国共同出资设立的中外合资有限责任公司，注册资</t>
+          <t>公司由上海友升铝业有限公司整体变更设立。根据会计师出具的《审计报告》，友升有限截至2020年5月31日的净资产为40,482.37万元。以友升有限截至2020年5月31日的净资产40,482.37万元按3.3735:1的比例折合股本12,000.00万元（每股面值1.00元），净资产超过股本部分全部计入资本公积。2020年9月9日，公司在上海市市场监督管理局登记注册。泽升贸易8,976.00万股(74.80%)，达晨创联基金1,800.00万股(15.00%)，共青城泽升1,020.00万股(8.50%)，罗世兵204.00万股(1.70%)。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>auto_extract:友升股份</t>
+          <t>友声股份2.md 第731-768行</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2020-09</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>设立的中外合资有限责任公司</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>1100.1333</v>
+          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1800</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>增资</t>
+          <t>整体变更</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>15.00%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>ea15746ec0381a6c0.jpg)
-&lt;details&gt;
-&lt;summary&gt;flowchart&lt;/summary&gt;
-```mermaid
-graph TD
-    A["友升股份设立\n(2020年9月, 股本12,000.00万元)"] --&gt; B["友升股份增资1,380万元\n(2020年9月, 股本13,380.00万元)"]
-    B --&gt; C["友升股份增资1,100.1333万元\n(2022年12月, 股本14,480.1333万元)"]
-    D["金浦临港基金增资840.00万元, 金浦科创基金增资360.00万元, 上海骁墨增资180.00万元"] -.-&gt; E["杉晖创业、上海联炻、安吉璞颉、深圳达晨创程等增资1,100.1333万元"]
-```
-&lt;/details&gt;
-# （一）有限责任公司的设立情况
-友升有限成立于 1992 年 12 月 4 日，由徐泾工业公司、友升太平洋美国共同出资设立的中外合资有限责任公司，注册资</t>
+          <t>公司由上海友升铝业有限公司整体变更设立。根据会计师出具的《审计报告》，友升有限截至2020年5月31日的净资产为40,482.37万元。以友升有限截至2020年5月31日的净资产40,482.37万元按3.3735:1的比例折合股本12,000.00万元（每股面值1.00元），净资产超过股本部分全部计入资本公积。2020年9月9日，公司在上海市市场监督管理局登记注册。泽升贸易8,976.00万股(74.80%)，达晨创联基金1,800.00万股(15.00%)，共青城泽升1,020.00万股(8.50%)，罗世兵204.00万股(1.70%)。</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>auto_extract:友升股份</t>
+          <t>友声股份2.md 第731-768行</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2020-09</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>金浦科创基金</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>12000</v>
+          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1020</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>增资</t>
+          <t>整体变更</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>8.50%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>art&lt;/summary&gt;
-```mermaid
-graph TD
-    A["友升股份设立\n(2020年9月, 股本12,000.00万元)"] --&gt; B["友升股份增资1,380万元\n(2020年9月, 股本13,380.00万元)"]
-    B --&gt; C["友升股份增资1,100.1333万元\n(2022年12月, 股本14,480.1333万元)"]
-    D["金浦临港基金增资840.00万元, 金浦科创基金增资360.00万元, 上海骁墨增资180.00万元"] -.-&gt; E["杉晖创业、上海联炻、安吉璞颉、深圳达晨创程等增资1,100.1333万元"]
-```
-&lt;/details&gt;
-# （一）有限责任公司的设立情况
-友升有限成立于 1992 年 12 月 4 日，由徐泾工业公司、友升太平洋美国共同出资设立的中外合资有限责任公司，注册资本为 400万美元。
-1992 年 10 月 22 日，青浦县人民政府出具《青浦县人民政府关于中美合资经营“</t>
+          <t>公司由上海友升铝业有限公司整体变更设立。根据会计师出具的《审计报告》，友升有限截至2020年5月31日的净资产为40,482.37万元。以友升有限截至2020年5月31日的净资产40,482.37万元按3.3735:1的比例折合股本12,000.00万元（每股面值1.00元），净资产超过股本部分全部计入资本公积。2020年9月9日，公司在上海市市场监督管理局登记注册。泽升贸易8,976.00万股(74.80%)，达晨创联基金1,800.00万股(15.00%)，共青城泽升1,020.00万股(8.50%)，罗世兵204.00万股(1.70%)。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>auto_extract:友升股份</t>
+          <t>友声股份2.md 第731-768行</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2020-09</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>（一）有限责任公司</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>1380</v>
+          <t>罗世兵</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>204</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>增资</t>
+          <t>整体变更</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1.70%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>art&lt;/summary&gt;
-```mermaid
-graph TD
-    A["友升股份设立\n(2020年9月, 股本12,000.00万元)"] --&gt; B["友升股份增资1,380万元\n(2020年9月, 股本13,380.00万元)"]
-    B --&gt; C["友升股份增资1,100.1333万元\n(2022年12月, 股本14,480.1333万元)"]
-    D["金浦临港基金增资840.00万元, 金浦科创基金增资360.00万元, 上海骁墨增资180.00万元"] -.-&gt; E["杉晖创业、上海联炻、安吉璞颉、深圳达晨创程等增资1,100.1333万元"]
-```
-&lt;/details&gt;
-# （一）有限责任公司的设立情况
-友升有限成立于 1992 年 12 月 4 日，由徐泾工业公司、友升太平洋美国共同出资设立的中外合资有限责任公司，注册资本为 400万美元。
-1992 年 10 月 22 日，青浦县人民政府出具《青浦县人民政府关于中美合资经营“</t>
+          <t>公司由上海友升铝业有限公司整体变更设立。根据会计师出具的《审计报告》，友升有限截至2020年5月31日的净资产为40,482.37万元。以友升有限截至2020年5月31日的净资产40,482.37万元按3.3735:1的比例折合股本12,000.00万元（每股面值1.00元），净资产超过股本部分全部计入资本公积。2020年9月9日，公司在上海市市场监督管理局登记注册。泽升贸易8,976.00万股(74.80%)，达晨创联基金1,800.00万股(15.00%)，共青城泽升1,020.00万股(8.50%)，罗世兵204.00万股(1.70%)。</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>auto_extract:友升股份</t>
+          <t>友声股份2.md 第769-802行</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2020-09</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>金浦临港基金</t>
-        </is>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>840</v>
       </c>
       <c r="E8" t="n">
-        <v>13380</v>
+        <v>7000</v>
+      </c>
+      <c r="F8" t="n">
+        <v>8.333299999999999</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
           <t>增资</t>
         </is>
       </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>6.28%</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>art&lt;/summary&gt;
-```mermaid
-graph TD
-    A["友升股份设立\n(2020年9月, 股本12,000.00万元)"] --&gt; B["友升股份增资1,380万元\n(2020年9月, 股本13,380.00万元)"]
-    B --&gt; C["友升股份增资1,100.1333万元\n(2022年12月, 股本14,480.1333万元)"]
-    D["金浦临港基金增资840.00万元, 金浦科创基金增资360.00万元, 上海骁墨增资180.00万元"] -.-&gt; E["杉晖创业、上海联炻、安吉璞颉、深圳达晨创程等增资1,100.1333万元"]
-```
-&lt;/details&gt;
-# （一）有限责任公司的设立情况
-友升有限成立于 1992 年 12 月 4 日，由徐泾工业公司、友升太平洋美国共同出资设立的中外合资有限责任公司，注册资本为 400万美元。
-1992 年 10 月 22 日，青浦县人民政府出具《青浦县人民政府关于中美合资经营“</t>
+          <t>2020年9月，金浦临港基金、金浦科创基金和上海骁墨与本次增资前公司股东泽升贸易、罗世兵、共青城泽升、达晨创联基金共同签署《投资协议》，约定金浦临港基金、金浦科创基金和上海骁墨分别以7,000万元、3,000万元和1,500万元认购发行人新增注册资本840万元、360万元和180万元。新增股份的认购价格为8.3333元/股。2020年9月30日完成工商变更。增资后：泽升贸易67.09%、达晨创联基金13.45%、共青城泽升7.62%、金浦临港基金6.28%、金浦科创基金2.69%、罗世兵1.52%、上海骁墨1.35%。</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>auto_extract:友升股份</t>
+          <t>友声股份2.md 第769-802行</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2020-09</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>设立的中外合资有限责任公司</t>
-        </is>
+          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>360</v>
       </c>
       <c r="E9" t="n">
-        <v>1100.1333</v>
+        <v>3000</v>
+      </c>
+      <c r="F9" t="n">
+        <v>8.333299999999999</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
           <t>增资</t>
         </is>
       </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2.69%</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>art&lt;/summary&gt;
-```mermaid
-graph TD
-    A["友升股份设立\n(2020年9月, 股本12,000.00万元)"] --&gt; B["友升股份增资1,380万元\n(2020年9月, 股本13,380.00万元)"]
-    B --&gt; C["友升股份增资1,100.1333万元\n(2022年12月, 股本14,480.1333万元)"]
-    D["金浦临港基金增资840.00万元, 金浦科创基金增资360.00万元, 上海骁墨增资180.00万元"] -.-&gt; E["杉晖创业、上海联炻、安吉璞颉、深圳达晨创程等增资1,100.1333万元"]
-```
-&lt;/details&gt;
-# （一）有限责任公司的设立情况
-友升有限成立于 1992 年 12 月 4 日，由徐泾工业公司、友升太平洋美国共同出资设立的中外合资有限责任公司，注册资本为 400万美元。
-1992 年 10 月 22 日，青浦县人民政府出具《青浦县人民政府关于中美合资经营“</t>
+          <t>2020年9月，金浦临港基金、金浦科创基金和上海骁墨与本次增资前公司股东泽升贸易、罗世兵、共青城泽升、达晨创联基金共同签署《投资协议》，约定金浦临港基金、金浦科创基金和上海骁墨分别以7,000万元、3,000万元和1,500万元认购发行人新增注册资本840万元、360万元和180万元。新增股份的认购价格为8.3333元/股。2020年9月30日完成工商变更。增资后：泽升贸易67.09%、达晨创联基金13.45%、共青城泽升7.62%、金浦临港基金6.28%、金浦科创基金2.69%、罗世兵1.52%、上海骁墨1.35%。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>auto_extract:友升股份</t>
+          <t>友声股份2.md 第769-802行</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2022-12</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>金浦科创基金</t>
-        </is>
+          <t>上海骁墨信息技术服务中心(有限合伙)</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>180</v>
       </c>
       <c r="E10" t="n">
-        <v>12000</v>
+        <v>1500</v>
+      </c>
+      <c r="F10" t="n">
+        <v>8.333299999999999</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
           <t>增资</t>
         </is>
       </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1.35%</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>股本12,000.00万元)"] --&gt; B["友升股份增资1,380万元\n(2020年9月, 股本13,380.00万元)"]
-    B --&gt; C["友升股份增资1,100.1333万元\n(2022年12月, 股本14,480.1333万元)"]
-    D["金浦临港基金增资840.00万元, 金浦科创基金增资360.00万元, 上海骁墨增资180.00万元"] -.-&gt; E["杉晖创业、上海联炻、安吉璞颉、深圳达晨创程等增资1,100.1333万元"]
-```
-&lt;/details&gt;
-# （一）有限责任公司的设立情况
-友升有限成立于 1992 年 12 月 4 日，由徐泾工业公司、友升太平洋美国共同出资设立的中外合资有限责任公司，注册资本为 400万美元。
-1992 年 10 月 22 日，青浦县人民政府出具《青浦县人民政府关于中美合资经营“上海友升铝业有限公司”合同、章程的批复》（青府贸（1992）289号），批复同意设立友升有限等相关事项。1992年 1</t>
+          <t>2020年9月，金浦临港基金、金浦科创基金和上海骁墨与本次增资前公司股东泽升贸易、罗世兵、共青城泽升、达晨创联基金共同签署《投资协议》，约定金浦临港基金、金浦科创基金和上海骁墨分别以7,000万元、3,000万元和1,500万元认购发行人新增注册资本840万元、360万元和180万元。新增股份的认购价格为8.3333元/股。2020年9月30日完成工商变更。增资后：泽升贸易67.09%、达晨创联基金13.45%、共青城泽升7.62%、金浦临港基金6.28%、金浦科创基金2.69%、罗世兵1.52%、上海骁墨1.35%。</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>auto_extract:友升股份</t>
+          <t>友声股份2.md 第804-870行</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2022-12</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>金浦临港基金</t>
-        </is>
+          <t>深圳市杉晖创业投资合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>297.3333</v>
       </c>
       <c r="E11" t="n">
-        <v>1380</v>
+        <v>10000</v>
+      </c>
+      <c r="F11" t="n">
+        <v>33.6323</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
           <t>增资</t>
         </is>
       </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2.05%</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>股本12,000.00万元)"] --&gt; B["友升股份增资1,380万元\n(2020年9月, 股本13,380.00万元)"]
-    B --&gt; C["友升股份增资1,100.1333万元\n(2022年12月, 股本14,480.1333万元)"]
-    D["金浦临港基金增资840.00万元, 金浦科创基金增资360.00万元, 上海骁墨增资180.00万元"] -.-&gt; E["杉晖创业、上海联炻、安吉璞颉、深圳达晨创程等增资1,100.1333万元"]
-```
-&lt;/details&gt;
-# （一）有限责任公司的设立情况
-友升有限成立于 1992 年 12 月 4 日，由徐泾工业公司、友升太平洋美国共同出资设立的中外合资有限责任公司，注册资本为 400万美元。
-1992 年 10 月 22 日，青浦县人民政府出具《青浦县人民政府关于中美合资经营“上海友升铝业有限公司”合同、章程的批复》（青府贸（1992）289号），批复同意设立友升有限等相关事项。1992年 1</t>
+          <t>2022年12月4日，友升股份召开第一届董事会第十六次会议，同意增加注册资本至14,480.1333万元，新增股份的认购价格为33.6323元/股。杉晖创业认购297.3333万股(10,000万元)，上海联炻认购297.3333万股(10,000万元)，安吉璞颉认购148.6667万股(5,000万元)，财投晨源认购89.2万股(3,000万元)，深圳达晨创程认购86.5984万股(2,912.5万元)，杉创智至认购59.4667万股(2,000万元)，杭州达晨创程认购51.959万股(1,747.5万元)，达晨财汇认购29.7333万股(1,000万元)，达晨财智认购29.7333万股(1,000万元)，财智创赢认购10.1093万股(340万元)。合计1,100.1333万股，37,000万元。2022年12月19日完成工商变更。</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>auto_extract:友升股份</t>
+          <t>友声股份2.md 第804-870行</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2022-12</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>（一）有限责任公司</t>
-        </is>
+          <t>上海联炻企业管理中心(有限合伙)</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>297.3333</v>
       </c>
       <c r="E12" t="n">
-        <v>13380</v>
+        <v>10000</v>
+      </c>
+      <c r="F12" t="n">
+        <v>33.6323</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
           <t>增资</t>
         </is>
       </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2.05%</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>股本12,000.00万元)"] --&gt; B["友升股份增资1,380万元\n(2020年9月, 股本13,380.00万元)"]
-    B --&gt; C["友升股份增资1,100.1333万元\n(2022年12月, 股本14,480.1333万元)"]
-    D["金浦临港基金增资840.00万元, 金浦科创基金增资360.00万元, 上海骁墨增资180.00万元"] -.-&gt; E["杉晖创业、上海联炻、安吉璞颉、深圳达晨创程等增资1,100.1333万元"]
-```
-&lt;/details&gt;
-# （一）有限责任公司的设立情况
-友升有限成立于 1992 年 12 月 4 日，由徐泾工业公司、友升太平洋美国共同出资设立的中外合资有限责任公司，注册资本为 400万美元。
-1992 年 10 月 22 日，青浦县人民政府出具《青浦县人民政府关于中美合资经营“上海友升铝业有限公司”合同、章程的批复》（青府贸（1992）289号），批复同意设立友升有限等相关事项。1992年 1</t>
+          <t>2022年12月4日，友升股份召开第一届董事会第十六次会议，同意增加注册资本至14,480.1333万元，新增股份的认购价格为33.6323元/股。杉晖创业认购297.3333万股(10,000万元)，上海联炻认购297.3333万股(10,000万元)，安吉璞颉认购148.6667万股(5,000万元)，财投晨源认购89.2万股(3,000万元)，深圳达晨创程认购86.5984万股(2,912.5万元)，杉创智至认购59.4667万股(2,000万元)，杭州达晨创程认购51.959万股(1,747.5万元)，达晨财汇认购29.7333万股(1,000万元)，达晨财智认购29.7333万股(1,000万元)，财智创赢认购10.1093万股(340万元)。合计1,100.1333万股，37,000万元。2022年12月19日完成工商变更。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>auto_extract:友升股份</t>
+          <t>友声股份2.md 第804-870行</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2022-12</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>上海友升铝业有限公司</t>
-        </is>
+          <t>安吉璞颉企业管理合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>148.6667</v>
       </c>
       <c r="E13" t="n">
-        <v>1100.1333</v>
+        <v>5000</v>
+      </c>
+      <c r="F13" t="n">
+        <v>33.6323</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
           <t>增资</t>
         </is>
       </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1.03%</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>股本12,000.00万元)"] --&gt; B["友升股份增资1,380万元\n(2020年9月, 股本13,380.00万元)"]
-    B --&gt; C["友升股份增资1,100.1333万元\n(2022年12月, 股本14,480.1333万元)"]
-    D["金浦临港基金增资840.00万元, 金浦科创基金增资360.00万元, 上海骁墨增资180.00万元"] -.-&gt; E["杉晖创业、上海联炻、安吉璞颉、深圳达晨创程等增资1,100.1333万元"]
-```
-&lt;/details&gt;
-# （一）有限责任公司的设立情况
-友升有限成立于 1992 年 12 月 4 日，由徐泾工业公司、友升太平洋美国共同出资设立的中外合资有限责任公司，注册资本为 400万美元。
-1992 年 10 月 22 日，青浦县人民政府出具《青浦县人民政府关于中美合资经营“上海友升铝业有限公司”合同、章程的批复》（青府贸（1992）289号），批复同意设立友升有限等相关事项。1992年 1</t>
+          <t>2022年12月4日，友升股份召开第一届董事会第十六次会议，同意增加注册资本至14,480.1333万元，新增股份的认购价格为33.6323元/股。杉晖创业认购297.3333万股(10,000万元)，上海联炻认购297.3333万股(10,000万元)，安吉璞颉认购148.6667万股(5,000万元)，财投晨源认购89.2万股(3,000万元)，深圳达晨创程认购86.5984万股(2,912.5万元)，杉创智至认购59.4667万股(2,000万元)，杭州达晨创程认购51.959万股(1,747.5万元)，达晨财汇认购29.7333万股(1,000万元)，达晨财智认购29.7333万股(1,000万元)，财智创赢认购10.1093万股(340万元)。合计1,100.1333万股，37,000万元。2022年12月19日完成工商变更。</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>auto_extract:友升股份</t>
+          <t>友声股份2.md 第804-870行</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2022-12</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>设立的中外合资有限责任公司</t>
-        </is>
+          <t>江西赣江新区财投晨源股权投资中心(有限合伙)</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>89.2</v>
       </c>
       <c r="E14" t="n">
-        <v>14480.1333</v>
+        <v>3000</v>
+      </c>
+      <c r="F14" t="n">
+        <v>33.6323</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
           <t>增资</t>
         </is>
       </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>0.62%</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>股本12,000.00万元)"] --&gt; B["友升股份增资1,380万元\n(2020年9月, 股本13,380.00万元)"]
-    B --&gt; C["友升股份增资1,100.1333万元\n(2022年12月, 股本14,480.1333万元)"]
-    D["金浦临港基金增资840.00万元, 金浦科创基金增资360.00万元, 上海骁墨增资180.00万元"] -.-&gt; E["杉晖创业、上海联炻、安吉璞颉、深圳达晨创程等增资1,100.1333万元"]
-```
-&lt;/details&gt;
-# （一）有限责任公司的设立情况
-友升有限成立于 1992 年 12 月 4 日，由徐泾工业公司、友升太平洋美国共同出资设立的中外合资有限责任公司，注册资本为 400万美元。
-1992 年 10 月 22 日，青浦县人民政府出具《青浦县人民政府关于中美合资经营“上海友升铝业有限公司”合同、章程的批复》（青府贸（1992）289号），批复同意设立友升有限等相关事项。1992年 1</t>
+          <t>2022年12月4日，友升股份召开第一届董事会第十六次会议，同意增加注册资本至14,480.1333万元，新增股份的认购价格为33.6323元/股。杉晖创业认购297.3333万股(10,000万元)，上海联炻认购297.3333万股(10,000万元)，安吉璞颉认购148.6667万股(5,000万元)，财投晨源认购89.2万股(3,000万元)，深圳达晨创程认购86.5984万股(2,912.5万元)，杉创智至认购59.4667万股(2,000万元)，杭州达晨创程认购51.959万股(1,747.5万元)，达晨财汇认购29.7333万股(1,000万元)，达晨财智认购29.7333万股(1,000万元)，财智创赢认购10.1093万股(340万元)。合计1,100.1333万股，37,000万元。2022年12月19日完成工商变更。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>友声股份2.md 第804-870行</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2022-12-19</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>深圳市达晨创程私募股权投资基金企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>86.5984</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2912.5</v>
+      </c>
+      <c r="F15" t="n">
+        <v>33.6323</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>增资</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>0.60%</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>2022年12月4日，友升股份召开第一届董事会第十六次会议，同意增加注册资本至14,480.1333万元，新增股份的认购价格为33.6323元/股。杉晖创业认购297.3333万股(10,000万元)，上海联炻认购297.3333万股(10,000万元)，安吉璞颉认购148.6667万股(5,000万元)，财投晨源认购89.2万股(3,000万元)，深圳达晨创程认购86.5984万股(2,912.5万元)，杉创智至认购59.4667万股(2,000万元)，杭州达晨创程认购51.959万股(1,747.5万元)，达晨财汇认购29.7333万股(1,000万元)，达晨财智认购29.7333万股(1,000万元)，财智创赢认购10.1093万股(340万元)。合计1,100.1333万股，37,000万元。2022年12月19日完成工商变更。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>友声股份2.md 第804-870行</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2022-12-19</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>上海杉创智至创业投资合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>59.4667</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F16" t="n">
+        <v>33.6323</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>增资</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>0.41%</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>2022年12月4日，友升股份召开第一届董事会第十六次会议，同意增加注册资本至14,480.1333万元，新增股份的认购价格为33.6323元/股。杉晖创业认购297.3333万股(10,000万元)，上海联炻认购297.3333万股(10,000万元)，安吉璞颉认购148.6667万股(5,000万元)，财投晨源认购89.2万股(3,000万元)，深圳达晨创程认购86.5984万股(2,912.5万元)，杉创智至认购59.4667万股(2,000万元)，杭州达晨创程认购51.959万股(1,747.5万元)，达晨财汇认购29.7333万股(1,000万元)，达晨财智认购29.7333万股(1,000万元)，财智创赢认购10.1093万股(340万元)。合计1,100.1333万股，37,000万元。2022年12月19日完成工商变更。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>友声股份2.md 第804-870行</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2022-12-19</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>杭州达晨创程股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>51.959</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1747.5</v>
+      </c>
+      <c r="F17" t="n">
+        <v>33.6323</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>增资</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>0.36%</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>2022年12月4日，友升股份召开第一届董事会第十六次会议，同意增加注册资本至14,480.1333万元，新增股份的认购价格为33.6323元/股。杉晖创业认购297.3333万股(10,000万元)，上海联炻认购297.3333万股(10,000万元)，安吉璞颉认购148.6667万股(5,000万元)，财投晨源认购89.2万股(3,000万元)，深圳达晨创程认购86.5984万股(2,912.5万元)，杉创智至认购59.4667万股(2,000万元)，杭州达晨创程认购51.959万股(1,747.5万元)，达晨财汇认购29.7333万股(1,000万元)，达晨财智认购29.7333万股(1,000万元)，财智创赢认购10.1093万股(340万元)。合计1,100.1333万股，37,000万元。2022年12月19日完成工商变更。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>友声股份2.md 第804-870行</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2022-12-19</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>29.7333</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F18" t="n">
+        <v>33.6323</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>增资</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>0.21%</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>2022年12月4日，友升股份召开第一届董事会第十六次会议，同意增加注册资本至14,480.1333万元，新增股份的认购价格为33.6323元/股。杉晖创业认购297.3333万股(10,000万元)，上海联炻认购297.3333万股(10,000万元)，安吉璞颉认购148.6667万股(5,000万元)，财投晨源认购89.2万股(3,000万元)，深圳达晨创程认购86.5984万股(2,912.5万元)，杉创智至认购59.4667万股(2,000万元)，杭州达晨创程认购51.959万股(1,747.5万元)，达晨财汇认购29.7333万股(1,000万元)，达晨财智认购29.7333万股(1,000万元)，财智创赢认购10.1093万股(340万元)。合计1,100.1333万股，37,000万元。2022年12月19日完成工商变更。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>友声股份2.md 第804-870行</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2022-12-19</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>深圳市达晨财智创业投资管理有限公司</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>29.7333</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F19" t="n">
+        <v>33.6323</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>增资</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0.21%</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>2022年12月4日，友升股份召开第一届董事会第十六次会议，同意增加注册资本至14,480.1333万元，新增股份的认购价格为33.6323元/股。杉晖创业认购297.3333万股(10,000万元)，上海联炻认购297.3333万股(10,000万元)，安吉璞颉认购148.6667万股(5,000万元)，财投晨源认购89.2万股(3,000万元)，深圳达晨创程认购86.5984万股(2,912.5万元)，杉创智至认购59.4667万股(2,000万元)，杭州达晨创程认购51.959万股(1,747.5万元)，达晨财汇认购29.7333万股(1,000万元)，达晨财智认购29.7333万股(1,000万元)，财智创赢认购10.1093万股(340万元)。合计1,100.1333万股，37,000万元。2022年12月19日完成工商变更。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>友声股份2.md 第804-870行</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2022-12-19</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>深圳市财智创赢私募股权投资企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>10.1093</v>
+      </c>
+      <c r="E20" t="n">
+        <v>340</v>
+      </c>
+      <c r="F20" t="n">
+        <v>33.6323</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>增资</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>0.07%</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>2022年12月4日，友升股份召开第一届董事会第十六次会议，同意增加注册资本至14,480.1333万元，新增股份的认购价格为33.6323元/股。杉晖创业认购297.3333万股(10,000万元)，上海联炻认购297.3333万股(10,000万元)，安吉璞颉认购148.6667万股(5,000万元)，财投晨源认购89.2万股(3,000万元)，深圳达晨创程认购86.5984万股(2,912.5万元)，杉创智至认购59.4667万股(2,000万元)，杭州达晨创程认购51.959万股(1,747.5万元)，达晨财汇认购29.7333万股(1,000万元)，达晨财智认购29.7333万股(1,000万元)，财智创赢认购10.1093万股(340万元)。合计1,100.1333万股，37,000万元。2022年12月19日完成工商变更。</t>
         </is>
       </c>
     </row>
@@ -1030,7 +1258,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1118,26 +1346,23 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>auto_extract:友升股份</t>
+          <t>友声股份2.md 第695-730行</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2022-12</t>
+          <t>1992-12-04</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>自动提取</t>
+          <t>设立后</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>徐泾工业公司</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>240</v>
+          <t>上海市青浦县徐泾乡工业公司</t>
+        </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -1146,38 +1371,45 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>t0</t>
+          <t>t1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>自动从股权结构表提取: 股东徐泾工业公司 持股None万股 占比60.00%。原始表格共4行，需人工核对PDF原文。</t>
+          <t>友升有限成立于1992年12月4日，由徐泾工业公司、友升太平洋美国共同出资设立的中外合资有限责任公司，注册资本为400万美元。徐泾工业公司出资240万美元(60%)，友升太平洋美国出资160万美元(40%)。上海青浦会计师事务所分别于1993年8月20日、1996年12月31日出具验资报告，确认友升有限400万美元注册资金已全部到位。</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>auto_extract:友升股份</t>
+          <t>友声股份2.md 第695-730行</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2022-12</t>
+          <t>1992-12-04</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>自动提取</t>
+          <t>设立后</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>友升太平洋美国</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>160</v>
+          <t>友升太平洋(美国)投资有限公司</t>
+        </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -1186,12 +1418,911 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>t0</t>
+          <t>t1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>外部PE</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>自动从股权结构表提取: 股东友升太平洋美国 持股None万股 占比40.00%。原始表格共4行，需人工核对PDF原文。</t>
+          <t>友升有限成立于1992年12月4日，由徐泾工业公司、友升太平洋美国共同出资设立的中外合资有限责任公司，注册资本为400万美元。徐泾工业公司出资240万美元(60%)，友升太平洋美国出资160万美元(40%)。上海青浦会计师事务所分别于1993年8月20日、1996年12月31日出具验资报告，确认友升有限400万美元注册资金已全部到位。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>友声股份2.md 第731-768行</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2020-09-09</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>整体变更后</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>上海泽升贸易有限公司</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>8976</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>74.80%</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>t2</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>公司由上海友升铝业有限公司整体变更设立。根据会计师出具的《审计报告》，友升有限截至2020年5月31日的净资产为40,482.37万元。以友升有限截至2020年5月31日的净资产40,482.37万元按3.3735:1的比例折合股本12,000.00万元（每股面值1.00元），净资产超过股本部分全部计入资本公积。2020年9月9日，公司在上海市市场监督管理局登记注册。泽升贸易8,976.00万股(74.80%)，达晨创联基金1,800.00万股(15.00%)，共青城泽升1,020.00万股(8.50%)，罗世兵204.00万股(1.70%)。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>友声股份2.md 第731-768行</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2020-09-09</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>整体变更后</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>1800</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>15.00%</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>t2</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>外部PE</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>公司由上海友升铝业有限公司整体变更设立。根据会计师出具的《审计报告》，友升有限截至2020年5月31日的净资产为40,482.37万元。以友升有限截至2020年5月31日的净资产40,482.37万元按3.3735:1的比例折合股本12,000.00万元（每股面值1.00元），净资产超过股本部分全部计入资本公积。2020年9月9日，公司在上海市市场监督管理局登记注册。泽升贸易8,976.00万股(74.80%)，达晨创联基金1,800.00万股(15.00%)，共青城泽升1,020.00万股(8.50%)，罗世兵204.00万股(1.70%)。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>友声股份2.md 第731-768行</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2020-09-09</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>整体变更后</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>1020</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>8.50%</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>t2</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>外部PE</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>公司由上海友升铝业有限公司整体变更设立。根据会计师出具的《审计报告》，友升有限截至2020年5月31日的净资产为40,482.37万元。以友升有限截至2020年5月31日的净资产40,482.37万元按3.3735:1的比例折合股本12,000.00万元（每股面值1.00元），净资产超过股本部分全部计入资本公积。2020年9月9日，公司在上海市市场监督管理局登记注册。泽升贸易8,976.00万股(74.80%)，达晨创联基金1,800.00万股(15.00%)，共青城泽升1,020.00万股(8.50%)，罗世兵204.00万股(1.70%)。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>友声股份2.md 第731-768行</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2020-09-09</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>整体变更后</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>罗世兵</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>204</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1.70%</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>t2</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>公司由上海友升铝业有限公司整体变更设立。根据会计师出具的《审计报告》，友升有限截至2020年5月31日的净资产为40,482.37万元。以友升有限截至2020年5月31日的净资产40,482.37万元按3.3735:1的比例折合股本12,000.00万元（每股面值1.00元），净资产超过股本部分全部计入资本公积。2020年9月9日，公司在上海市市场监督管理局登记注册。泽升贸易8,976.00万股(74.80%)，达晨创联基金1,800.00万股(15.00%)，共青城泽升1,020.00万股(8.50%)，罗世兵204.00万股(1.70%)。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>友声股份2.md 第769-802行</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>增资后</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>840</v>
+      </c>
+      <c r="H8" t="n">
+        <v>7000</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>6.28%</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>t3</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>外部PE</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2020年9月，金浦临港基金、金浦科创基金和上海骁墨与本次增资前公司股东泽升贸易、罗世兵、共青城泽升、达晨创联基金共同签署《投资协议》，约定金浦临港基金、金浦科创基金和上海骁墨分别以7,000万元、3,000万元和1,500万元认购发行人新增注册资本840万元、360万元和180万元。新增股份的认购价格为8.3333元/股。2020年9月30日完成工商变更。增资后：泽升贸易67.09%、达晨创联基金13.45%、共青城泽升7.62%、金浦临港基金6.28%、金浦科创基金2.69%、罗世兵1.52%、上海骁墨1.35%。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>友声股份2.md 第769-802行</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>增资后</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>360</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2.69%</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>t3</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>外部PE</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2020年9月，金浦临港基金、金浦科创基金和上海骁墨与本次增资前公司股东泽升贸易、罗世兵、共青城泽升、达晨创联基金共同签署《投资协议》，约定金浦临港基金、金浦科创基金和上海骁墨分别以7,000万元、3,000万元和1,500万元认购发行人新增注册资本840万元、360万元和180万元。新增股份的认购价格为8.3333元/股。2020年9月30日完成工商变更。增资后：泽升贸易67.09%、达晨创联基金13.45%、共青城泽升7.62%、金浦临港基金6.28%、金浦科创基金2.69%、罗世兵1.52%、上海骁墨1.35%。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>友声股份2.md 第769-802行</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>增资后</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>上海骁墨信息技术服务中心(有限合伙)</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>180</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1.35%</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>t3</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>外部PE</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2020年9月，金浦临港基金、金浦科创基金和上海骁墨与本次增资前公司股东泽升贸易、罗世兵、共青城泽升、达晨创联基金共同签署《投资协议》，约定金浦临港基金、金浦科创基金和上海骁墨分别以7,000万元、3,000万元和1,500万元认购发行人新增注册资本840万元、360万元和180万元。新增股份的认购价格为8.3333元/股。2020年9月30日完成工商变更。增资后：泽升贸易67.09%、达晨创联基金13.45%、共青城泽升7.62%、金浦临港基金6.28%、金浦科创基金2.69%、罗世兵1.52%、上海骁墨1.35%。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>友声股份2.md 第804-870行</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2022-12-19</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>增资后</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>深圳市杉晖创业投资合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>297.3333</v>
+      </c>
+      <c r="H11" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2.05%</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>t4</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>外部PE</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2022年12月4日，友升股份召开第一届董事会第十六次会议，同意增加注册资本至14,480.1333万元，新增股份的认购价格为33.6323元/股。杉晖创业认购297.3333万股(10,000万元)，上海联炻认购297.3333万股(10,000万元)，安吉璞颉认购148.6667万股(5,000万元)，财投晨源认购89.2万股(3,000万元)，深圳达晨创程认购86.5984万股(2,912.5万元)，杉创智至认购59.4667万股(2,000万元)，杭州达晨创程认购51.959万股(1,747.5万元)，达晨财汇认购29.7333万股(1,000万元)，达晨财智认购29.7333万股(1,000万元)，财智创赢认购10.1093万股(340万元)。合计1,100.1333万股，37,000万元。2022年12月19日完成工商变更。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>友声股份2.md 第804-870行</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2022-12-19</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>增资后</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>上海联炻企业管理中心(有限合伙)</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>297.3333</v>
+      </c>
+      <c r="H12" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2.05%</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>t4</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>外部PE</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2022年12月4日，友升股份召开第一届董事会第十六次会议，同意增加注册资本至14,480.1333万元，新增股份的认购价格为33.6323元/股。杉晖创业认购297.3333万股(10,000万元)，上海联炻认购297.3333万股(10,000万元)，安吉璞颉认购148.6667万股(5,000万元)，财投晨源认购89.2万股(3,000万元)，深圳达晨创程认购86.5984万股(2,912.5万元)，杉创智至认购59.4667万股(2,000万元)，杭州达晨创程认购51.959万股(1,747.5万元)，达晨财汇认购29.7333万股(1,000万元)，达晨财智认购29.7333万股(1,000万元)，财智创赢认购10.1093万股(340万元)。合计1,100.1333万股，37,000万元。2022年12月19日完成工商变更。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>友声股份2.md 第804-870行</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2022-12-19</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>增资后</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>安吉璞颉企业管理合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>148.6667</v>
+      </c>
+      <c r="H13" t="n">
+        <v>5000</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1.03%</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>t4</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>外部PE</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2022年12月4日，友升股份召开第一届董事会第十六次会议，同意增加注册资本至14,480.1333万元，新增股份的认购价格为33.6323元/股。杉晖创业认购297.3333万股(10,000万元)，上海联炻认购297.3333万股(10,000万元)，安吉璞颉认购148.6667万股(5,000万元)，财投晨源认购89.2万股(3,000万元)，深圳达晨创程认购86.5984万股(2,912.5万元)，杉创智至认购59.4667万股(2,000万元)，杭州达晨创程认购51.959万股(1,747.5万元)，达晨财汇认购29.7333万股(1,000万元)，达晨财智认购29.7333万股(1,000万元)，财智创赢认购10.1093万股(340万元)。合计1,100.1333万股，37,000万元。2022年12月19日完成工商变更。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>友声股份2.md 第804-870行</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2022-12-19</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>增资后</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>江西赣江新区财投晨源股权投资中心(有限合伙)</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>89.2</v>
+      </c>
+      <c r="H14" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>0.62%</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>t4</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>外部PE</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2022年12月4日，友升股份召开第一届董事会第十六次会议，同意增加注册资本至14,480.1333万元，新增股份的认购价格为33.6323元/股。杉晖创业认购297.3333万股(10,000万元)，上海联炻认购297.3333万股(10,000万元)，安吉璞颉认购148.6667万股(5,000万元)，财投晨源认购89.2万股(3,000万元)，深圳达晨创程认购86.5984万股(2,912.5万元)，杉创智至认购59.4667万股(2,000万元)，杭州达晨创程认购51.959万股(1,747.5万元)，达晨财汇认购29.7333万股(1,000万元)，达晨财智认购29.7333万股(1,000万元)，财智创赢认购10.1093万股(340万元)。合计1,100.1333万股，37,000万元。2022年12月19日完成工商变更。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>友声股份2.md 第804-870行</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2022-12-19</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>增资后</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>深圳市达晨创程私募股权投资基金企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>86.5984</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2912.5</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>0.60%</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>t4</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>外部PE</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2022年12月4日，友升股份召开第一届董事会第十六次会议，同意增加注册资本至14,480.1333万元，新增股份的认购价格为33.6323元/股。杉晖创业认购297.3333万股(10,000万元)，上海联炻认购297.3333万股(10,000万元)，安吉璞颉认购148.6667万股(5,000万元)，财投晨源认购89.2万股(3,000万元)，深圳达晨创程认购86.5984万股(2,912.5万元)，杉创智至认购59.4667万股(2,000万元)，杭州达晨创程认购51.959万股(1,747.5万元)，达晨财汇认购29.7333万股(1,000万元)，达晨财智认购29.7333万股(1,000万元)，财智创赢认购10.1093万股(340万元)。合计1,100.1333万股，37,000万元。2022年12月19日完成工商变更。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>友声股份2.md 第804-870行</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2022-12-19</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>增资后</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>上海杉创智至创业投资合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>59.4667</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>0.41%</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>t4</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>外部PE</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2022年12月4日，友升股份召开第一届董事会第十六次会议，同意增加注册资本至14,480.1333万元，新增股份的认购价格为33.6323元/股。杉晖创业认购297.3333万股(10,000万元)，上海联炻认购297.3333万股(10,000万元)，安吉璞颉认购148.6667万股(5,000万元)，财投晨源认购89.2万股(3,000万元)，深圳达晨创程认购86.5984万股(2,912.5万元)，杉创智至认购59.4667万股(2,000万元)，杭州达晨创程认购51.959万股(1,747.5万元)，达晨财汇认购29.7333万股(1,000万元)，达晨财智认购29.7333万股(1,000万元)，财智创赢认购10.1093万股(340万元)。合计1,100.1333万股，37,000万元。2022年12月19日完成工商变更。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>友声股份2.md 第804-870行</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2022-12-19</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>增资后</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>杭州达晨创程股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>51.959</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1747.5</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>0.36%</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>t4</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>外部PE</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2022年12月4日，友升股份召开第一届董事会第十六次会议，同意增加注册资本至14,480.1333万元，新增股份的认购价格为33.6323元/股。杉晖创业认购297.3333万股(10,000万元)，上海联炻认购297.3333万股(10,000万元)，安吉璞颉认购148.6667万股(5,000万元)，财投晨源认购89.2万股(3,000万元)，深圳达晨创程认购86.5984万股(2,912.5万元)，杉创智至认购59.4667万股(2,000万元)，杭州达晨创程认购51.959万股(1,747.5万元)，达晨财汇认购29.7333万股(1,000万元)，达晨财智认购29.7333万股(1,000万元)，财智创赢认购10.1093万股(340万元)。合计1,100.1333万股，37,000万元。2022年12月19日完成工商变更。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>友声股份2.md 第804-870行</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2022-12-19</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>增资后</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>29.7333</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>0.21%</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>t4</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>外部PE</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2022年12月4日，友升股份召开第一届董事会第十六次会议，同意增加注册资本至14,480.1333万元，新增股份的认购价格为33.6323元/股。杉晖创业认购297.3333万股(10,000万元)，上海联炻认购297.3333万股(10,000万元)，安吉璞颉认购148.6667万股(5,000万元)，财投晨源认购89.2万股(3,000万元)，深圳达晨创程认购86.5984万股(2,912.5万元)，杉创智至认购59.4667万股(2,000万元)，杭州达晨创程认购51.959万股(1,747.5万元)，达晨财汇认购29.7333万股(1,000万元)，达晨财智认购29.7333万股(1,000万元)，财智创赢认购10.1093万股(340万元)。合计1,100.1333万股，37,000万元。2022年12月19日完成工商变更。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>友声股份2.md 第804-870行</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2022-12-19</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>增资后</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>深圳市达晨财智创业投资管理有限公司</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>29.7333</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0.21%</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>t4</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>外部PE</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2022年12月4日，友升股份召开第一届董事会第十六次会议，同意增加注册资本至14,480.1333万元，新增股份的认购价格为33.6323元/股。杉晖创业认购297.3333万股(10,000万元)，上海联炻认购297.3333万股(10,000万元)，安吉璞颉认购148.6667万股(5,000万元)，财投晨源认购89.2万股(3,000万元)，深圳达晨创程认购86.5984万股(2,912.5万元)，杉创智至认购59.4667万股(2,000万元)，杭州达晨创程认购51.959万股(1,747.5万元)，达晨财汇认购29.7333万股(1,000万元)，达晨财智认购29.7333万股(1,000万元)，财智创赢认购10.1093万股(340万元)。合计1,100.1333万股，37,000万元。2022年12月19日完成工商变更。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>友声股份2.md 第804-870行</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2022-12-19</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>增资后</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>深圳市财智创赢私募股权投资企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>10.1093</v>
+      </c>
+      <c r="H20" t="n">
+        <v>340</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>0.07%</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>t4</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>外部PE</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>2022年12月4日，友升股份召开第一届董事会第十六次会议，同意增加注册资本至14,480.1333万元，新增股份的认购价格为33.6323元/股。杉晖创业认购297.3333万股(10,000万元)，上海联炻认购297.3333万股(10,000万元)，安吉璞颉认购148.6667万股(5,000万元)，财投晨源认购89.2万股(3,000万元)，深圳达晨创程认购86.5984万股(2,912.5万元)，杉创智至认购59.4667万股(2,000万元)，杭州达晨创程认购51.959万股(1,747.5万元)，达晨财汇认购29.7333万股(1,000万元)，达晨财智认购29.7333万股(1,000万元)，财智创赢认购10.1093万股(340万元)。合计1,100.1333万股，37,000万元。2022年12月19日完成工商变更。</t>
         </is>
       </c>
     </row>
@@ -1206,7 +2337,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L143"/>
+  <dimension ref="A1:L211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1948,15 +3079,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>深圳市云汉电子有限公司</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>25.0</t>
-        </is>
-      </c>
+      <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
@@ -1968,7 +3095,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -1990,7 +3117,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
+          <t>东方富海（上海）创业投资企业（有限合伙）</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
@@ -2028,11 +3155,15 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>刘云锋</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>25.0</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
@@ -2044,7 +3175,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2066,7 +3197,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>东方富海（上海）创业投资企业（有限合伙）</t>
+          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
@@ -2104,7 +3235,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>刘云锋</t>
+          <t>深圳市云汉电子有限公司</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
@@ -2146,7 +3277,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>丰利财富（北京）国际资本管理股份有限公司</t>
+          <t>东方富海（上海）创业投资企业（有限合伙）</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
@@ -2162,7 +3293,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2184,7 +3315,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>东方富海（上海）创业投资企业（有限合伙）</t>
+          <t>深圳市创新投资集团有限公司</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
@@ -2200,7 +3331,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2222,7 +3353,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>昆山红土高新创业投资有限公司</t>
+          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
@@ -2238,7 +3369,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2260,7 +3391,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>深圳市创新投资集团有限公司</t>
+          <t>镇江红土创业投资有限公司</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
@@ -2298,7 +3429,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
+          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
@@ -2314,7 +3445,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2336,7 +3467,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>丰利财富（北京）国际资本管理股份有限公司</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
@@ -2352,7 +3483,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2374,7 +3505,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
@@ -2390,7 +3521,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2412,7 +3543,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>镇江红土创业投资有限公司</t>
+          <t>昆山红土高新创业投资有限公司</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
@@ -2450,7 +3581,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>昆山红土高新创业投资有限公司</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
@@ -2466,7 +3597,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2564,15 +3695,11 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>丰利财富（北京）国际资本管理股份有限公司</t>
+          <t>昆山红土高新创业投资有限公司</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
@@ -2606,11 +3733,15 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>丰利财富（北京）国际资本管理股份有限公司</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
@@ -2622,7 +3753,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2644,7 +3775,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
+          <t>刘云锋</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
@@ -2660,7 +3791,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2720,7 +3851,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>刘云锋</t>
+          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
@@ -2736,7 +3867,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2796,7 +3927,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
+          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
@@ -2872,7 +4003,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>夏东</t>
+          <t>CASREV FUND</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
@@ -2948,7 +4079,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
@@ -2964,7 +4095,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2986,7 +4117,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>珠海拓域投资合伙企业（有限合伙）</t>
+          <t>夏东</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
@@ -3024,7 +4155,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
@@ -3040,7 +4171,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3062,7 +4193,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>CASREV FUND</t>
+          <t>珠海拓域投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
@@ -3100,13 +4231,13 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>CASREV FUND</t>
+          <t>夏东</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="G66" t="inlineStr"/>
@@ -3142,15 +4273,11 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
+          <t>火炬电子科技股份有限公司</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>7412.0</t>
-        </is>
-      </c>
+      <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>
@@ -3162,7 +4289,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3184,13 +4311,13 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
+          <t>珠海拓域投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>1000.0</t>
         </is>
       </c>
       <c r="G68" t="inlineStr"/>
@@ -3226,13 +4353,13 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>珠海拓域投资合伙企业（有限合伙）</t>
+          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
-          <t>1000.0</t>
+          <t>1584.0</t>
         </is>
       </c>
       <c r="G69" t="inlineStr"/>
@@ -3268,11 +4395,15 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>火炬电子科技股份有限公司</t>
+          <t>CASREV FUND</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr"/>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
@@ -3284,7 +4415,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3306,13 +4437,13 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
+          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
-          <t>1584.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="G71" t="inlineStr"/>
@@ -3348,13 +4479,13 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>夏东</t>
+          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>7412.0</t>
         </is>
       </c>
       <c r="G72" t="inlineStr"/>
@@ -3390,15 +4521,11 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>火炬电子科技股份有限公司</t>
+          <t>厦门西堤股权投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>5000.0</t>
-        </is>
-      </c>
+      <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr"/>
@@ -3410,7 +4537,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3432,11 +4559,15 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>中小企业发展基金（深圳有限合伙）</t>
+          <t>火炬电子科技股份有限公司</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr"/>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>5000.0</t>
+        </is>
+      </c>
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr"/>
@@ -3448,7 +4579,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3470,7 +4601,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>厦门西堤股权投资合伙企业（有限合伙）</t>
+          <t>中小企业发展基金（深圳有限合伙）</t>
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
@@ -3546,11 +4677,15 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>昆山谷捷金属制品有限公司</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr"/>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr"/>
@@ -3562,7 +4697,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3584,7 +4719,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
@@ -3622,15 +4757,11 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>昆山谷捷金属制品有限公司</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr"/>
@@ -3642,7 +4773,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3664,7 +4795,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>张俊武</t>
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
@@ -3698,7 +4829,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>张俊武</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
@@ -3732,7 +4863,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
@@ -3766,7 +4897,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
+          <t>张俊武</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
@@ -3782,7 +4913,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3804,7 +4935,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>上海广弘实业有限公司</t>
+          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
@@ -3842,7 +4973,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>上海广弘实业有限公司</t>
         </is>
       </c>
       <c r="E85" t="inlineStr"/>
@@ -3858,7 +4989,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3880,7 +5011,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>张俊武</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
@@ -3918,7 +5049,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E87" t="inlineStr"/>
@@ -3956,11 +5087,15 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>黄山佳捷股权管理中心（有限合伙）</t>
+          <t>上海广弘实业有限公司</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr"/>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>10377.0</t>
+        </is>
+      </c>
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr"/>
@@ -3972,7 +5107,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3994,15 +5129,11 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
+          <t>黄山佳捷股权管理中心（有限合伙）</t>
         </is>
       </c>
       <c r="E89" t="inlineStr"/>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>1153.0</t>
-        </is>
-      </c>
+      <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr"/>
@@ -4014,7 +5145,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -4036,13 +5167,13 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>上海广弘实业有限公司</t>
+          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
         </is>
       </c>
       <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
-          <t>10377.0</t>
+          <t>1153.0</t>
         </is>
       </c>
       <c r="G90" t="inlineStr"/>
@@ -4078,11 +5209,15 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
+          <t>黄山佳捷股权管理中心（有限合伙）</t>
         </is>
       </c>
       <c r="E91" t="inlineStr"/>
-      <c r="F91" t="inlineStr"/>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2124.81</t>
+        </is>
+      </c>
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr"/>
@@ -4092,11 +5227,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L91" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
+      <c r="L91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -4116,7 +5247,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>上海广弘实业有限公司</t>
+          <t>张俊武</t>
         </is>
       </c>
       <c r="E92" t="inlineStr"/>
@@ -4154,7 +5285,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
         </is>
       </c>
       <c r="E93" t="inlineStr"/>
@@ -4192,15 +5323,11 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>黄山佳捷股权管理中心（有限合伙）</t>
+          <t>上海广弘实业有限公司</t>
         </is>
       </c>
       <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2124.81</t>
-        </is>
-      </c>
+      <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr"/>
@@ -4210,7 +5337,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L94" t="inlineStr"/>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -4230,7 +5361,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>张俊武</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E95" t="inlineStr"/>
@@ -4268,7 +5399,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E96" t="inlineStr"/>
@@ -4291,30 +5422,42 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>2015-01</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr"/>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr"/>
-      <c r="G97" t="inlineStr"/>
-      <c r="H97" t="inlineStr"/>
-      <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>6999.972</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>7000.0</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>-0.028</t>
+        </is>
+      </c>
       <c r="K97" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4322,37 +5465,49 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>2015-01</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr"/>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr"/>
-      <c r="G98" t="inlineStr"/>
-      <c r="H98" t="inlineStr"/>
-      <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>2999.988</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>3000.0</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>-0.012</t>
+        </is>
+      </c>
       <c r="K98" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4360,37 +5515,49 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>2015-01</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr"/>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>QM101 Limited</t>
+          <t>上海骁墨信息技术服务中心(有限合伙)</t>
         </is>
       </c>
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr"/>
-      <c r="G99" t="inlineStr"/>
-      <c r="H99" t="inlineStr"/>
-      <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>1499.994</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>1500.0</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>-0.006</t>
+        </is>
+      </c>
       <c r="K99" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4398,37 +5565,49 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>2015-01</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr"/>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>厦门富凯海创投资管理有限责任公司</t>
+          <t>深圳市杉晖创业投资合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr"/>
-      <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr"/>
-      <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>297.3333</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>10000.0027</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>10000.0</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>0.0027</t>
+        </is>
+      </c>
       <c r="K100" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4436,37 +5615,49 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>2015-01</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr"/>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>深圳市伊敦传媒投资基金合伙企业（有限合伙）</t>
+          <t>上海联炻企业管理中心(有限合伙)</t>
         </is>
       </c>
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr"/>
-      <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr"/>
-      <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>297.3333</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>10000.0027</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>10000.0</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>0.0027</t>
+        </is>
+      </c>
       <c r="K101" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4474,37 +5665,49 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>2015-01</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr"/>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>安吉璞颉企业管理合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr"/>
-      <c r="G102" t="inlineStr"/>
-      <c r="H102" t="inlineStr"/>
-      <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>148.6667</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>5000.0031</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>5000.0</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>0.0031</t>
+        </is>
+      </c>
       <c r="K102" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4512,37 +5715,49 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>2015-01</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr"/>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>深圳中证投资有限责任公司</t>
+          <t>江西赣江新区财投晨源股权投资中心(有限合伙)</t>
         </is>
       </c>
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr"/>
-      <c r="G103" t="inlineStr"/>
-      <c r="H103" t="inlineStr"/>
-      <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>89.2</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>3000.0012</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>3000.0</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>0.0012</t>
+        </is>
+      </c>
       <c r="K103" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4550,37 +5765,49 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>2015-01</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr"/>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>金石智娱股权投资（深圳）合伙企业（有限合伙）</t>
+          <t>深圳市达晨创程私募股权投资基金企业(有限合伙)</t>
         </is>
       </c>
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr"/>
-      <c r="G104" t="inlineStr"/>
-      <c r="H104" t="inlineStr"/>
-      <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>86.5984</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>2912.5034</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>2912.5</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>0.0034</t>
+        </is>
+      </c>
       <c r="K104" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4588,37 +5815,49 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>2015-01</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr"/>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>华金同达（深圳）投资合伙企业（有限合伙）</t>
+          <t>上海杉创智至创业投资合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr"/>
-      <c r="G105" t="inlineStr"/>
-      <c r="H105" t="inlineStr"/>
-      <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>59.4667</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>2000.0019</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>2000.0</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>0.0019</t>
+        </is>
+      </c>
       <c r="K105" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4626,75 +5865,99 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>2015-07-09</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr"/>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>杭州达晨创程股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E106" t="inlineStr"/>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr"/>
-      <c r="H106" t="inlineStr"/>
-      <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
+      <c r="F106" t="inlineStr"/>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>51.959</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>1747.5007</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>1747.5</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>0.0007</t>
+        </is>
+      </c>
       <c r="K106" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="L106" t="inlineStr"/>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>price×shares vs amount diff=0.0%</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>2015-07-09</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr"/>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr"/>
-      <c r="G107" t="inlineStr"/>
-      <c r="H107" t="inlineStr"/>
-      <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>999.9993</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>-0.0007</t>
+        </is>
+      </c>
       <c r="K107" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4702,37 +5965,49 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>2015-07-09</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr"/>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>QM101 Limited</t>
+          <t>深圳市达晨财智创业投资管理有限公司</t>
         </is>
       </c>
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr"/>
-      <c r="G108" t="inlineStr"/>
-      <c r="H108" t="inlineStr"/>
-      <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>999.9993</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>-0.0007</t>
+        </is>
+      </c>
       <c r="K108" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4740,37 +6015,49 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>2015-07-09</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr"/>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>深圳市财智创赢私募股权投资企业(有限合伙)</t>
         </is>
       </c>
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr"/>
-      <c r="G109" t="inlineStr"/>
-      <c r="H109" t="inlineStr"/>
-      <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>10.1093</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>339.999</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>340.0</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>-0.001</t>
+        </is>
+      </c>
       <c r="K109" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4778,29 +6065,29 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>1992-12-04</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2023-03-24</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>上海市青浦县徐泾乡工业公司</t>
         </is>
       </c>
       <c r="E110" t="inlineStr"/>
@@ -4823,29 +6110,37 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>1992-12-04</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2023-03-24</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr"/>
-      <c r="G111" t="inlineStr"/>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
       <c r="H111" t="inlineStr"/>
-      <c r="I111" t="inlineStr"/>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr">
         <is>
@@ -4854,36 +6149,44 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>1992-12-04</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2023-03-24</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>QM101 Limited</t>
+          <t>上海泽升贸易有限公司</t>
         </is>
       </c>
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr"/>
-      <c r="G112" t="inlineStr"/>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>8976.0</t>
+        </is>
+      </c>
       <c r="H112" t="inlineStr"/>
-      <c r="I112" t="inlineStr"/>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>8976.0</t>
+        </is>
+      </c>
       <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr">
         <is>
@@ -4892,36 +6195,44 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>1992-12-04</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2023-03-24</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>汇智同裕（深圳）投资合伙企业（有限合伙）</t>
+          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr"/>
-      <c r="G113" t="inlineStr"/>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>1020.0</t>
+        </is>
+      </c>
       <c r="H113" t="inlineStr"/>
-      <c r="I113" t="inlineStr"/>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>1020.0</t>
+        </is>
+      </c>
       <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr">
         <is>
@@ -4937,22 +6248,22 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>1992-12-04</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2023-03-24</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>友升太平洋(美国)投资有限公司</t>
         </is>
       </c>
       <c r="E114" t="inlineStr"/>
@@ -4975,42 +6286,38 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>920100_三协电机</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr"/>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>1992-12-04</t>
+        </is>
+      </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2023-09-06</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>盛祎等15名自然人</t>
+          <t>罗世兵</t>
         </is>
       </c>
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr">
         <is>
-          <t>321.5</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>1739.315</t>
-        </is>
-      </c>
+          <t>204.0</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr"/>
       <c r="I115" t="inlineStr">
         <is>
-          <t>1723.09</t>
-        </is>
-      </c>
-      <c r="J115" t="inlineStr">
-        <is>
-          <t>16.225</t>
-        </is>
-      </c>
+          <t>204.0</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5018,36 +6325,44 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>price×shares vs amount diff=0.9%</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>920100_三协电机</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2002-11-07</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2022-08-09</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>深圳市稳正景明创业投资企业(有限合伙)</t>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr"/>
-      <c r="G116" t="inlineStr"/>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
       <c r="H116" t="inlineStr"/>
-      <c r="I116" t="inlineStr"/>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
       <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr">
         <is>
@@ -5063,29 +6378,37 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>920100_三协电机</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2002-11-07</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2022-08-09</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>盛祎</t>
+          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr"/>
-      <c r="G117" t="inlineStr"/>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
       <c r="H117" t="inlineStr"/>
-      <c r="I117" t="inlineStr"/>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
       <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr">
         <is>
@@ -5094,35 +6417,47 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>920100_三协电机</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2002-11-07</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2022-08-09</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>朱绶青</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr"/>
+          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
       <c r="F118" t="inlineStr"/>
-      <c r="G118" t="inlineStr"/>
-      <c r="H118" t="inlineStr"/>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>3600.0</t>
+        </is>
+      </c>
       <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr">
@@ -5139,33 +6474,37 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2016-12-14</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>四方股份</t>
+          <t>上海骁墨信息技术服务中心(有限合伙)</t>
         </is>
       </c>
       <c r="E119" t="inlineStr"/>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>1200.0</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr"/>
+      <c r="F119" t="inlineStr"/>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
       <c r="H119" t="inlineStr"/>
-      <c r="I119" t="inlineStr"/>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr">
         <is>
@@ -5174,35 +6513,47 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2016-12-14</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>牛威</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr"/>
+          <t>上海泽升贸易有限公司</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>8976.0</t>
+        </is>
+      </c>
       <c r="F120" t="inlineStr"/>
-      <c r="G120" t="inlineStr"/>
-      <c r="H120" t="inlineStr"/>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>8976.0</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>17952.0</t>
+        </is>
+      </c>
       <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr">
@@ -5212,35 +6563,47 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2016-12-14</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>吴功友</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr"/>
+          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>1020.0</t>
+        </is>
+      </c>
       <c r="F121" t="inlineStr"/>
-      <c r="G121" t="inlineStr"/>
-      <c r="H121" t="inlineStr"/>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>1020.0</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>2040.0</t>
+        </is>
+      </c>
       <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr">
@@ -5250,39 +6613,47 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2016-12-14</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>牛威(罗永红代持)</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr"/>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>400.0</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr"/>
-      <c r="H122" t="inlineStr"/>
+          <t>罗世兵</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>204.0</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr"/>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>204.0</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>408.0</t>
+        </is>
+      </c>
       <c r="I122" t="inlineStr"/>
       <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr">
@@ -5299,33 +6670,37 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2016-12-14</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>吴功友(王金林代持)</t>
+          <t>深圳市达晨财智创业投资管理有限公司</t>
         </is>
       </c>
       <c r="E123" t="inlineStr"/>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>400.0</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr"/>
+      <c r="F123" t="inlineStr"/>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
       <c r="H123" t="inlineStr"/>
-      <c r="I123" t="inlineStr"/>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
       <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr">
         <is>
@@ -5334,42 +6709,42 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>策星银河</t>
+          <t>江西赣江新区财投晨源股权投资中心(有限合伙)</t>
         </is>
       </c>
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr">
         <is>
-          <t>279.0</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr">
         <is>
-          <t>279.0</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="J124" t="inlineStr"/>
@@ -5387,33 +6762,37 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>牛威</t>
+          <t>上海联炻企业管理中心(有限合伙)</t>
         </is>
       </c>
       <c r="E125" t="inlineStr"/>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr"/>
+      <c r="F125" t="inlineStr"/>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>297.3333</t>
+        </is>
+      </c>
       <c r="H125" t="inlineStr"/>
-      <c r="I125" t="inlineStr"/>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>297.3333</t>
+        </is>
+      </c>
       <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr">
         <is>
@@ -5422,42 +6801,42 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>幸福二期</t>
+          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr">
         <is>
-          <t>300.0</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="H126" t="inlineStr"/>
       <c r="I126" t="inlineStr">
         <is>
-          <t>300.0</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="J126" t="inlineStr"/>
@@ -5475,37 +6854,45 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>策星揽月</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr"/>
-      <c r="F127" t="inlineStr"/>
+          <t>上海骁墨信息技术服务中心(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>1500.0</t>
+        </is>
+      </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>412.5</t>
-        </is>
-      </c>
-      <c r="H127" t="inlineStr"/>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>412.5</t>
-        </is>
-      </c>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
       <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr">
         <is>
@@ -5514,44 +6901,52 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>幸福一期</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr"/>
-      <c r="F128" t="inlineStr"/>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>7000.0</t>
+        </is>
+      </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>917.4219</t>
-        </is>
-      </c>
-      <c r="H128" t="inlineStr"/>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>917.4219</t>
-        </is>
-      </c>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>1680.0</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
       <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr">
         <is>
@@ -5560,42 +6955,42 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>策星九天</t>
+          <t>安吉璞颉企业管理合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr">
         <is>
-          <t>2345.0781</t>
+          <t>148.6667</t>
         </is>
       </c>
       <c r="H129" t="inlineStr"/>
       <c r="I129" t="inlineStr">
         <is>
-          <t>2345.0781</t>
+          <t>148.6667</t>
         </is>
       </c>
       <c r="J129" t="inlineStr"/>
@@ -5613,33 +7008,37 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>吴功友</t>
+          <t>上海杉创智至创业投资合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E130" t="inlineStr"/>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr"/>
+      <c r="F130" t="inlineStr"/>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>59.4667</t>
+        </is>
+      </c>
       <c r="H130" t="inlineStr"/>
-      <c r="I130" t="inlineStr"/>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>59.4667</t>
+        </is>
+      </c>
       <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr">
         <is>
@@ -5648,42 +7047,42 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>策星逐日</t>
+          <t>深圳市财智创赢私募股权投资企业(有限合伙)</t>
         </is>
       </c>
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr"/>
       <c r="G131" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>10.1093</t>
         </is>
       </c>
       <c r="H131" t="inlineStr"/>
       <c r="I131" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>10.1093</t>
         </is>
       </c>
       <c r="J131" t="inlineStr"/>
@@ -5701,37 +7100,45 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>中科星图股份有限公司</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr"/>
-      <c r="F132" t="inlineStr"/>
+          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>3000.0</t>
+        </is>
+      </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>3825.0</t>
-        </is>
-      </c>
-      <c r="H132" t="inlineStr"/>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>3825.0</t>
-        </is>
-      </c>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>720.0</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
       <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr">
         <is>
@@ -5740,49 +7147,45 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr"/>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>中科星图股份有限公司 (认缴→存量)</t>
+          <t>深圳市杉晖创业投资合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr"/>
       <c r="G133" t="inlineStr">
         <is>
-          <t>3825.0</t>
-        </is>
-      </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>3825.0</t>
-        </is>
-      </c>
+          <t>297.3333</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr"/>
       <c r="I133" t="inlineStr">
         <is>
-          <t>3825.0</t>
-        </is>
-      </c>
-      <c r="J133" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>297.3333</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5790,49 +7193,45 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr"/>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>策星九天 (认缴→存量)</t>
+          <t>深圳市达晨创程私募股权投资基金企业(有限合伙)</t>
         </is>
       </c>
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr">
         <is>
-          <t>2345.0781</t>
-        </is>
-      </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>2345.0781</t>
-        </is>
-      </c>
+          <t>86.5984</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr"/>
       <c r="I134" t="inlineStr">
         <is>
-          <t>2345.0781</t>
-        </is>
-      </c>
-      <c r="J134" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>86.5984</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr"/>
       <c r="K134" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5840,49 +7239,45 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr"/>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>幸福一期 (认缴→存量)</t>
+          <t>杭州达晨创程股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr"/>
       <c r="G135" t="inlineStr">
         <is>
-          <t>917.4219</t>
-        </is>
-      </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>917.4219</t>
-        </is>
-      </c>
+          <t>51.959</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr"/>
       <c r="I135" t="inlineStr">
         <is>
-          <t>917.4219</t>
-        </is>
-      </c>
-      <c r="J135" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>51.959</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5890,42 +7285,42 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B136" t="inlineStr"/>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>策星揽月 (认缴→存量)</t>
+          <t>上海泽升贸易有限公司 (认缴→存量)</t>
         </is>
       </c>
       <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr"/>
       <c r="G136" t="inlineStr">
         <is>
-          <t>412.5</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>412.5</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>412.5</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -5947,35 +7342,35 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B137" t="inlineStr"/>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>幸福二期 (认缴→存量)</t>
+          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr"/>
       <c r="G137" t="inlineStr">
         <is>
-          <t>300.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>300.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>300.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -5997,35 +7392,35 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B138" t="inlineStr"/>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>策星银河 (认缴→存量)</t>
+          <t>共青城泽升投资管理合伙企业(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr"/>
       <c r="G138" t="inlineStr">
         <is>
-          <t>279.0</t>
+          <t>1020.0</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>279.0</t>
+          <t>1020.0</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>279.0</t>
+          <t>1020.0</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -6047,35 +7442,35 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B139" t="inlineStr"/>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>策星逐日 (认缴→存量)</t>
+          <t>罗世兵 (认缴→存量)</t>
         </is>
       </c>
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr"/>
       <c r="G139" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -6094,24 +7489,2932 @@
         </is>
       </c>
     </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr"/>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr"/>
+      <c r="F140" t="inlineStr"/>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
     <row r="141">
-      <c r="A141" s="3" t="inlineStr">
-        <is>
-          <t>认缴流量: 13 条</t>
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr"/>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr"/>
+      <c r="F141" t="inlineStr"/>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
         </is>
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="3" t="inlineStr">
-        <is>
-          <t>股权存量: 2 条</t>
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr"/>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>上海骁墨信息技术服务中心(有限合伙) (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr"/>
+      <c r="F142" t="inlineStr"/>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>生成时间: 2026-06-12T17:00:58.807950</t>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr"/>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>2022-12-19</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>深圳市杉晖创业投资合伙企业(有限合伙) (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr"/>
+      <c r="F143" t="inlineStr"/>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>297.3333</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>297.3333</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>297.3333</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr"/>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>2022-12-19</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>上海联炻企业管理中心(有限合伙) (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr"/>
+      <c r="F144" t="inlineStr"/>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>297.3333</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>297.3333</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>297.3333</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr"/>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>2022-12-19</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>安吉璞颉企业管理合伙企业(有限合伙) (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr"/>
+      <c r="F145" t="inlineStr"/>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>148.6667</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>148.6667</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>148.6667</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr"/>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>2022-12-19</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>江西赣江新区财投晨源股权投资中心(有限合伙) (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr"/>
+      <c r="F146" t="inlineStr"/>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>89.2</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>89.2</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>89.2</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr"/>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>2022-12-19</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>深圳市达晨创程私募股权投资基金企业(有限合伙) (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr"/>
+      <c r="F147" t="inlineStr"/>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>86.5984</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>86.5984</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>86.5984</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr"/>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>2022-12-19</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>上海杉创智至创业投资合伙企业(有限合伙) (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr"/>
+      <c r="F148" t="inlineStr"/>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>59.4667</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>59.4667</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>59.4667</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr"/>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>2022-12-19</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>杭州达晨创程股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr"/>
+      <c r="F149" t="inlineStr"/>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>51.959</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>51.959</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>51.959</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr"/>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>2022-12-19</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr"/>
+      <c r="F150" t="inlineStr"/>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr"/>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>2022-12-19</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>深圳市达晨财智创业投资管理有限公司 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr"/>
+      <c r="F151" t="inlineStr"/>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr"/>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>2022-12-19</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>深圳市财智创赢私募股权投资企业(有限合伙) (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr"/>
+      <c r="F152" t="inlineStr"/>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>10.1093</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>10.1093</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>10.1093</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>688758_赛分科技</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>国寿疌泉</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr"/>
+      <c r="F153" t="inlineStr"/>
+      <c r="G153" t="inlineStr"/>
+      <c r="H153" t="inlineStr"/>
+      <c r="I153" t="inlineStr"/>
+      <c r="J153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>688758_赛分科技</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Cheer Rise Consultants Limited</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr"/>
+      <c r="F154" t="inlineStr"/>
+      <c r="G154" t="inlineStr"/>
+      <c r="H154" t="inlineStr"/>
+      <c r="I154" t="inlineStr"/>
+      <c r="J154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>688758_赛分科技</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>复星惟盈</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr"/>
+      <c r="F155" t="inlineStr"/>
+      <c r="G155" t="inlineStr"/>
+      <c r="H155" t="inlineStr"/>
+      <c r="I155" t="inlineStr"/>
+      <c r="J155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>688758_赛分科技</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>苏州贤达</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr"/>
+      <c r="F156" t="inlineStr"/>
+      <c r="G156" t="inlineStr"/>
+      <c r="H156" t="inlineStr"/>
+      <c r="I156" t="inlineStr"/>
+      <c r="J156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>688758_赛分科技</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>黄学英</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr"/>
+      <c r="F157" t="inlineStr"/>
+      <c r="G157" t="inlineStr"/>
+      <c r="H157" t="inlineStr"/>
+      <c r="I157" t="inlineStr"/>
+      <c r="J157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>688758_赛分科技</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>史建伟</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr"/>
+      <c r="F158" t="inlineStr"/>
+      <c r="G158" t="inlineStr"/>
+      <c r="H158" t="inlineStr"/>
+      <c r="I158" t="inlineStr"/>
+      <c r="J158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>688758_赛分科技</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>周金清</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr"/>
+      <c r="F159" t="inlineStr"/>
+      <c r="G159" t="inlineStr"/>
+      <c r="H159" t="inlineStr"/>
+      <c r="I159" t="inlineStr"/>
+      <c r="J159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>688758_赛分科技</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>周乃鼎</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr"/>
+      <c r="F160" t="inlineStr"/>
+      <c r="G160" t="inlineStr"/>
+      <c r="H160" t="inlineStr"/>
+      <c r="I160" t="inlineStr"/>
+      <c r="J160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>688758_赛分科技</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>华泰大健康一号</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr"/>
+      <c r="F161" t="inlineStr"/>
+      <c r="G161" t="inlineStr"/>
+      <c r="H161" t="inlineStr"/>
+      <c r="I161" t="inlineStr"/>
+      <c r="J161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>688758_赛分科技</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>高新同华</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr"/>
+      <c r="F162" t="inlineStr"/>
+      <c r="G162" t="inlineStr"/>
+      <c r="H162" t="inlineStr"/>
+      <c r="I162" t="inlineStr"/>
+      <c r="J162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>688758_赛分科技</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>陆民</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr"/>
+      <c r="F163" t="inlineStr"/>
+      <c r="G163" t="inlineStr"/>
+      <c r="H163" t="inlineStr"/>
+      <c r="I163" t="inlineStr"/>
+      <c r="J163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>688758_赛分科技</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>黄学英/刘鸿雁</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr"/>
+      <c r="F164" t="inlineStr"/>
+      <c r="G164" t="inlineStr"/>
+      <c r="H164" t="inlineStr"/>
+      <c r="I164" t="inlineStr"/>
+      <c r="J164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>EARN ACE LIMITED</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr"/>
+      <c r="F165" t="inlineStr"/>
+      <c r="G165" t="inlineStr"/>
+      <c r="H165" t="inlineStr"/>
+      <c r="I165" t="inlineStr"/>
+      <c r="J165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>深圳中证投资有限责任公司</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr"/>
+      <c r="F166" t="inlineStr"/>
+      <c r="G166" t="inlineStr"/>
+      <c r="H166" t="inlineStr"/>
+      <c r="I166" t="inlineStr"/>
+      <c r="J166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>华金同达（深圳）投资合伙企业（有限合伙）</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr"/>
+      <c r="F167" t="inlineStr"/>
+      <c r="G167" t="inlineStr"/>
+      <c r="H167" t="inlineStr"/>
+      <c r="I167" t="inlineStr"/>
+      <c r="J167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>香港迅雷有限公司</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr"/>
+      <c r="F168" t="inlineStr"/>
+      <c r="G168" t="inlineStr"/>
+      <c r="H168" t="inlineStr"/>
+      <c r="I168" t="inlineStr"/>
+      <c r="J168" t="inlineStr"/>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>北京岚锋创视网络科技有限公司</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr"/>
+      <c r="F169" t="inlineStr"/>
+      <c r="G169" t="inlineStr"/>
+      <c r="H169" t="inlineStr"/>
+      <c r="I169" t="inlineStr"/>
+      <c r="J169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>深圳市伊敦传媒投资基金合伙企业（有限合伙）</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr"/>
+      <c r="F170" t="inlineStr"/>
+      <c r="G170" t="inlineStr"/>
+      <c r="H170" t="inlineStr"/>
+      <c r="I170" t="inlineStr"/>
+      <c r="J170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>QM101 Limited</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr"/>
+      <c r="F171" t="inlineStr"/>
+      <c r="G171" t="inlineStr"/>
+      <c r="H171" t="inlineStr"/>
+      <c r="I171" t="inlineStr"/>
+      <c r="J171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>金石智娱股权投资（深圳）合伙企业（有限合伙）</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr"/>
+      <c r="F172" t="inlineStr"/>
+      <c r="G172" t="inlineStr"/>
+      <c r="H172" t="inlineStr"/>
+      <c r="I172" t="inlineStr"/>
+      <c r="J172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>厦门富凯海创投资管理有限责任公司</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr"/>
+      <c r="F173" t="inlineStr"/>
+      <c r="G173" t="inlineStr"/>
+      <c r="H173" t="inlineStr"/>
+      <c r="I173" t="inlineStr"/>
+      <c r="J173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>2020-02-26</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>QM101 Limited</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr"/>
+      <c r="F174" t="inlineStr"/>
+      <c r="G174" t="inlineStr"/>
+      <c r="H174" t="inlineStr"/>
+      <c r="I174" t="inlineStr"/>
+      <c r="J174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>2020-02-26</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>EARN ACE LIMITED</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr"/>
+      <c r="F175" t="inlineStr"/>
+      <c r="G175" t="inlineStr"/>
+      <c r="H175" t="inlineStr"/>
+      <c r="I175" t="inlineStr"/>
+      <c r="J175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>2020-02-26</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>香港迅雷有限公司</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr"/>
+      <c r="F176" t="inlineStr"/>
+      <c r="G176" t="inlineStr"/>
+      <c r="H176" t="inlineStr"/>
+      <c r="I176" t="inlineStr"/>
+      <c r="J176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>2020-02-26</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>北京岚锋创视网络科技有限公司</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr"/>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr"/>
+      <c r="H177" t="inlineStr"/>
+      <c r="I177" t="inlineStr"/>
+      <c r="J177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L177" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>2020-02-26</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>2023-03-24</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>汇智同裕（深圳）投资合伙企业（有限合伙）</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr"/>
+      <c r="F178" t="inlineStr"/>
+      <c r="G178" t="inlineStr"/>
+      <c r="H178" t="inlineStr"/>
+      <c r="I178" t="inlineStr"/>
+      <c r="J178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>2020-02-26</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>2023-03-24</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>QM101 Limited</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr"/>
+      <c r="F179" t="inlineStr"/>
+      <c r="G179" t="inlineStr"/>
+      <c r="H179" t="inlineStr"/>
+      <c r="I179" t="inlineStr"/>
+      <c r="J179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>2020-02-26</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>2023-03-24</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>EARN ACE LIMITED</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr"/>
+      <c r="F180" t="inlineStr"/>
+      <c r="G180" t="inlineStr"/>
+      <c r="H180" t="inlineStr"/>
+      <c r="I180" t="inlineStr"/>
+      <c r="J180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>2020-02-26</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>2023-03-24</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>香港迅雷有限公司</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr"/>
+      <c r="F181" t="inlineStr"/>
+      <c r="G181" t="inlineStr"/>
+      <c r="H181" t="inlineStr"/>
+      <c r="I181" t="inlineStr"/>
+      <c r="J181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>2020-02-26</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>2023-03-24</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>北京岚锋创视网络科技有限公司</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr"/>
+      <c r="F182" t="inlineStr"/>
+      <c r="G182" t="inlineStr"/>
+      <c r="H182" t="inlineStr"/>
+      <c r="I182" t="inlineStr"/>
+      <c r="J182" t="inlineStr"/>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>920100_三协电机</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr"/>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>2023-09-06</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>盛祎等15名自然人</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr"/>
+      <c r="F183" t="inlineStr"/>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>321.5</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>1739.315</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>1723.09</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>16.225</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>price×shares vs amount diff=0.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>920100_三协电机</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>2002-11-07</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>2022-08-09</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>盛祎</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr"/>
+      <c r="F184" t="inlineStr"/>
+      <c r="G184" t="inlineStr"/>
+      <c r="H184" t="inlineStr"/>
+      <c r="I184" t="inlineStr"/>
+      <c r="J184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>920100_三协电机</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>2002-11-07</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>2022-08-09</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>深圳市稳正景明创业投资企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr"/>
+      <c r="F185" t="inlineStr"/>
+      <c r="G185" t="inlineStr"/>
+      <c r="H185" t="inlineStr"/>
+      <c r="I185" t="inlineStr"/>
+      <c r="J185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>920100_三协电机</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>2002-11-07</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>2022-08-09</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>朱绶青</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr"/>
+      <c r="F186" t="inlineStr"/>
+      <c r="G186" t="inlineStr"/>
+      <c r="H186" t="inlineStr"/>
+      <c r="I186" t="inlineStr"/>
+      <c r="J186" t="inlineStr"/>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>2016-12-14</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>四方股份</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr"/>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>1200.0</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr"/>
+      <c r="H187" t="inlineStr"/>
+      <c r="I187" t="inlineStr"/>
+      <c r="J187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>2016-12-14</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>吴功友(王金林代持)</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr"/>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>400.0</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr"/>
+      <c r="H188" t="inlineStr"/>
+      <c r="I188" t="inlineStr"/>
+      <c r="J188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>2016-12-14</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>牛威</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr"/>
+      <c r="F189" t="inlineStr"/>
+      <c r="G189" t="inlineStr"/>
+      <c r="H189" t="inlineStr"/>
+      <c r="I189" t="inlineStr"/>
+      <c r="J189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>2016-12-14</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>吴功友</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr"/>
+      <c r="F190" t="inlineStr"/>
+      <c r="G190" t="inlineStr"/>
+      <c r="H190" t="inlineStr"/>
+      <c r="I190" t="inlineStr"/>
+      <c r="J190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>2016-12-14</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>牛威(罗永红代持)</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr"/>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>400.0</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr"/>
+      <c r="H191" t="inlineStr"/>
+      <c r="I191" t="inlineStr"/>
+      <c r="J191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>策星九天</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr"/>
+      <c r="F192" t="inlineStr"/>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>2345.0781</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr"/>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>2345.0781</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>幸福二期</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr"/>
+      <c r="F193" t="inlineStr"/>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr"/>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr"/>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>策星逐日</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr"/>
+      <c r="F194" t="inlineStr"/>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>171.0</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr"/>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>171.0</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr"/>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>牛威</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr"/>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr"/>
+      <c r="H195" t="inlineStr"/>
+      <c r="I195" t="inlineStr"/>
+      <c r="J195" t="inlineStr"/>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>吴功友</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr"/>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr"/>
+      <c r="H196" t="inlineStr"/>
+      <c r="I196" t="inlineStr"/>
+      <c r="J196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>中科星图股份有限公司</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr"/>
+      <c r="F197" t="inlineStr"/>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>3825.0</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr"/>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>3825.0</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>幸福一期</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr"/>
+      <c r="F198" t="inlineStr"/>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>917.4219</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr"/>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>917.4219</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>策星揽月</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr"/>
+      <c r="F199" t="inlineStr"/>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>412.5</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr"/>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>412.5</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>策星银河</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr"/>
+      <c r="F200" t="inlineStr"/>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr"/>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr"/>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>中科星图股份有限公司 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr"/>
+      <c r="F201" t="inlineStr"/>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>3825.0</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>3825.0</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>3825.0</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr"/>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>策星九天 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr"/>
+      <c r="F202" t="inlineStr"/>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>2345.0781</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>2345.0781</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>2345.0781</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr"/>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>幸福一期 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr"/>
+      <c r="F203" t="inlineStr"/>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>917.4219</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>917.4219</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>917.4219</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr"/>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>策星揽月 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr"/>
+      <c r="F204" t="inlineStr"/>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>412.5</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>412.5</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>412.5</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr"/>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>幸福二期 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr"/>
+      <c r="F205" t="inlineStr"/>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr"/>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>策星银河 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr"/>
+      <c r="F206" t="inlineStr"/>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr"/>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>策星逐日 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr"/>
+      <c r="F207" t="inlineStr"/>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>171.0</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>171.0</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>171.0</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="3" t="inlineStr">
+        <is>
+          <t>认缴流量: 19 条</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="3" t="inlineStr">
+        <is>
+          <t>股权存量: 19 条</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>生成时间: 2026-06-12T17:05:42.663288</t>
         </is>
       </c>
     </row>
